--- a/workbook/capex_tracker.xlsx
+++ b/workbook/capex_tracker.xlsx
@@ -2041,7 +2041,7 @@
         <t>Source: [BABA] FY2025 6-K (filed 2025-08-06)
 Derivation:
   Derived: 9M = Q1+Q2+Q3
-Report: https://www.sec.gov/Archives/edgar/data/1577552/000110465925074564/tm2522605d1_ex99-2.htm</t>
+Report: https://www.sec.gov/Archives/edgar/data/1577552/000110465925085638/tm2524743d1_ex99-1.htm</t>
       </text>
     </comment>
     <comment ref="AR5" authorId="0" shapeId="0">
@@ -9666,6 +9666,17 @@
 Report: https://www.sec.gov/Archives/edgar/data/1577552/000095017025090161/baba-20250331.htm</t>
       </text>
     </comment>
+    <comment ref="AQ5" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BABA] FY2025 6-K (filed 2025-08-06)
+Section: 6-K Press Release — Cloud Intelligence Group
+Line item: "Cloud Intelligence Group For the quarter ended June 30, 2025, revenue from Cloud Intelligence Group was RMB33,398 million"
+Value: CNY 33,398M → $4,661M USD
+FX: CNY/USD 0.1396 @ 2025-06-30 (source: ECB via frankfurter.app)
+Method: baba-cloud-6k@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1577552/000110465925085638/tm2524743d1_ex99-1.htm</t>
+      </text>
+    </comment>
     <comment ref="AR5" authorId="0" shapeId="0">
       <text>
         <t>Source: [BABA] FY2025 6-K (filed 2025-11-25)
@@ -19648,7 +19659,7 @@
         <t>Source: [BABA] FY2025 6-K (filed 2025-08-06)
 Derivation:
   Derived: 9M = Q1+Q2+Q3
-Report: https://www.sec.gov/Archives/edgar/data/1577552/000110465925074564/tm2522605d1_ex99-2.htm</t>
+Report: https://www.sec.gov/Archives/edgar/data/1577552/000110465925085638/tm2524743d1_ex99-1.htm</t>
       </text>
     </comment>
     <comment ref="AS20" authorId="0" shapeId="0">
@@ -20071,6 +20082,17 @@
 FX: CNY/USD 0.1379 @ 2025-03-31 (source: ECB via frankfurter.app)
 Method: claude-code
 Report: https://www.sec.gov/Archives/edgar/data/1577552/000095017025090161/baba-20250331.htm</t>
+      </text>
+    </comment>
+    <comment ref="AR21" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BABA] FY2025 6-K (filed 2025-08-06)
+Section: 6-K Press Release — Cloud Intelligence Group
+Line item: "Cloud Intelligence Group For the quarter ended June 30, 2025, revenue from Cloud Intelligence Group was RMB33,398 million"
+Value: CNY 33,398M → $4,661M USD
+FX: CNY/USD 0.1396 @ 2025-06-30 (source: ECB via frankfurter.app)
+Method: baba-cloud-6k@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1577552/000110465925085638/tm2524743d1_ex99-1.htm</t>
       </text>
     </comment>
     <comment ref="AS21" authorId="0" shapeId="0">
@@ -29593,7 +29615,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-04-18 21:47 UTC</t>
+          <t>2026-04-19 15:09 UTC</t>
         </is>
       </c>
     </row>
@@ -29617,7 +29639,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2561</t>
         </is>
       </c>
     </row>
@@ -30109,7 +30131,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-18 21:47 UTC</t>
+          <t>2026-04-19 15:09 UTC</t>
         </is>
       </c>
     </row>
@@ -30120,7 +30142,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2560</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="5">
@@ -30284,7 +30306,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -36228,6 +36250,9 @@
       </c>
       <c r="AP5" s="9" t="n">
         <v>16273</v>
+      </c>
+      <c r="AQ5" s="9" t="n">
+        <v>4661</v>
       </c>
       <c r="AR5" s="9" t="n">
         <v>5594</v>
@@ -41067,6 +41092,9 @@
       <c r="AQ21" s="9" t="n">
         <v>16273</v>
       </c>
+      <c r="AR21" s="9" t="n">
+        <v>4661</v>
+      </c>
       <c r="AS21" s="9" t="n">
         <v>5594</v>
       </c>

--- a/workbook/capex_tracker.xlsx
+++ b/workbook/capex_tracker.xlsx
@@ -9699,6 +9699,287 @@
 Report: https://www.sec.gov/Archives/edgar/data/1577552/000110465926032060/tm269353d1_ex99-1.htm</t>
       </text>
     </comment>
+    <comment ref="R6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2019 6-K (filed 2019-03-31)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
+Line item: "[PROXY: other_revenues] Other revenues were RMB 6.5 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 6,500M → $969M USD
+FX: CNY/USD 0.1490 @ 2019-03-31 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312519152169/d727883dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="S6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2019 6-K (filed 2019-06-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
+Line item: "[PROXY: other_revenues] Other revenues were RMB 7.1 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 7,100M → $1,033M USD
+FX: CNY/USD 0.1456 @ 2019-06-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312519226398/d691391dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="T6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2019 6-K (filed 2019-09-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
+Line item: "[PROXY: other_revenues] Other revenues were RMB 7.6 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 7,600M → $1,064M USD
+FX: CNY/USD 0.1400 @ 2019-09-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312519290462/d827580dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="U6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2019 20-F (filed 2020-03-13)
+Section: Baidu Core Revenue by type, Cloud services
+Line item: "Cloud services 6,370 (direct disclosure in Baidu Core revenue)"
+Value: CNY 6,370M → $915M USD
+FX: CNY/USD 0.1436 @ 2019-12-31 (source: ECB via frankfurter.app)
+Method: claude-code
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312520073092/d833212d20f.htm</t>
+      </text>
+    </comment>
+    <comment ref="V6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2020 6-K (filed 2020-03-31)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
+Line item: "[PROXY: other_revenues] Other revenues were RMB 8.3 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 8,300M → $1,169M USD
+FX: CNY/USD 0.1409 @ 2020-03-31 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312520146636/d927979dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="W6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2020 6-K (filed 2020-06-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
+Line item: "[PROXY: other_revenues] Other revenues were RMB 8.3 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 8,300M → $1,173M USD
+FX: CNY/USD 0.1414 @ 2020-06-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312520222418/d82228dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="Y6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2020 20-F (filed 2021-03-09)
+Section: Baidu Core Revenue by type, Cloud services
+Line item: "Cloud services 9,173 (direct disclosure in Baidu Core revenue)"
+Value: CNY 9,173M → $1,403M USD
+FX: CNY/USD 0.1530 @ 2020-12-31 (source: ECB via frankfurter.app)
+Method: claude-code
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312521074038/d46900d20f.htm</t>
+      </text>
+    </comment>
+    <comment ref="AA6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2021 6-K (filed 2021-06-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB 5.0 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 5,000M → $774M USD
+FX: CNY/USD 0.1549 @ 2021-06-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312521245436/d175957dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AC6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2021 20-F (filed 2022-03-28)
+Section: Baidu Core Revenue by type, Cloud services
+Line item: "Cloud services 15,070 (direct disclosure in Baidu Core revenue)"
+Value: CNY 15,070M → $2,372M USD
+FX: CNY/USD 0.1574 @ 2021-12-31 (source: ECB via frankfurter.app)
+Method: claude-code
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312522086036/d272011d20f.htm</t>
+      </text>
+    </comment>
+    <comment ref="AD6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2022 6-K (filed 2022-03-31)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB5.7 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 5,700M → $899M USD
+FX: CNY/USD 0.1577 @ 2022-03-31 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312522161778/d335526dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AE6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2022 6-K (filed 2022-06-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB 6.1 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 6,100M → $910M USD
+FX: CNY/USD 0.1492 @ 2022-06-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312522234500/d393584dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AF6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2022 6-K (filed 2022-09-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.5 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 6,500M → $913M USD
+FX: CNY/USD 0.1405 @ 2022-09-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312522291565/d313453dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AG6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2022 20-F (filed 2023-03-22)
+Section: Baidu Core Revenue by type, Cloud services
+Line item: "Cloud services 17,721 (direct disclosure in Baidu Core revenue)"
+Value: CNY 17,721M → $2,569M USD
+FX: CNY/USD 0.1449 @ 2022-12-31 (source: ECB via frankfurter.app)
+Method: claude-code
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312523076192/d362351d20f.htm</t>
+      </text>
+    </comment>
+    <comment ref="AH6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2023 6-K (filed 2023-03-31)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.4 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 6,400M → $931M USD
+FX: CNY/USD 0.1455 @ 2023-03-31 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312523145594/d472126dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AI6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2023 6-K (filed 2023-06-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.8 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 6,800M → $935M USD
+FX: CNY/USD 0.1376 @ 2023-06-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312523217413/d502468dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AJ6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2023 6-K (filed 2023-09-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.9 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 6,900M → $945M USD
+FX: CNY/USD 0.1370 @ 2023-09-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312523281151/d551070dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AK6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2023 20-F (filed 2024-03-15)
+Derivation:
+  Baidu reports revenue as "Online marketing services" and "Others".
+  Per 20-F footnote (i): "Others mainly include revenue from cloud services and iQIYI's video membership services".
+  iQIYI (NASDAQ: IQ) is a separately listed subsidiary whose standalone revenue is disclosed in Baidu's segment table.
+  Note: overstates cloud slightly — "Others" includes non-cloud, non-iQIYI items.
+Value: CNY 21,522M → $3,029M USD
+FX: CNY/USD 0.1407 @ 2023-12-31 (source: ECB via frankfurter.app)
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312524068527/d584913d20f.htm</t>
+      </text>
+    </comment>
+    <comment ref="AL6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2024 6-K (filed 2024-03-31)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.8 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 6,800M → $941M USD
+FX: CNY/USD 0.1384 @ 2024-03-31 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312524140513/d782149dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AM6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2024 6-K (filed 2024-06-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB7.5 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 7,500M → $1,033M USD
+FX: CNY/USD 0.1377 @ 2024-06-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312524204906/d227518dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AN6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2024 6-K (filed 2024-09-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB7.7 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 7,700M → $1,098M USD
+FX: CNY/USD 0.1426 @ 2024-09-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312524263052/d802709dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AO6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2024 20-F (filed 2025-03-28)
+Derivation:
+  Baidu reports revenue as "Online marketing services" and "Others".
+  Per 20-F footnote (i): "Others mainly include revenue from cloud services and iQIYI's video membership services".
+  iQIYI (NASDAQ: IQ) is a separately listed subsidiary whose standalone revenue is disclosed in Baidu's segment table.
+  Note: overstates cloud slightly — "Others" includes non-cloud, non-iQIYI items.
+Value: CNY 25,337M → $3,471M USD
+FX: CNY/USD 0.1370 @ 2024-12-31 (source: ECB via frankfurter.app)
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312525066199/d853848d20f.htm</t>
+      </text>
+    </comment>
+    <comment ref="AP6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2025 6-K (filed 2025-03-31)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB9.4 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 9,400M → $1,296M USD
+FX: CNY/USD 0.1379 @ 2025-03-31 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312525123961/d58002dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AQ6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2025 6-K (filed 2025-06-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB10.0 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 10,000M → $1,396M USD
+FX: CNY/USD 0.1396 @ 2025-06-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312525183792/d938996dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AR6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2025 6-K (filed 2025-09-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB9.3 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 9,300M → $1,306M USD
+FX: CNY/USD 0.1405 @ 2025-09-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312525285391/d52736dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AS6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2025 20-F (filed 2026-03-17)
+Derivation:
+  Baidu reports revenue as "Online marketing services" and "Others".
+  Per 20-F footnote (i): "Others mainly include revenue from cloud services and iQIYI's video membership services".
+  iQIYI (NASDAQ: IQ) is a separately listed subsidiary whose standalone revenue is disclosed in Baidu's segment table.
+  Note: overstates cloud slightly — "Others" includes non-cloud, non-iQIYI items.
+Value: CNY 33,952M → $4,850M USD
+FX: CNY/USD 0.1428 @ 2025-12-31 (source: ECB via frankfurter.app)
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312526109289/d38065d20f.htm</t>
+      </text>
+    </comment>
     <comment ref="AL7" authorId="0" shapeId="0">
       <text>
         <t>Source: [CRWV] FY2024 Q1 10-Q (filed 2025-05-15)
@@ -20592,6 +20873,287 @@
 Section: Consolidated Statements of Income, line "Total revenue"
 Value: $18,458M (as reported)
 Method: XBRL companyfacts API
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312526109289/d38065d20f.htm</t>
+      </text>
+    </comment>
+    <comment ref="S27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2019 6-K (filed 2019-03-31)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
+Line item: "[PROXY: other_revenues] Other revenues were RMB 6.5 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 6,500M → $969M USD
+FX: CNY/USD 0.1490 @ 2019-03-31 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312519152169/d727883dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="T27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2019 6-K (filed 2019-06-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
+Line item: "[PROXY: other_revenues] Other revenues were RMB 7.1 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 7,100M → $1,033M USD
+FX: CNY/USD 0.1456 @ 2019-06-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312519226398/d691391dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="U27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2019 6-K (filed 2019-09-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
+Line item: "[PROXY: other_revenues] Other revenues were RMB 7.6 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 7,600M → $1,064M USD
+FX: CNY/USD 0.1400 @ 2019-09-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312519290462/d827580dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="V27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2019 20-F (filed 2020-03-13)
+Section: Baidu Core Revenue by type, Cloud services
+Line item: "Cloud services 6,370 (direct disclosure in Baidu Core revenue)"
+Value: CNY 6,370M → $915M USD
+FX: CNY/USD 0.1436 @ 2019-12-31 (source: ECB via frankfurter.app)
+Method: claude-code
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312520073092/d833212d20f.htm</t>
+      </text>
+    </comment>
+    <comment ref="W27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2020 6-K (filed 2020-03-31)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
+Line item: "[PROXY: other_revenues] Other revenues were RMB 8.3 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 8,300M → $1,169M USD
+FX: CNY/USD 0.1409 @ 2020-03-31 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312520146636/d927979dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="X27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2020 6-K (filed 2020-06-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
+Line item: "[PROXY: other_revenues] Other revenues were RMB 8.3 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 8,300M → $1,173M USD
+FX: CNY/USD 0.1414 @ 2020-06-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312520222418/d82228dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="Z27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2020 20-F (filed 2021-03-09)
+Section: Baidu Core Revenue by type, Cloud services
+Line item: "Cloud services 9,173 (direct disclosure in Baidu Core revenue)"
+Value: CNY 9,173M → $1,403M USD
+FX: CNY/USD 0.1530 @ 2020-12-31 (source: ECB via frankfurter.app)
+Method: claude-code
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312521074038/d46900d20f.htm</t>
+      </text>
+    </comment>
+    <comment ref="AB27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2021 6-K (filed 2021-06-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB 5.0 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 5,000M → $774M USD
+FX: CNY/USD 0.1549 @ 2021-06-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312521245436/d175957dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AD27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2021 20-F (filed 2022-03-28)
+Section: Baidu Core Revenue by type, Cloud services
+Line item: "Cloud services 15,070 (direct disclosure in Baidu Core revenue)"
+Value: CNY 15,070M → $2,372M USD
+FX: CNY/USD 0.1574 @ 2021-12-31 (source: ECB via frankfurter.app)
+Method: claude-code
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312522086036/d272011d20f.htm</t>
+      </text>
+    </comment>
+    <comment ref="AE27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2022 6-K (filed 2022-03-31)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB5.7 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 5,700M → $899M USD
+FX: CNY/USD 0.1577 @ 2022-03-31 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312522161778/d335526dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AF27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2022 6-K (filed 2022-06-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB 6.1 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 6,100M → $910M USD
+FX: CNY/USD 0.1492 @ 2022-06-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312522234500/d393584dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AG27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2022 6-K (filed 2022-09-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.5 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 6,500M → $913M USD
+FX: CNY/USD 0.1405 @ 2022-09-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312522291565/d313453dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AH27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2022 20-F (filed 2023-03-22)
+Section: Baidu Core Revenue by type, Cloud services
+Line item: "Cloud services 17,721 (direct disclosure in Baidu Core revenue)"
+Value: CNY 17,721M → $2,569M USD
+FX: CNY/USD 0.1449 @ 2022-12-31 (source: ECB via frankfurter.app)
+Method: claude-code
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312523076192/d362351d20f.htm</t>
+      </text>
+    </comment>
+    <comment ref="AI27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2023 6-K (filed 2023-03-31)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.4 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 6,400M → $931M USD
+FX: CNY/USD 0.1455 @ 2023-03-31 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312523145594/d472126dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AJ27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2023 6-K (filed 2023-06-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.8 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 6,800M → $935M USD
+FX: CNY/USD 0.1376 @ 2023-06-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312523217413/d502468dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AK27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2023 6-K (filed 2023-09-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.9 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 6,900M → $945M USD
+FX: CNY/USD 0.1370 @ 2023-09-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312523281151/d551070dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AL27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2023 20-F (filed 2024-03-15)
+Derivation:
+  Baidu reports revenue as "Online marketing services" and "Others".
+  Per 20-F footnote (i): "Others mainly include revenue from cloud services and iQIYI's video membership services".
+  iQIYI (NASDAQ: IQ) is a separately listed subsidiary whose standalone revenue is disclosed in Baidu's segment table.
+  Note: overstates cloud slightly — "Others" includes non-cloud, non-iQIYI items.
+Value: CNY 21,522M → $3,029M USD
+FX: CNY/USD 0.1407 @ 2023-12-31 (source: ECB via frankfurter.app)
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312524068527/d584913d20f.htm</t>
+      </text>
+    </comment>
+    <comment ref="AM27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2024 6-K (filed 2024-03-31)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.8 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 6,800M → $941M USD
+FX: CNY/USD 0.1384 @ 2024-03-31 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312524140513/d782149dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AN27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2024 6-K (filed 2024-06-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB7.5 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 7,500M → $1,033M USD
+FX: CNY/USD 0.1377 @ 2024-06-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312524204906/d227518dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AO27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2024 6-K (filed 2024-09-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB7.7 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 7,700M → $1,098M USD
+FX: CNY/USD 0.1426 @ 2024-09-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312524263052/d802709dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AP27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2024 20-F (filed 2025-03-28)
+Derivation:
+  Baidu reports revenue as "Online marketing services" and "Others".
+  Per 20-F footnote (i): "Others mainly include revenue from cloud services and iQIYI's video membership services".
+  iQIYI (NASDAQ: IQ) is a separately listed subsidiary whose standalone revenue is disclosed in Baidu's segment table.
+  Note: overstates cloud slightly — "Others" includes non-cloud, non-iQIYI items.
+Value: CNY 25,337M → $3,471M USD
+FX: CNY/USD 0.1370 @ 2024-12-31 (source: ECB via frankfurter.app)
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312525066199/d853848d20f.htm</t>
+      </text>
+    </comment>
+    <comment ref="AQ27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2025 6-K (filed 2025-03-31)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB9.4 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 9,400M → $1,296M USD
+FX: CNY/USD 0.1379 @ 2025-03-31 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312525123961/d58002dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AR27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2025 6-K (filed 2025-06-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB10.0 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 10,000M → $1,396M USD
+FX: CNY/USD 0.1396 @ 2025-06-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312525183792/d938996dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AS27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2025 6-K (filed 2025-09-30)
+Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
+Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB9.3 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
+Value: CNY 9,300M → $1,306M USD
+FX: CNY/USD 0.1405 @ 2025-09-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-6k-proxy@0.1.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312525285391/d52736dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AT27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2025 20-F (filed 2026-03-17)
+Derivation:
+  Baidu reports revenue as "Online marketing services" and "Others".
+  Per 20-F footnote (i): "Others mainly include revenue from cloud services and iQIYI's video membership services".
+  iQIYI (NASDAQ: IQ) is a separately listed subsidiary whose standalone revenue is disclosed in Baidu's segment table.
+  Note: overstates cloud slightly — "Others" includes non-cloud, non-iQIYI items.
+Value: CNY 33,952M → $4,850M USD
+FX: CNY/USD 0.1428 @ 2025-12-31 (source: ECB via frankfurter.app)
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312526109289/d38065d20f.htm</t>
       </text>
     </comment>
@@ -29615,7 +30177,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-04-19 15:09 UTC</t>
+          <t>2026-04-19 15:17 UTC</t>
         </is>
       </c>
     </row>
@@ -29639,7 +30201,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2579</t>
         </is>
       </c>
     </row>
@@ -30131,7 +30693,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-19 15:09 UTC</t>
+          <t>2026-04-19 15:17 UTC</t>
         </is>
       </c>
     </row>
@@ -30142,7 +30704,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2561</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="5">
@@ -30336,11 +30898,11 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>xbrl-verified,reconcile-derived,claude-code,llm-dual-agent,6k-press-release</t>
+          <t>xbrl-verified,reconcile-derived,claude-code,llm-dual-agent,6k-press-release,bidu-cloud-6k-proxy@0.1.0</t>
         </is>
       </c>
     </row>
@@ -36266,6 +36828,81 @@
         <is>
           <t>BIDU</t>
         </is>
+      </c>
+      <c r="R6" s="9" t="n">
+        <v>969</v>
+      </c>
+      <c r="S6" s="9" t="n">
+        <v>1033</v>
+      </c>
+      <c r="T6" s="9" t="n">
+        <v>1064</v>
+      </c>
+      <c r="U6" s="9" t="n">
+        <v>915</v>
+      </c>
+      <c r="V6" s="9" t="n">
+        <v>1169</v>
+      </c>
+      <c r="W6" s="9" t="n">
+        <v>1173</v>
+      </c>
+      <c r="Y6" s="9" t="n">
+        <v>1403</v>
+      </c>
+      <c r="AA6" s="9" t="n">
+        <v>774</v>
+      </c>
+      <c r="AC6" s="9" t="n">
+        <v>2372</v>
+      </c>
+      <c r="AD6" s="9" t="n">
+        <v>899</v>
+      </c>
+      <c r="AE6" s="9" t="n">
+        <v>910</v>
+      </c>
+      <c r="AF6" s="9" t="n">
+        <v>913</v>
+      </c>
+      <c r="AG6" s="9" t="n">
+        <v>2569</v>
+      </c>
+      <c r="AH6" s="9" t="n">
+        <v>931</v>
+      </c>
+      <c r="AI6" s="9" t="n">
+        <v>935</v>
+      </c>
+      <c r="AJ6" s="9" t="n">
+        <v>945</v>
+      </c>
+      <c r="AK6" s="9" t="n">
+        <v>3029</v>
+      </c>
+      <c r="AL6" s="9" t="n">
+        <v>941</v>
+      </c>
+      <c r="AM6" s="9" t="n">
+        <v>1033</v>
+      </c>
+      <c r="AN6" s="9" t="n">
+        <v>1098</v>
+      </c>
+      <c r="AO6" s="9" t="n">
+        <v>3471</v>
+      </c>
+      <c r="AP6" s="9" t="n">
+        <v>1296</v>
+      </c>
+      <c r="AQ6" s="9" t="n">
+        <v>1396</v>
+      </c>
+      <c r="AR6" s="9" t="n">
+        <v>1306</v>
+      </c>
+      <c r="AS6" s="9" t="n">
+        <v>4850</v>
       </c>
     </row>
     <row r="7">
@@ -41293,6 +41930,81 @@
           <t>cloud_segment_revenue</t>
         </is>
       </c>
+      <c r="S27" s="9" t="n">
+        <v>969</v>
+      </c>
+      <c r="T27" s="9" t="n">
+        <v>1033</v>
+      </c>
+      <c r="U27" s="9" t="n">
+        <v>1064</v>
+      </c>
+      <c r="V27" s="9" t="n">
+        <v>915</v>
+      </c>
+      <c r="W27" s="9" t="n">
+        <v>1169</v>
+      </c>
+      <c r="X27" s="9" t="n">
+        <v>1173</v>
+      </c>
+      <c r="Z27" s="9" t="n">
+        <v>1403</v>
+      </c>
+      <c r="AB27" s="9" t="n">
+        <v>774</v>
+      </c>
+      <c r="AD27" s="9" t="n">
+        <v>2372</v>
+      </c>
+      <c r="AE27" s="9" t="n">
+        <v>899</v>
+      </c>
+      <c r="AF27" s="9" t="n">
+        <v>910</v>
+      </c>
+      <c r="AG27" s="9" t="n">
+        <v>913</v>
+      </c>
+      <c r="AH27" s="9" t="n">
+        <v>2569</v>
+      </c>
+      <c r="AI27" s="9" t="n">
+        <v>931</v>
+      </c>
+      <c r="AJ27" s="9" t="n">
+        <v>935</v>
+      </c>
+      <c r="AK27" s="9" t="n">
+        <v>945</v>
+      </c>
+      <c r="AL27" s="9" t="n">
+        <v>3029</v>
+      </c>
+      <c r="AM27" s="9" t="n">
+        <v>941</v>
+      </c>
+      <c r="AN27" s="9" t="n">
+        <v>1033</v>
+      </c>
+      <c r="AO27" s="9" t="n">
+        <v>1098</v>
+      </c>
+      <c r="AP27" s="9" t="n">
+        <v>3471</v>
+      </c>
+      <c r="AQ27" s="9" t="n">
+        <v>1296</v>
+      </c>
+      <c r="AR27" s="9" t="n">
+        <v>1396</v>
+      </c>
+      <c r="AS27" s="9" t="n">
+        <v>1306</v>
+      </c>
+      <c r="AT27" s="9" t="n">
+        <v>4850</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">

--- a/workbook/capex_tracker.xlsx
+++ b/workbook/capex_tracker.xlsx
@@ -9699,92 +9699,37 @@
 Report: https://www.sec.gov/Archives/edgar/data/1577552/000110465926032060/tm269353d1_ex99-1.htm</t>
       </text>
     </comment>
-    <comment ref="R6" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [BIDU] FY2019 6-K (filed 2019-03-31)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
-Line item: "[PROXY: other_revenues] Other revenues were RMB 6.5 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 6,500M → $969M USD
-FX: CNY/USD 0.1490 @ 2019-03-31 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
-Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312519152169/d727883dex991.htm</t>
-      </text>
-    </comment>
-    <comment ref="S6" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [BIDU] FY2019 6-K (filed 2019-06-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
-Line item: "[PROXY: other_revenues] Other revenues were RMB 7.1 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 7,100M → $1,033M USD
-FX: CNY/USD 0.1456 @ 2019-06-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
-Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312519226398/d691391dex991.htm</t>
-      </text>
-    </comment>
-    <comment ref="T6" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [BIDU] FY2019 6-K (filed 2019-09-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
-Line item: "[PROXY: other_revenues] Other revenues were RMB 7.6 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 7,600M → $1,064M USD
-FX: CNY/USD 0.1400 @ 2019-09-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
-Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312519290462/d827580dex991.htm</t>
-      </text>
-    </comment>
-    <comment ref="U6" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [BIDU] FY2019 20-F (filed 2020-03-13)
-Section: Baidu Core Revenue by type, Cloud services
-Line item: "Cloud services 6,370 (direct disclosure in Baidu Core revenue)"
-Value: CNY 6,370M → $915M USD
-FX: CNY/USD 0.1436 @ 2019-12-31 (source: ECB via frankfurter.app)
-Method: claude-code
-Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312520073092/d833212d20f.htm</t>
-      </text>
-    </comment>
-    <comment ref="V6" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [BIDU] FY2020 6-K (filed 2020-03-31)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
-Line item: "[PROXY: other_revenues] Other revenues were RMB 8.3 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 8,300M → $1,169M USD
-FX: CNY/USD 0.1409 @ 2020-03-31 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
-Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312520146636/d927979dex991.htm</t>
-      </text>
-    </comment>
-    <comment ref="W6" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [BIDU] FY2020 6-K (filed 2020-06-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
-Line item: "[PROXY: other_revenues] Other revenues were RMB 8.3 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 8,300M → $1,173M USD
-FX: CNY/USD 0.1414 @ 2020-06-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
-Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312520222418/d82228dex991.htm</t>
-      </text>
-    </comment>
-    <comment ref="Y6" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [BIDU] FY2020 20-F (filed 2021-03-09)
-Section: Baidu Core Revenue by type, Cloud services
-Line item: "Cloud services 9,173 (direct disclosure in Baidu Core revenue)"
-Value: CNY 9,173M → $1,403M USD
-FX: CNY/USD 0.1530 @ 2020-12-31 (source: ECB via frankfurter.app)
-Method: claude-code
-Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312521074038/d46900d20f.htm</t>
+    <comment ref="Z6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2021 6-K (filed 2021-03-31)
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=28100.0M, Online=16300.0M, iQIYI=8000.0M, non_online=NoneM =&gt; cloud=3800M RMB"
+Value: CNY 3,800M → $580M USD
+FX: CNY/USD 0.1527 @ 2021-03-31 (source: ECB via frankfurter.app)
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312521167243/d184935dex991.htm</t>
       </text>
     </comment>
     <comment ref="AA6" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2021 6-K (filed 2021-06-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB 5.0 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 5,000M → $774M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=31400.0M, Online=19000.0M, iQIYI=7600.0M, non_online=5000.0M =&gt; cloud=4800M RMB"
+Value: CNY 4,800M → $743M USD
 FX: CNY/USD 0.1549 @ 2021-06-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312521245436/d175957dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AB6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2021 6-K (filed 2021-09-30)
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=31900.0M, Online=19500.0M, iQIYI=7600.0M, non_online=5200.0M =&gt; cloud=4800M RMB"
+Value: CNY 4,800M → $743M USD
+FX: CNY/USD 0.1547 @ 2021-09-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312521317741/d232228dex992.htm</t>
       </text>
     </comment>
     <comment ref="AC6" authorId="0" shapeId="0">
@@ -9801,33 +9746,33 @@
     <comment ref="AD6" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2022 6-K (filed 2022-03-31)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB5.7 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 5,700M → $899M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=28400.0M, Online=15700.0M, iQIYI=7300.0M, non_online=5700.0M =&gt; cloud=5400M RMB"
+Value: CNY 5,400M → $851M USD
 FX: CNY/USD 0.1577 @ 2022-03-31 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312522161778/d335526dex991.htm</t>
       </text>
     </comment>
     <comment ref="AE6" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2022 6-K (filed 2022-06-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB 6.1 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 6,100M → $910M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=29600.0M, Online=17100.0M, iQIYI=6700.0M, non_online=6100.0M =&gt; cloud=5800M RMB"
+Value: CNY 5,800M → $865M USD
 FX: CNY/USD 0.1492 @ 2022-06-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312522234500/d393584dex991.htm</t>
       </text>
     </comment>
     <comment ref="AF6" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2022 6-K (filed 2022-09-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.5 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 6,500M → $913M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=32500.0M, Online=18700.0M, iQIYI=7500.0M, non_online=6500.0M =&gt; cloud=6300M RMB"
+Value: CNY 6,300M → $885M USD
 FX: CNY/USD 0.1405 @ 2022-09-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312522291565/d313453dex991.htm</t>
       </text>
     </comment>
@@ -9845,33 +9790,33 @@
     <comment ref="AH6" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2023 6-K (filed 2023-03-31)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.4 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 6,400M → $931M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=31100.0M, Online=16600.0M, iQIYI=8300.0M, non_online=6400.0M =&gt; cloud=6200M RMB"
+Value: CNY 6,200M → $902M USD
 FX: CNY/USD 0.1455 @ 2023-03-31 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312523145594/d472126dex991.htm</t>
       </text>
     </comment>
     <comment ref="AI6" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2023 6-K (filed 2023-06-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.8 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 6,800M → $935M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=34100.0M, Online=19600.0M, iQIYI=7800.0M, non_online=6800.0M =&gt; cloud=6700M RMB"
+Value: CNY 6,700M → $922M USD
 FX: CNY/USD 0.1376 @ 2023-06-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312523217413/d502468dex991.htm</t>
       </text>
     </comment>
     <comment ref="AJ6" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2023 6-K (filed 2023-09-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.9 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 6,900M → $945M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=34400.0M, Online=19700.0M, iQIYI=8000.0M, non_online=6900.0M =&gt; cloud=6700M RMB"
+Value: CNY 6,700M → $918M USD
 FX: CNY/USD 0.1370 @ 2023-09-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312523281151/d551070dex991.htm</t>
       </text>
     </comment>
@@ -9891,33 +9836,33 @@
     <comment ref="AL6" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2024 6-K (filed 2024-03-31)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.8 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 6,800M → $941M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=31500.0M, Online=17000.0M, iQIYI=7900.0M, non_online=6800.0M =&gt; cloud=6600M RMB"
+Value: CNY 6,600M → $913M USD
 FX: CNY/USD 0.1384 @ 2024-03-31 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312524140513/d782149dex991.htm</t>
       </text>
     </comment>
     <comment ref="AM6" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2024 6-K (filed 2024-06-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB7.5 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 7,500M → $1,033M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=33900.0M, Online=19200.0M, iQIYI=7400.0M, non_online=7500.0M =&gt; cloud=7300M RMB"
+Value: CNY 7,300M → $1,005M USD
 FX: CNY/USD 0.1377 @ 2024-06-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312524204906/d227518dex991.htm</t>
       </text>
     </comment>
     <comment ref="AN6" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2024 6-K (filed 2024-09-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB7.7 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 7,700M → $1,098M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=33600.0M, Online=18800.0M, iQIYI=7200.0M, non_online=7700.0M =&gt; cloud=7600M RMB"
+Value: CNY 7,600M → $1,084M USD
 FX: CNY/USD 0.1426 @ 2024-09-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312524263052/d802709dex991.htm</t>
       </text>
     </comment>
@@ -9937,33 +9882,33 @@
     <comment ref="AP6" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2025 6-K (filed 2025-03-31)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB9.4 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 9,400M → $1,296M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=32500.0M, Online=16000.0M, iQIYI=7200.0M, non_online=9400.0M =&gt; cloud=9300M RMB"
+Value: CNY 9,300M → $1,282M USD
 FX: CNY/USD 0.1379 @ 2025-03-31 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312525123961/d58002dex991.htm</t>
       </text>
     </comment>
     <comment ref="AQ6" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2025 6-K (filed 2025-06-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB10.0 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 10,000M → $1,396M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=32700.000000000004M, Online=16200.0M, iQIYI=6600.0M, non_online=10000.0M =&gt; cloud=9900M RMB"
+Value: CNY 9,900M → $1,382M USD
 FX: CNY/USD 0.1396 @ 2025-06-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312525183792/d938996dex991.htm</t>
       </text>
     </comment>
     <comment ref="AR6" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2025 6-K (filed 2025-09-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB9.3 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 9,300M → $1,306M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=31200.0M, Online=15300.0M, iQIYI=6700.0M, non_online=9300.0M =&gt; cloud=9200M RMB"
+Value: CNY 9,200M → $1,292M USD
 FX: CNY/USD 0.1405 @ 2025-09-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312525285391/d52736dex991.htm</t>
       </text>
     </comment>
@@ -20876,92 +20821,37 @@
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312526109289/d38065d20f.htm</t>
       </text>
     </comment>
-    <comment ref="S27" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [BIDU] FY2019 6-K (filed 2019-03-31)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
-Line item: "[PROXY: other_revenues] Other revenues were RMB 6.5 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 6,500M → $969M USD
-FX: CNY/USD 0.1490 @ 2019-03-31 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
-Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312519152169/d727883dex991.htm</t>
-      </text>
-    </comment>
-    <comment ref="T27" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [BIDU] FY2019 6-K (filed 2019-06-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
-Line item: "[PROXY: other_revenues] Other revenues were RMB 7.1 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 7,100M → $1,033M USD
-FX: CNY/USD 0.1456 @ 2019-06-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
-Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312519226398/d691391dex991.htm</t>
-      </text>
-    </comment>
-    <comment ref="U27" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [BIDU] FY2019 6-K (filed 2019-09-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
-Line item: "[PROXY: other_revenues] Other revenues were RMB 7.6 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 7,600M → $1,064M USD
-FX: CNY/USD 0.1400 @ 2019-09-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
-Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312519290462/d827580dex991.htm</t>
-      </text>
-    </comment>
-    <comment ref="V27" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [BIDU] FY2019 20-F (filed 2020-03-13)
-Section: Baidu Core Revenue by type, Cloud services
-Line item: "Cloud services 6,370 (direct disclosure in Baidu Core revenue)"
-Value: CNY 6,370M → $915M USD
-FX: CNY/USD 0.1436 @ 2019-12-31 (source: ECB via frankfurter.app)
-Method: claude-code
-Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312520073092/d833212d20f.htm</t>
-      </text>
-    </comment>
-    <comment ref="W27" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [BIDU] FY2020 6-K (filed 2020-03-31)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
-Line item: "[PROXY: other_revenues] Other revenues were RMB 8.3 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 8,300M → $1,169M USD
-FX: CNY/USD 0.1409 @ 2020-03-31 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
-Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312520146636/d927979dex991.htm</t>
-      </text>
-    </comment>
-    <comment ref="X27" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [BIDU] FY2020 6-K (filed 2020-06-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=other_revenues)
-Line item: "[PROXY: other_revenues] Other revenues were RMB 8.3 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 8,300M → $1,173M USD
-FX: CNY/USD 0.1414 @ 2020-06-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
-Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312520222418/d82228dex991.htm</t>
-      </text>
-    </comment>
-    <comment ref="Z27" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [BIDU] FY2020 20-F (filed 2021-03-09)
-Section: Baidu Core Revenue by type, Cloud services
-Line item: "Cloud services 9,173 (direct disclosure in Baidu Core revenue)"
-Value: CNY 9,173M → $1,403M USD
-FX: CNY/USD 0.1530 @ 2020-12-31 (source: ECB via frankfurter.app)
-Method: claude-code
-Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312521074038/d46900d20f.htm</t>
+    <comment ref="AA27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2021 6-K (filed 2021-03-31)
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=28100.0M, Online=16300.0M, iQIYI=8000.0M, non_online=NoneM =&gt; cloud=3800M RMB"
+Value: CNY 3,800M → $580M USD
+FX: CNY/USD 0.1527 @ 2021-03-31 (source: ECB via frankfurter.app)
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312521167243/d184935dex991.htm</t>
       </text>
     </comment>
     <comment ref="AB27" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2021 6-K (filed 2021-06-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB 5.0 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 5,000M → $774M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=31400.0M, Online=19000.0M, iQIYI=7600.0M, non_online=5000.0M =&gt; cloud=4800M RMB"
+Value: CNY 4,800M → $743M USD
 FX: CNY/USD 0.1549 @ 2021-06-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312521245436/d175957dex991.htm</t>
+      </text>
+    </comment>
+    <comment ref="AC27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [BIDU] FY2021 6-K (filed 2021-09-30)
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=31900.0M, Online=19500.0M, iQIYI=7600.0M, non_online=5200.0M =&gt; cloud=4800M RMB"
+Value: CNY 4,800M → $743M USD
+FX: CNY/USD 0.1547 @ 2021-09-30 (source: ECB via frankfurter.app)
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
+Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312521317741/d232228dex992.htm</t>
       </text>
     </comment>
     <comment ref="AD27" authorId="0" shapeId="0">
@@ -20978,33 +20868,33 @@
     <comment ref="AE27" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2022 6-K (filed 2022-03-31)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB5.7 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 5,700M → $899M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=28400.0M, Online=15700.0M, iQIYI=7300.0M, non_online=5700.0M =&gt; cloud=5400M RMB"
+Value: CNY 5,400M → $851M USD
 FX: CNY/USD 0.1577 @ 2022-03-31 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312522161778/d335526dex991.htm</t>
       </text>
     </comment>
     <comment ref="AF27" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2022 6-K (filed 2022-06-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB 6.1 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 6,100M → $910M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=29600.0M, Online=17100.0M, iQIYI=6700.0M, non_online=6100.0M =&gt; cloud=5800M RMB"
+Value: CNY 5,800M → $865M USD
 FX: CNY/USD 0.1492 @ 2022-06-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312522234500/d393584dex991.htm</t>
       </text>
     </comment>
     <comment ref="AG27" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2022 6-K (filed 2022-09-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.5 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 6,500M → $913M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=32500.0M, Online=18700.0M, iQIYI=7500.0M, non_online=6500.0M =&gt; cloud=6300M RMB"
+Value: CNY 6,300M → $885M USD
 FX: CNY/USD 0.1405 @ 2022-09-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312522291565/d313453dex991.htm</t>
       </text>
     </comment>
@@ -21022,33 +20912,33 @@
     <comment ref="AI27" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2023 6-K (filed 2023-03-31)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.4 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 6,400M → $931M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=31100.0M, Online=16600.0M, iQIYI=8300.0M, non_online=6400.0M =&gt; cloud=6200M RMB"
+Value: CNY 6,200M → $902M USD
 FX: CNY/USD 0.1455 @ 2023-03-31 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312523145594/d472126dex991.htm</t>
       </text>
     </comment>
     <comment ref="AJ27" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2023 6-K (filed 2023-06-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.8 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 6,800M → $935M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=34100.0M, Online=19600.0M, iQIYI=7800.0M, non_online=6800.0M =&gt; cloud=6700M RMB"
+Value: CNY 6,700M → $922M USD
 FX: CNY/USD 0.1376 @ 2023-06-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312523217413/d502468dex991.htm</t>
       </text>
     </comment>
     <comment ref="AK27" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2023 6-K (filed 2023-09-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.9 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 6,900M → $945M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=34400.0M, Online=19700.0M, iQIYI=8000.0M, non_online=6900.0M =&gt; cloud=6700M RMB"
+Value: CNY 6,700M → $918M USD
 FX: CNY/USD 0.1370 @ 2023-09-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312523281151/d551070dex991.htm</t>
       </text>
     </comment>
@@ -21068,33 +20958,33 @@
     <comment ref="AM27" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2024 6-K (filed 2024-03-31)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB6.8 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 6,800M → $941M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=31500.0M, Online=17000.0M, iQIYI=7900.0M, non_online=6800.0M =&gt; cloud=6600M RMB"
+Value: CNY 6,600M → $913M USD
 FX: CNY/USD 0.1384 @ 2024-03-31 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312524140513/d782149dex991.htm</t>
       </text>
     </comment>
     <comment ref="AN27" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2024 6-K (filed 2024-06-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB7.5 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 7,500M → $1,033M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=33900.0M, Online=19200.0M, iQIYI=7400.0M, non_online=7500.0M =&gt; cloud=7300M RMB"
+Value: CNY 7,300M → $1,005M USD
 FX: CNY/USD 0.1377 @ 2024-06-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312524204906/d227518dex991.htm</t>
       </text>
     </comment>
     <comment ref="AO27" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2024 6-K (filed 2024-09-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB7.7 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 7,700M → $1,098M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=33600.0M, Online=18800.0M, iQIYI=7200.0M, non_online=7700.0M =&gt; cloud=7600M RMB"
+Value: CNY 7,600M → $1,084M USD
 FX: CNY/USD 0.1426 @ 2024-09-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312524263052/d802709dex991.htm</t>
       </text>
     </comment>
@@ -21114,33 +21004,33 @@
     <comment ref="AQ27" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2025 6-K (filed 2025-03-31)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB9.4 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 9,400M → $1,296M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=32500.0M, Online=16000.0M, iQIYI=7200.0M, non_online=9400.0M =&gt; cloud=9300M RMB"
+Value: CNY 9,300M → $1,282M USD
 FX: CNY/USD 0.1379 @ 2025-03-31 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312525123961/d58002dex991.htm</t>
       </text>
     </comment>
     <comment ref="AR27" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2025 6-K (filed 2025-06-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB10.0 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 10,000M → $1,396M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=32700.000000000004M, Online=16200.0M, iQIYI=6600.0M, non_online=10000.0M =&gt; cloud=9900M RMB"
+Value: CNY 9,900M → $1,382M USD
 FX: CNY/USD 0.1396 @ 2025-06-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312525183792/d938996dex991.htm</t>
       </text>
     </comment>
     <comment ref="AS27" authorId="0" shapeId="0">
       <text>
         <t>Source: [BIDU] FY2025 6-K (filed 2025-09-30)
-Section: 6-K Press Release — Non-online marketing proxy (AI Cloud + Apollo + smart-device hardware; pattern=non_online_marketing)
-Line item: "[PROXY: non_online_marketing] non-online marketing revenue was RMB9.3 billion — Note: BIDU does not disclose quarterly AI Cloud standalone; this figure is Baidu Core non-online marketing revenue, of which AI Cloud is the dominant component."
-Value: CNY 9,300M → $1,306M USD
+Section: 6-K earnings press release (Exhibit 99.1): Total − Online − iQIYI
+Line item: "[Total − Online marketing − iQIYI] Total=31200.0M, Online=15300.0M, iQIYI=6700.0M, non_online=9300.0M =&gt; cloud=9200M RMB"
+Value: CNY 9,200M → $1,292M USD
 FX: CNY/USD 0.1405 @ 2025-09-30 (source: ECB via frankfurter.app)
-Method: bidu-cloud-6k-proxy@0.1.0
+Method: bidu-cloud-total-minus-online-minus-iqiyi@0.3.0
 Report: https://www.sec.gov/Archives/edgar/data/1329099/000119312525285391/d52736dex991.htm</t>
       </text>
     </comment>
@@ -30177,7 +30067,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-04-19 15:17 UTC</t>
+          <t>2026-04-19 15:43 UTC</t>
         </is>
       </c>
     </row>
@@ -30693,7 +30583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-19 15:17 UTC</t>
+          <t>2026-04-19 15:43 UTC</t>
         </is>
       </c>
     </row>
@@ -30812,7 +30702,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>claude-code-segment,reconcile-derived,xbrl-verified,claude-code,segment-quarterly@0.1.0</t>
+          <t>claude-code-segment,xbrl-verified,segment-quarterly@0.1.0,reconcile-derived,claude-code</t>
         </is>
       </c>
     </row>
@@ -30842,7 +30732,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>xbrl-verified,claude-code,reconcile-derived,whole-company-copy@0.1.0</t>
+          <t>xbrl-verified,claude-code,whole-company-copy@0.1.0,reconcile-derived</t>
         </is>
       </c>
     </row>
@@ -30872,7 +30762,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>xbrl-verified,claude-code,reconcile-derived,claude-code-test,baba-cloud-6k@0.1.0,6k-press-release,llm-dual-agent</t>
+          <t>xbrl-verified,baba-cloud-6k@0.1.0,6k-press-release,claude-code,reconcile-derived,llm-dual-agent,claude-code-test</t>
         </is>
       </c>
     </row>
@@ -30902,7 +30792,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>xbrl-verified,reconcile-derived,claude-code,llm-dual-agent,6k-press-release,bidu-cloud-6k-proxy@0.1.0</t>
+          <t>xbrl-verified,llm-dual-agent,reconcile-derived,6k-press-release,claude-code,bidu-cloud-total-minus-online-minus-iqiyi@0.3.0</t>
         </is>
       </c>
     </row>
@@ -30962,7 +30852,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>xbrl-verified,claude-code,whole-company-copy@0.1.0,reconcile-derived,llm-dual-agent</t>
+          <t>xbrl-verified,claude-code,whole-company-copy@0.1.0,llm-dual-agent,reconcile-derived</t>
         </is>
       </c>
     </row>
@@ -30992,7 +30882,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>reconcile-derived,xbrl-verified,claude-code-segment,claude-code,segment-quarterly@0.1.0</t>
+          <t>xbrl-verified,reconcile-derived,claude-code-segment,segment-quarterly@0.1.0,claude-code</t>
         </is>
       </c>
     </row>
@@ -31052,7 +30942,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>reconcile-derived,xbrl-verified</t>
+          <t>xbrl-verified,reconcile-derived</t>
         </is>
       </c>
     </row>
@@ -31082,7 +30972,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>reconcile-derived,xbrl-verified,claude-code-segment,msft-original-10k-restatement-fix,claude-code,segment-quarterly@0.1.0</t>
+          <t>xbrl-verified,reconcile-derived,claude-code-segment,segment-quarterly@0.1.0,msft-original-10k-restatement-fix,claude-code</t>
         </is>
       </c>
     </row>
@@ -31112,7 +31002,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>xbrl-verified,claude-code,whole-company-copy@0.1.0,reconcile-derived,llm-dual-agent</t>
+          <t>xbrl-verified,claude-code,whole-company-copy@0.1.0,llm-dual-agent,reconcile-derived</t>
         </is>
       </c>
     </row>
@@ -31142,7 +31032,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>reconcile-derived,xbrl-verified,claude-code-segment,orcl-cs-ls-10k-backfill,segment-quarterly@0.1.0</t>
+          <t>xbrl-verified,segment-quarterly@0.1.0,reconcile-derived,claude-code-segment,orcl-cs-ls-10k-backfill</t>
         </is>
       </c>
     </row>
@@ -36829,77 +36719,62 @@
           <t>BIDU</t>
         </is>
       </c>
-      <c r="R6" s="9" t="n">
-        <v>969</v>
-      </c>
-      <c r="S6" s="9" t="n">
-        <v>1033</v>
-      </c>
-      <c r="T6" s="9" t="n">
-        <v>1064</v>
-      </c>
-      <c r="U6" s="9" t="n">
-        <v>915</v>
-      </c>
-      <c r="V6" s="9" t="n">
-        <v>1169</v>
-      </c>
-      <c r="W6" s="9" t="n">
-        <v>1173</v>
-      </c>
-      <c r="Y6" s="9" t="n">
-        <v>1403</v>
+      <c r="Z6" s="9" t="n">
+        <v>580</v>
       </c>
       <c r="AA6" s="9" t="n">
-        <v>774</v>
+        <v>743</v>
+      </c>
+      <c r="AB6" s="9" t="n">
+        <v>743</v>
       </c>
       <c r="AC6" s="9" t="n">
         <v>2372</v>
       </c>
       <c r="AD6" s="9" t="n">
-        <v>899</v>
+        <v>851</v>
       </c>
       <c r="AE6" s="9" t="n">
-        <v>910</v>
+        <v>865</v>
       </c>
       <c r="AF6" s="9" t="n">
-        <v>913</v>
+        <v>885</v>
       </c>
       <c r="AG6" s="9" t="n">
         <v>2569</v>
       </c>
       <c r="AH6" s="9" t="n">
-        <v>931</v>
+        <v>902</v>
       </c>
       <c r="AI6" s="9" t="n">
-        <v>935</v>
+        <v>922</v>
       </c>
       <c r="AJ6" s="9" t="n">
-        <v>945</v>
+        <v>918</v>
       </c>
       <c r="AK6" s="9" t="n">
         <v>3029</v>
       </c>
       <c r="AL6" s="9" t="n">
-        <v>941</v>
+        <v>913</v>
       </c>
       <c r="AM6" s="9" t="n">
-        <v>1033</v>
+        <v>1005</v>
       </c>
       <c r="AN6" s="9" t="n">
-        <v>1098</v>
+        <v>1084</v>
       </c>
       <c r="AO6" s="9" t="n">
         <v>3471</v>
       </c>
       <c r="AP6" s="9" t="n">
-        <v>1296</v>
+        <v>1282</v>
       </c>
       <c r="AQ6" s="9" t="n">
-        <v>1396</v>
+        <v>1382</v>
       </c>
       <c r="AR6" s="9" t="n">
-        <v>1306</v>
+        <v>1292</v>
       </c>
       <c r="AS6" s="9" t="n">
         <v>4850</v>
@@ -41930,77 +41805,62 @@
           <t>cloud_segment_revenue</t>
         </is>
       </c>
-      <c r="S27" s="9" t="n">
-        <v>969</v>
-      </c>
-      <c r="T27" s="9" t="n">
-        <v>1033</v>
-      </c>
-      <c r="U27" s="9" t="n">
-        <v>1064</v>
-      </c>
-      <c r="V27" s="9" t="n">
-        <v>915</v>
-      </c>
-      <c r="W27" s="9" t="n">
-        <v>1169</v>
-      </c>
-      <c r="X27" s="9" t="n">
-        <v>1173</v>
-      </c>
-      <c r="Z27" s="9" t="n">
-        <v>1403</v>
+      <c r="AA27" s="9" t="n">
+        <v>580</v>
       </c>
       <c r="AB27" s="9" t="n">
-        <v>774</v>
+        <v>743</v>
+      </c>
+      <c r="AC27" s="9" t="n">
+        <v>743</v>
       </c>
       <c r="AD27" s="9" t="n">
         <v>2372</v>
       </c>
       <c r="AE27" s="9" t="n">
-        <v>899</v>
+        <v>851</v>
       </c>
       <c r="AF27" s="9" t="n">
-        <v>910</v>
+        <v>865</v>
       </c>
       <c r="AG27" s="9" t="n">
-        <v>913</v>
+        <v>885</v>
       </c>
       <c r="AH27" s="9" t="n">
         <v>2569</v>
       </c>
       <c r="AI27" s="9" t="n">
-        <v>931</v>
+        <v>902</v>
       </c>
       <c r="AJ27" s="9" t="n">
-        <v>935</v>
+        <v>922</v>
       </c>
       <c r="AK27" s="9" t="n">
-        <v>945</v>
+        <v>918</v>
       </c>
       <c r="AL27" s="9" t="n">
         <v>3029</v>
       </c>
       <c r="AM27" s="9" t="n">
-        <v>941</v>
+        <v>913</v>
       </c>
       <c r="AN27" s="9" t="n">
-        <v>1033</v>
+        <v>1005</v>
       </c>
       <c r="AO27" s="9" t="n">
-        <v>1098</v>
+        <v>1084</v>
       </c>
       <c r="AP27" s="9" t="n">
         <v>3471</v>
       </c>
       <c r="AQ27" s="9" t="n">
-        <v>1296</v>
+        <v>1282</v>
       </c>
       <c r="AR27" s="9" t="n">
-        <v>1396</v>
+        <v>1382</v>
       </c>
       <c r="AS27" s="9" t="n">
-        <v>1306</v>
+        <v>1292</v>
       </c>
       <c r="AT27" s="9" t="n">
         <v>4850</v>

--- a/workbook/capex_tracker.xlsx
+++ b/workbook/capex_tracker.xlsx
@@ -344,6 +344,15 @@
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872426000004/amzn-20251231.htm</t>
       </text>
     </comment>
+    <comment ref="H4" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [APLD] FY2021 10-K (filed 2022-08-29)
+Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
+Value: $0M (as reported)
+Method: XBRL companyfacts API
+Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1144879&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
+      </text>
+    </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
         <t>Source: [APLD] FY2022 10-K (filed 2022-08-29)
@@ -374,9 +383,8 @@
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
         <t>Source: [APLD] FY2025 10-K (filed 2025-07-30)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $144M (as reported)
-Method: XBRL companyfacts API
+Derivation:
+  Derived: 9M = Q1+Q2+Q3
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487925000021/apld-20250531.htm</t>
       </text>
     </comment>
@@ -1147,7 +1155,7 @@
       <text>
         <t>Source: [AMZN] FY2017 Q3 10-Q (filed 2017-10-27)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $117,413M (as reported)
+Value: $43,744M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872417000135/amzn-20170930x10q.htm</t>
       </text>
@@ -1172,9 +1180,9 @@
     </comment>
     <comment ref="O3" authorId="0" shapeId="0">
       <text>
-        <t>Source: [AMZN] FY2018 Q2 10-Q (filed 2018-07-27)
+        <t>Source: [AMZN] FY2018 10-K (filed 2019-02-01)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $103,928M (as reported)
+Value: $52,886M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872418000108/amzn-20180630x10q.htm</t>
       </text>
@@ -1183,7 +1191,7 @@
       <text>
         <t>Source: [AMZN] FY2018 Q3 10-Q (filed 2018-10-26)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $160,504M (as reported)
+Value: $56,576M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872418000159/amzn-20180930x10q.htm</t>
       </text>
@@ -1199,7 +1207,7 @@
     </comment>
     <comment ref="R3" authorId="0" shapeId="0">
       <text>
-        <t>Source: [AMZN] FY2019 Q1 10-Q (filed 2019-04-26)
+        <t>Source: [AMZN] FY2019 10-K (filed 2020-01-31)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
 Value: $59,700M (as reported)
 Method: XBRL companyfacts API
@@ -1210,7 +1218,7 @@
       <text>
         <t>Source: [AMZN] FY2019 Q2 10-Q (filed 2019-07-26)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $123,104M (as reported)
+Value: $63,404M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872419000071/amzn-2019630x10q.htm</t>
       </text>
@@ -1219,7 +1227,7 @@
       <text>
         <t>Source: [AMZN] FY2019 Q3 10-Q (filed 2019-10-25)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $193,086M (as reported)
+Value: $69,981M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872419000089/amzn-2019930x10q.htm</t>
       </text>
@@ -1235,7 +1243,7 @@
     </comment>
     <comment ref="V3" authorId="0" shapeId="0">
       <text>
-        <t>Source: [AMZN] FY2020 Q1 10-Q (filed 2020-05-01)
+        <t>Source: [AMZN] FY2020 10-K (filed 2021-02-03)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
 Value: $75,452M (as reported)
 Method: XBRL companyfacts API
@@ -1246,7 +1254,7 @@
       <text>
         <t>Source: [AMZN] FY2020 Q2 10-Q (filed 2020-07-31)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $164,364M (as reported)
+Value: $88,912M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872420000021/amzn-20200630.htm</t>
       </text>
@@ -1255,7 +1263,7 @@
       <text>
         <t>Source: [AMZN] FY2020 Q3 10-Q (filed 2020-10-30)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $260,509M (as reported)
+Value: $96,145M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872420000030/amzn-20200930.htm</t>
       </text>
@@ -1282,7 +1290,7 @@
       <text>
         <t>Source: [AMZN] FY2021 Q2 10-Q (filed 2021-07-30)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $221,598M (as reported)
+Value: $113,080M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872421000020/amzn-20210630.htm</t>
       </text>
@@ -1291,7 +1299,7 @@
       <text>
         <t>Source: [AMZN] FY2021 Q3 10-Q (filed 2021-10-29)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $332,410M (as reported)
+Value: $110,812M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872421000028/amzn-20210930.htm</t>
       </text>
@@ -1318,7 +1326,7 @@
       <text>
         <t>Source: [AMZN] FY2022 Q2 10-Q (filed 2022-07-29)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $237,678M (as reported)
+Value: $121,234M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872422000019/amzn-20220630.htm</t>
       </text>
@@ -1327,7 +1335,7 @@
       <text>
         <t>Source: [AMZN] FY2022 Q3 10-Q (filed 2022-10-28)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $364,779M (as reported)
+Value: $127,101M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872422000023/amzn-20220930.htm</t>
       </text>
@@ -1354,7 +1362,7 @@
       <text>
         <t>Source: [AMZN] FY2023 Q2 10-Q (filed 2023-08-04)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $261,741M (as reported)
+Value: $134,383M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872423000012/amzn-20230630.htm</t>
       </text>
@@ -1363,7 +1371,7 @@
       <text>
         <t>Source: [AMZN] FY2023 Q3 10-Q (filed 2023-10-27)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $404,824M (as reported)
+Value: $143,083M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872423000018/amzn-20230930.htm</t>
       </text>
@@ -1390,7 +1398,7 @@
       <text>
         <t>Source: [AMZN] FY2024 Q2 10-Q (filed 2024-08-02)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $291,290M (as reported)
+Value: $147,977M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872424000130/amzn-20240630.htm</t>
       </text>
@@ -1399,7 +1407,7 @@
       <text>
         <t>Source: [AMZN] FY2024 Q3 10-Q (filed 2024-11-01)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $450,167M (as reported)
+Value: $158,877M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872424000161/amzn-20240930.htm</t>
       </text>
@@ -1426,7 +1434,7 @@
       <text>
         <t>Source: [AMZN] FY2025 Q2 10-Q (filed 2025-08-01)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $323,369M (as reported)
+Value: $167,702M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872425000086/amzn-20250630.htm</t>
       </text>
@@ -1435,7 +1443,7 @@
       <text>
         <t>Source: [AMZN] FY2025 Q3 10-Q (filed 2025-10-31)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $503,538M (as reported)
+Value: $180,169M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872425000123/amzn-20250930.htm</t>
       </text>
@@ -1449,6 +1457,42 @@
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872426000004/amzn-20251231.htm</t>
       </text>
     </comment>
+    <comment ref="Z4" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [APLD] FY2021 10-Q (filed 2022-05-13)
+Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
+Value: $0M (as reported)
+Method: XBRL companyfacts API
+Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1144879&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
+      </text>
+    </comment>
+    <comment ref="AA4" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [APLD] FY2021 10-K (filed 2022-08-29)
+Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
+Value: $0M (as reported)
+Method: XBRL companyfacts API
+Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1144879&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
+      </text>
+    </comment>
+    <comment ref="AB4" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [APLD] FY2021 10-Q (filed 2022-10-12)
+Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
+Value: $0M (as reported)
+Method: XBRL companyfacts API
+Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1144879&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
+      </text>
+    </comment>
+    <comment ref="AC4" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [APLD] FY2021 10-Q (filed 2023-01-10)
+Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
+Value: $0M (as reported)
+Method: XBRL companyfacts API
+Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1144879&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
+      </text>
+    </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
         <t>Source: [APLD] FY2022 10-Q (filed 2022-05-13)
@@ -1480,7 +1524,7 @@
       <text>
         <t>Source: [APLD] FY2022 10-Q (filed 2023-01-10)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $19M (as reported)
+Value: $12M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487923000028/apld-20221130.htm</t>
       </text>
@@ -1489,7 +1533,7 @@
       <text>
         <t>Source: [APLD] FY2023 10-Q (filed 2023-04-06)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $33M (as reported)
+Value: $14M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487923000101/apld-20230228.htm</t>
       </text>
@@ -1516,7 +1560,7 @@
       <text>
         <t>Source: [APLD] FY2023 10-Q (filed 2024-01-16)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $79M (as reported)
+Value: $42M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487924000010/apld-20231130.htm</t>
       </text>
@@ -1525,7 +1569,7 @@
       <text>
         <t>Source: [APLD] FY2024 10-Q (filed 2024-04-11)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $122M (as reported)
+Value: $43M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487924000078/apld-20240229.htm</t>
       </text>
@@ -1552,7 +1596,7 @@
       <text>
         <t>Source: [APLD] FY2024 10-Q (filed 2025-01-14)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $125M (as reported)
+Value: $64M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487925000006/apld-20241130.htm</t>
       </text>
@@ -1561,7 +1605,7 @@
       <text>
         <t>Source: [APLD] FY2025 10-Q (filed 2025-04-14)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $177M (as reported)
+Value: $53M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000162828025017684/apld-20250228.htm</t>
       </text>
@@ -1569,18 +1613,16 @@
     <comment ref="AQ4" authorId="0" shapeId="0">
       <text>
         <t>Source: [APLD] FY2025 10-K (filed 2025-07-30)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $144M (as reported)
-Method: XBRL companyfacts API
+Derivation:
+  Derived: 9M = Q1+Q2+Q3
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487925000021/apld-20250531.htm</t>
       </text>
     </comment>
     <comment ref="AR4" authorId="0" shapeId="0">
       <text>
         <t>Source: [APLD] FY2025 10-Q (filed 2025-10-09)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $64M (as reported)
-Method: XBRL companyfacts API
+Derivation:
+  Derived: 9M = Q1+Q2+Q3
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487925000069/apld-20250831.htm</t>
       </text>
     </comment>
@@ -1588,7 +1630,7 @@
       <text>
         <t>Source: [APLD] FY2025 10-Q (filed 2026-01-08)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $191M (as reported)
+Value: $127M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487926000006/apld-20251130.htm</t>
       </text>
@@ -1597,7 +1639,7 @@
       <text>
         <t>Source: [APLD] FY2026 10-Q (filed 2026-04-08)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $353M (as reported)
+Value: $127M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487926000030/apld-20260228.htm</t>
       </text>
@@ -2561,29 +2603,29 @@
       <text>
         <t>Source: [CRWV] FY2024 Q2 10-Q (filed 2025-08-13)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
+Value: $395M (as reported)
+Method: XBRL companyfacts API
+Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1769628&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
+      </text>
+    </comment>
+    <comment ref="AN7" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [CRWV] FY2024 Q3 10-Q (filed 2025-11-13)
+Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
 Value: $584M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1769628&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
       </text>
     </comment>
-    <comment ref="AN7" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [CRWV] FY2024 Q3 10-Q (filed 2025-11-13)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $1,168M (as reported)
+    <comment ref="AO7" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [CRWV] FY2024 10-K (filed 2026-03-02)
+Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
+Value: $1,915M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1769628&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
       </text>
     </comment>
-    <comment ref="AO7" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [CRWV] FY2024 10-K (filed 2026-03-02)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $1,915M (as reported)
-Method: XBRL companyfacts API
-Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1769628&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
-      </text>
-    </comment>
     <comment ref="AP7" authorId="0" shapeId="0">
       <text>
         <t>Source: [CRWV] FY2025 Q1 10-Q (filed 2025-05-15)
@@ -2597,7 +2639,7 @@
       <text>
         <t>Source: [CRWV] FY2025 Q2 10-Q (filed 2025-08-13)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $2,194M (as reported)
+Value: $1,213M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1769628/000176962825000041/crwv-20250630.htm</t>
       </text>
@@ -2606,7 +2648,7 @@
       <text>
         <t>Source: [CRWV] FY2025 Q3 10-Q (filed 2025-11-13)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $3,559M (as reported)
+Value: $1,365M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1769628/000176962825000062/crwv-20250930.htm</t>
       </text>
@@ -3059,7 +3101,7 @@
       <text>
         <t>Source: [GOOGL] FY2015 Q2 10-Q (filed 2016-08-04)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $34,985M (as reported)
+Value: $17,727M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000156761922020201/xslForm13F_X01/primary_doc.xml</t>
       </text>
@@ -3068,7 +3110,7 @@
       <text>
         <t>Source: [GOOGL] FY2015 Q3 10-Q (filed 2015-10-29)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $53,660M (as reported)
+Value: $18,675M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204415000005/alpha10-qq32015.htm</t>
       </text>
@@ -3095,7 +3137,7 @@
       <text>
         <t>Source: [GOOGL] FY2016 Q2 10-Q (filed 2016-08-04)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $41,757M (as reported)
+Value: $21,500M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204416000032/goog10-qq22016.htm</t>
       </text>
@@ -3104,7 +3146,7 @@
       <text>
         <t>Source: [GOOGL] FY2016 Q3 10-Q (filed 2016-11-03)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $64,208M (as reported)
+Value: $22,451M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204416000038/goog10-qq32016.htm</t>
       </text>
@@ -3131,7 +3173,7 @@
       <text>
         <t>Source: [GOOGL] FY2017 Q2 10-Q (filed 2017-07-25)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $50,760M (as reported)
+Value: $26,010M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204417000026/goog10-qq22017.htm</t>
       </text>
@@ -3140,7 +3182,7 @@
       <text>
         <t>Source: [GOOGL] FY2017 Q3 10-Q (filed 2017-10-27)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $78,532M (as reported)
+Value: $27,772M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204417000042/goog10-qq32017.htm</t>
       </text>
@@ -3167,7 +3209,7 @@
       <text>
         <t>Source: [GOOGL] FY2018 Q2 10-Q (filed 2018-07-24)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $63,803M (as reported)
+Value: $32,657M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204418000027/goog10-qq22018.htm</t>
       </text>
@@ -3176,7 +3218,7 @@
       <text>
         <t>Source: [GOOGL] FY2018 Q3 10-Q (filed 2018-10-26)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $97,543M (as reported)
+Value: $33,740M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204418000035/goog10-qq32018.htm</t>
       </text>
@@ -3203,7 +3245,7 @@
       <text>
         <t>Source: [GOOGL] FY2019 Q2 10-Q (filed 2019-07-26)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $75,283M (as reported)
+Value: $38,944M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204419000023/goog10-qq22019.htm</t>
       </text>
@@ -3212,7 +3254,7 @@
       <text>
         <t>Source: [GOOGL] FY2019 Q3 10-Q (filed 2019-10-29)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $115,782M (as reported)
+Value: $40,499M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204419000032/goog10-qq32019.htm</t>
       </text>
@@ -3239,7 +3281,7 @@
       <text>
         <t>Source: [GOOGL] FY2020 Q2 10-Q (filed 2020-07-31)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $79,456M (as reported)
+Value: $38,297M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204420000032/goog-20200630.htm</t>
       </text>
@@ -3248,7 +3290,7 @@
       <text>
         <t>Source: [GOOGL] FY2020 Q3 10-Q (filed 2020-10-30)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $125,629M (as reported)
+Value: $46,173M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204420000050/goog-20200930.htm</t>
       </text>
@@ -3275,7 +3317,7 @@
       <text>
         <t>Source: [GOOGL] FY2021 Q2 10-Q (filed 2021-07-28)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $117,194M (as reported)
+Value: $61,880M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204421000047/goog-20210630.htm</t>
       </text>
@@ -3284,7 +3326,7 @@
       <text>
         <t>Source: [GOOGL] FY2021 Q3 10-Q (filed 2021-10-27)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $182,312M (as reported)
+Value: $65,118M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204421000057/goog-20210930.htm</t>
       </text>
@@ -3311,7 +3353,7 @@
       <text>
         <t>Source: [GOOGL] FY2022 Q2 10-Q (filed 2022-07-27)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $137,696M (as reported)
+Value: $69,685M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204422000071/goog-20220630.htm</t>
       </text>
@@ -3320,7 +3362,7 @@
       <text>
         <t>Source: [GOOGL] FY2022 Q3 10-Q (filed 2022-10-26)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $206,788M (as reported)
+Value: $69,092M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204422000090/goog-20220930.htm</t>
       </text>
@@ -3347,7 +3389,7 @@
       <text>
         <t>Source: [GOOGL] FY2023 Q2 10-Q (filed 2023-07-26)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $144,391M (as reported)
+Value: $74,604M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204423000070/goog-20230630.htm</t>
       </text>
@@ -3356,7 +3398,7 @@
       <text>
         <t>Source: [GOOGL] FY2023 Q3 10-Q (filed 2023-10-25)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $221,084M (as reported)
+Value: $76,693M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204423000094/goog-20230930.htm</t>
       </text>
@@ -3383,7 +3425,7 @@
       <text>
         <t>Source: [GOOGL] FY2024 Q2 10-Q (filed 2024-07-24)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $165,281M (as reported)
+Value: $84,742M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204424000079/goog-20240630.htm</t>
       </text>
@@ -3392,7 +3434,7 @@
       <text>
         <t>Source: [GOOGL] FY2024 Q3 10-Q (filed 2024-10-30)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $253,549M (as reported)
+Value: $88,268M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204424000118/goog-20240930.htm</t>
       </text>
@@ -3419,7 +3461,7 @@
       <text>
         <t>Source: [GOOGL] FY2025 Q2 10-Q (filed 2025-07-24)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $186,662M (as reported)
+Value: $96,428M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204425000062/goog-20250630.htm</t>
       </text>
@@ -3428,7 +3470,7 @@
       <text>
         <t>Source: [GOOGL] FY2025 Q3 10-Q (filed 2025-10-30)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $289,007M (as reported)
+Value: $102,346M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204425000091/goog-20250930.htm</t>
       </text>
@@ -3500,7 +3542,7 @@
       <text>
         <t>Source: [META] FY2015 Q2 10-Q (filed 2015-07-31)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $7,586M (as reported)
+Value: $4,042M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680115000028/fb-6302015x10q.htm</t>
       </text>
@@ -3509,7 +3551,7 @@
       <text>
         <t>Source: [META] FY2015 Q3 10-Q (filed 2015-11-05)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $12,087M (as reported)
+Value: $4,501M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680115000032/fb-9302015x10q.htm</t>
       </text>
@@ -3536,7 +3578,7 @@
       <text>
         <t>Source: [META] FY2016 Q2 10-Q (filed 2016-07-28)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $11,818M (as reported)
+Value: $6,436M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680116000082/fb-6302016x10q.htm</t>
       </text>
@@ -3545,7 +3587,7 @@
       <text>
         <t>Source: [META] FY2016 Q3 10-Q (filed 2016-11-03)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $18,829M (as reported)
+Value: $7,011M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680116000087/fb-9302016x10q.htm</t>
       </text>
@@ -3572,7 +3614,7 @@
       <text>
         <t>Source: [META] FY2017 Q2 10-Q (filed 2017-07-27)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $17,353M (as reported)
+Value: $9,321M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680117000038/fb-06302017x10q.htm</t>
       </text>
@@ -3581,7 +3623,7 @@
       <text>
         <t>Source: [META] FY2017 Q3 10-Q (filed 2017-11-02)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $27,681M (as reported)
+Value: $10,328M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680117000053/fb-09302017x10q.htm</t>
       </text>
@@ -3608,7 +3650,7 @@
       <text>
         <t>Source: [META] FY2018 Q2 10-Q (filed 2018-07-26)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $25,197M (as reported)
+Value: $13,231M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680118000057/fb-06302018x10q.htm</t>
       </text>
@@ -3617,7 +3659,7 @@
       <text>
         <t>Source: [META] FY2018 Q3 10-Q (filed 2018-10-31)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $38,924M (as reported)
+Value: $13,727M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680118000067/fb-09302018x10q.htm</t>
       </text>
@@ -3644,7 +3686,7 @@
       <text>
         <t>Source: [META] FY2019 Q2 10-Q (filed 2019-07-25)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $31,963M (as reported)
+Value: $16,886M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680119000055/fb-06302019x10q.htm</t>
       </text>
@@ -3653,7 +3695,7 @@
       <text>
         <t>Source: [META] FY2019 Q3 10-Q (filed 2019-10-31)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $49,615M (as reported)
+Value: $17,652M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680119000069/fb-09302019x10q.htm</t>
       </text>
@@ -3680,7 +3722,7 @@
       <text>
         <t>Source: [META] FY2020 Q2 10-Q (filed 2020-07-31)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $36,423M (as reported)
+Value: $18,687M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680120000076/fb-06302020x10q.htm</t>
       </text>
@@ -3689,7 +3731,7 @@
       <text>
         <t>Source: [META] FY2020 Q3 10-Q (filed 2020-10-30)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $57,893M (as reported)
+Value: $21,470M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680120000084/fb-09302020x10q.htm</t>
       </text>
@@ -3716,7 +3758,7 @@
       <text>
         <t>Source: [META] FY2021 Q2 10-Q (filed 2021-07-29)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $55,248M (as reported)
+Value: $29,077M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680121000049/fb-20210630.htm</t>
       </text>
@@ -3725,7 +3767,7 @@
       <text>
         <t>Source: [META] FY2021 Q3 10-Q (filed 2021-10-26)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $84,258M (as reported)
+Value: $29,010M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680121000065/fb-20210930.htm</t>
       </text>
@@ -3752,7 +3794,7 @@
       <text>
         <t>Source: [META] FY2022 Q2 10-Q (filed 2022-07-28)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $56,729M (as reported)
+Value: $28,822M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680122000082/meta-20220630.htm</t>
       </text>
@@ -3761,7 +3803,7 @@
       <text>
         <t>Source: [META] FY2022 Q3 10-Q (filed 2022-10-27)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $84,444M (as reported)
+Value: $27,714M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680122000108/meta-20220930.htm</t>
       </text>
@@ -3788,7 +3830,7 @@
       <text>
         <t>Source: [META] FY2023 Q2 10-Q (filed 2023-07-27)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $60,645M (as reported)
+Value: $31,999M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680123000093/meta-20230630.htm</t>
       </text>
@@ -3797,7 +3839,7 @@
       <text>
         <t>Source: [META] FY2023 Q3 10-Q (filed 2023-10-26)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $94,791M (as reported)
+Value: $34,146M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680123000103/meta-20230930.htm</t>
       </text>
@@ -3824,7 +3866,7 @@
       <text>
         <t>Source: [META] FY2024 Q2 10-Q (filed 2024-08-01)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $75,527M (as reported)
+Value: $39,071M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680124000069/meta-20240630.htm</t>
       </text>
@@ -3833,7 +3875,7 @@
       <text>
         <t>Source: [META] FY2024 Q3 10-Q (filed 2024-10-31)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $116,116M (as reported)
+Value: $40,589M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680124000081/meta-20240930.htm</t>
       </text>
@@ -3860,7 +3902,7 @@
       <text>
         <t>Source: [META] FY2025 Q2 10-Q (filed 2025-07-31)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $89,830M (as reported)
+Value: $47,516M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000162828025036791/meta-20250630.htm</t>
       </text>
@@ -3869,7 +3911,7 @@
       <text>
         <t>Source: [META] FY2025 Q3 10-Q (filed 2025-10-30)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $141,073M (as reported)
+Value: $51,242M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000162828025047240/meta-20250930.htm</t>
       </text>
@@ -3883,45 +3925,9 @@
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000162828026003942/meta-20251231.htm</t>
       </text>
     </comment>
-    <comment ref="L12" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [MSFT] FY2017 10-K (filed 2018-08-03)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $24,538M (as reported)
-Method: XBRL companyfacts API
-Report: https://www.sec.gov/Archives/edgar/data/789019/000156459017020171/msft-10q_20170930.htm</t>
-      </text>
-    </comment>
-    <comment ref="M12" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [MSFT] FY2017 10-Q (filed 2018-01-31)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $53,456M (as reported)
-Method: XBRL companyfacts API
-Report: https://www.sec.gov/Archives/edgar/data/789019/000156459018001129/msft-10q_20171231.htm</t>
-      </text>
-    </comment>
-    <comment ref="N12" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [MSFT] FY2018 Q1 10-Q (filed 2018-04-26)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $80,275M (as reported)
-Method: XBRL companyfacts API
-Report: https://www.sec.gov/Archives/edgar/data/789019/000156459018009307/msft-10q_20180331.htm</t>
-      </text>
-    </comment>
-    <comment ref="O12" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [MSFT] FY2018 10-K (filed 2018-08-03)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $110,360M (as reported)
-Method: XBRL companyfacts API
-Report: https://www.sec.gov/Archives/edgar/data/789019/000156459018019062/msft-10k_20180630.htm</t>
-      </text>
-    </comment>
     <comment ref="P12" authorId="0" shapeId="0">
       <text>
-        <t>Source: [MSFT] FY2018 Q3 10-Q (filed 2018-10-24)
+        <t>Source: [MSFT] FY2018 10-K (filed 2019-08-01)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
 Value: $29,084M (as reported)
 Method: XBRL companyfacts API
@@ -3932,7 +3938,7 @@
       <text>
         <t>Source: [MSFT] FY2018 10-Q (filed 2019-01-30)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $61,555M (as reported)
+Value: $32,471M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459019001392/msft-10q_20181231.htm</t>
       </text>
@@ -3941,7 +3947,7 @@
       <text>
         <t>Source: [MSFT] FY2019 Q1 10-Q (filed 2019-04-24)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $92,126M (as reported)
+Value: $30,571M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459019012709/msft-10q_20190331.htm</t>
       </text>
@@ -3957,7 +3963,7 @@
     </comment>
     <comment ref="T12" authorId="0" shapeId="0">
       <text>
-        <t>Source: [MSFT] FY2019 Q3 10-Q (filed 2019-10-23)
+        <t>Source: [MSFT] FY2019 10-K (filed 2020-07-30)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
 Value: $33,055M (as reported)
 Method: XBRL companyfacts API
@@ -3968,7 +3974,7 @@
       <text>
         <t>Source: [MSFT] FY2019 10-Q (filed 2020-01-29)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $69,961M (as reported)
+Value: $36,906M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459020002450/msft-10q_20191231.htm</t>
       </text>
@@ -3977,7 +3983,7 @@
       <text>
         <t>Source: [MSFT] FY2020 Q1 10-Q (filed 2020-04-29)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $104,982M (as reported)
+Value: $35,021M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459020019706/msft-10q_20200331.htm</t>
       </text>
@@ -4004,7 +4010,7 @@
       <text>
         <t>Source: [MSFT] FY2020 10-Q (filed 2021-01-26)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $80,230M (as reported)
+Value: $43,076M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459021002316/msft-10q_20201231.htm</t>
       </text>
@@ -4013,7 +4019,7 @@
       <text>
         <t>Source: [MSFT] FY2021 Q1 10-Q (filed 2021-04-27)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $121,936M (as reported)
+Value: $41,706M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459021020891/msft-10q_20210331.htm</t>
       </text>
@@ -4040,7 +4046,7 @@
       <text>
         <t>Source: [MSFT] FY2021 10-Q (filed 2022-01-25)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $97,045M (as reported)
+Value: $51,728M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459022002324/msft-10q_20211231.htm</t>
       </text>
@@ -4049,7 +4055,7 @@
       <text>
         <t>Source: [MSFT] FY2022 Q1 10-Q (filed 2022-04-26)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $146,405M (as reported)
+Value: $49,360M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459022015675/msft-10q_20220331.htm</t>
       </text>
@@ -4076,7 +4082,7 @@
       <text>
         <t>Source: [MSFT] FY2022 10-Q (filed 2023-01-24)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $102,869M (as reported)
+Value: $52,747M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459023000733/msft-10q_20221231.htm</t>
       </text>
@@ -4085,7 +4091,7 @@
       <text>
         <t>Source: [MSFT] FY2023 Q1 10-Q (filed 2023-04-25)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $155,726M (as reported)
+Value: $52,857M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017023014423/msft-20230331.htm</t>
       </text>
@@ -4112,7 +4118,7 @@
       <text>
         <t>Source: [MSFT] FY2023 10-Q (filed 2024-01-30)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $118,537M (as reported)
+Value: $62,020M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017024008814/msft-20231231.htm</t>
       </text>
@@ -4121,7 +4127,7 @@
       <text>
         <t>Source: [MSFT] FY2024 Q1 10-Q (filed 2024-04-25)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $180,395M (as reported)
+Value: $61,858M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017024048288/msft-20240331.htm</t>
       </text>
@@ -4148,7 +4154,7 @@
       <text>
         <t>Source: [MSFT] FY2024 10-Q (filed 2025-01-29)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $135,217M (as reported)
+Value: $69,632M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017025010491/msft-20241231.htm</t>
       </text>
@@ -4157,7 +4163,7 @@
       <text>
         <t>Source: [MSFT] FY2025 Q1 10-Q (filed 2025-04-30)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $205,283M (as reported)
+Value: $70,066M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017025061046/msft-20250331.htm</t>
       </text>
@@ -4174,9 +4180,8 @@
     <comment ref="AR12" authorId="0" shapeId="0">
       <text>
         <t>Source: [MSFT] FY2025 Q3 10-Q (filed 2025-10-29)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $77,673M (as reported)
-Method: XBRL companyfacts API
+Derivation:
+  Derived: H1 = Q1+Q2
 Report: https://www.sec.gov/Archives/edgar/data/789019/000119312525256321/msft-20250930.htm</t>
       </text>
     </comment>
@@ -4184,7 +4189,7 @@
       <text>
         <t>Source: [MSFT] FY2025 10-Q (filed 2026-01-28)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $158,946M (as reported)
+Value: $81,273M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000119312526027207/msft-20251231.htm</t>
       </text>
@@ -4205,7 +4210,7 @@
       <text>
         <t>Source: [ORCL] FY2015 10-Q (filed 2015-03-19)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $27,520M (as reported)
+Value: $9,327M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312515098586/d851089d10q.htm</t>
       </text>
@@ -4232,7 +4237,7 @@
       <text>
         <t>Source: [ORCL] FY2015 10-Q (filed 2015-12-18)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $17,441M (as reported)
+Value: $8,993M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312515407703/d134252d10q.htm</t>
       </text>
@@ -4241,7 +4246,7 @@
       <text>
         <t>Source: [ORCL] FY2016 10-Q (filed 2016-03-18)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $26,453M (as reported)
+Value: $9,012M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312516510333/d48108d10q.htm</t>
       </text>
@@ -4268,7 +4273,7 @@
       <text>
         <t>Source: [ORCL] FY2016 10-Q (filed 2016-12-19)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $17,630M (as reported)
+Value: $9,035M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312516797253/d289857d10q.htm</t>
       </text>
@@ -4277,7 +4282,7 @@
       <text>
         <t>Source: [ORCL] FY2017 10-Q (filed 2017-03-17)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $26,835M (as reported)
+Value: $9,205M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312517087309/d353998d10q.htm</t>
       </text>
@@ -4304,7 +4309,7 @@
       <text>
         <t>Source: [ORCL] FY2017 10-Q (filed 2017-12-18)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $18,809M (as reported)
+Value: $9,621M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312517372232/d510241d10q.htm</t>
       </text>
@@ -4313,7 +4318,7 @@
       <text>
         <t>Source: [ORCL] FY2018 10-Q (filed 2018-03-21)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $28,579M (as reported)
+Value: $9,771M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312518090646/d548579d10q.htm</t>
       </text>
@@ -4340,7 +4345,7 @@
       <text>
         <t>Source: [ORCL] FY2018 10-Q (filed 2018-12-19)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $18,755M (as reported)
+Value: $9,562M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459018031113/orcl-10q_20181130.htm</t>
       </text>
@@ -4349,7 +4354,7 @@
       <text>
         <t>Source: [ORCL] FY2019 10-Q (filed 2019-03-18)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $28,369M (as reported)
+Value: $9,614M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459019008273/orcl-10q_20190228.htm</t>
       </text>
@@ -4376,7 +4381,7 @@
       <text>
         <t>Source: [ORCL] FY2019 10-Q (filed 2019-12-13)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $18,832M (as reported)
+Value: $9,614M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459019045966/orcl-10q_20191130.htm</t>
       </text>
@@ -4385,7 +4390,7 @@
       <text>
         <t>Source: [ORCL] FY2020 10-Q (filed 2020-03-13)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $28,629M (as reported)
+Value: $9,796M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459020010833/orcl-10q_20200229.htm</t>
       </text>
@@ -4412,7 +4417,7 @@
       <text>
         <t>Source: [ORCL] FY2020 10-Q (filed 2020-12-11)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $19,167M (as reported)
+Value: $9,800M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459020056896/orcl-10q_20201130.htm</t>
       </text>
@@ -4421,7 +4426,7 @@
       <text>
         <t>Source: [ORCL] FY2021 10-Q (filed 2021-03-11)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $29,252M (as reported)
+Value: $10,085M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459021012539/orcl-10q_20210228.htm</t>
       </text>
@@ -4448,7 +4453,7 @@
       <text>
         <t>Source: [ORCL] FY2021 10-Q (filed 2021-12-10)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $20,087M (as reported)
+Value: $10,360M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459021060022/orcl-10q_20211130.htm</t>
       </text>
@@ -4457,7 +4462,7 @@
       <text>
         <t>Source: [ORCL] FY2022 10-Q (filed 2022-03-11)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $30,600M (as reported)
+Value: $10,513M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459022009859/orcl-10q_20220228.htm</t>
       </text>
@@ -4484,7 +4489,7 @@
       <text>
         <t>Source: [ORCL] FY2022 10-Q (filed 2022-12-13)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $23,720M (as reported)
+Value: $12,275M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459022039278/orcl-10q_20221130.htm</t>
       </text>
@@ -4493,7 +4498,7 @@
       <text>
         <t>Source: [ORCL] FY2023 10-Q (filed 2023-03-10)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $36,118M (as reported)
+Value: $12,398M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459023003413/orcl-10q_20230228.htm</t>
       </text>
@@ -4520,7 +4525,7 @@
       <text>
         <t>Source: [ORCL] FY2023 10-Q (filed 2023-12-12)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $25,394M (as reported)
+Value: $12,941M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000095017023069682/orcl-20231130.htm</t>
       </text>
@@ -4529,7 +4534,7 @@
       <text>
         <t>Source: [ORCL] FY2024 10-Q (filed 2024-03-12)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $38,674M (as reported)
+Value: $13,280M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000095017024029904/orcl-20240229.htm</t>
       </text>
@@ -4556,7 +4561,7 @@
       <text>
         <t>Source: [ORCL] FY2024 10-Q (filed 2024-12-10)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $27,366M (as reported)
+Value: $14,059M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000095017024134973/orcl-20241130.htm</t>
       </text>
@@ -4565,7 +4570,7 @@
       <text>
         <t>Source: [ORCL] FY2025 10-Q (filed 2025-03-11)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $41,496M (as reported)
+Value: $14,130M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000095017025037143/orcl-20250228.htm</t>
       </text>
@@ -4582,9 +4587,8 @@
     <comment ref="AR14" authorId="0" shapeId="0">
       <text>
         <t>Source: [ORCL] FY2025 10-Q (filed 2025-09-10)
-Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $14,926M (as reported)
-Method: XBRL companyfacts API
+Derivation:
+  Derived: 9M = Q1+Q2+Q3
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312525200095/orcl-20250831.htm</t>
       </text>
     </comment>
@@ -4592,7 +4596,7 @@
       <text>
         <t>Source: [ORCL] FY2025 10-Q (filed 2025-12-11)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $30,983M (as reported)
+Value: $16,058M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312525315925/orcl-20251130.htm</t>
       </text>
@@ -4601,7 +4605,7 @@
       <text>
         <t>Source: [ORCL] FY2026 10-Q (filed 2026-03-11)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $48,173M (as reported)
+Value: $17,190M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312526101045/orcl-20260228.htm</t>
       </text>
@@ -5461,7 +5465,7 @@
       <text>
         <t>Source: [AMZN] FY2015 Q1 10-Q (filed 2015-04-24)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $4,684M (as reported)
+Value: $871M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872415000038/amzn-20150331x10q.htm</t>
       </text>
@@ -5470,7 +5474,7 @@
       <text>
         <t>Source: [AMZN] FY2015 Q2 10-Q (filed 2015-07-24)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $4,607M (as reported)
+Value: $1,213M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872415000087/amzn-20150630x10q.htm</t>
       </text>
@@ -5479,7 +5483,7 @@
       <text>
         <t>Source: [AMZN] FY2015 Q3 10-Q (filed 2015-10-23)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $4,424M (as reported)
+Value: $1,195M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872415000126/amzn-20150930x10q.htm</t>
       </text>
@@ -5497,7 +5501,7 @@
       <text>
         <t>Source: [AMZN] FY2016 Q1 10-Q (filed 2016-04-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $4,897M (as reported)
+Value: $1,179M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872416000227/amzn-20160331x10q.htm</t>
       </text>
@@ -5506,7 +5510,7 @@
       <text>
         <t>Source: [AMZN] FY2016 Q2 10-Q (filed 2016-07-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $5,395M (as reported)
+Value: $1,711M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872416000286/amzn-20160630x10q.htm</t>
       </text>
@@ -5515,7 +5519,7 @@
       <text>
         <t>Source: [AMZN] FY2016 Q3 10-Q (filed 2016-10-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $6,040M (as reported)
+Value: $1,841M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872416000324/amzn-20160930x10q.htm</t>
       </text>
@@ -5533,7 +5537,7 @@
       <text>
         <t>Source: [AMZN] FY2017 Q1 10-Q (filed 2017-04-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $7,417M (as reported)
+Value: $1,861M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872417000051/amzn-20170331x10q.htm</t>
       </text>
@@ -5542,7 +5546,7 @@
       <text>
         <t>Source: [AMZN] FY2017 Q3 10-Q (filed 2017-10-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $10,750M (as reported)
+Value: $3,074M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872417000135/amzn-20170930x10q.htm</t>
       </text>
@@ -5560,7 +5564,7 @@
       <text>
         <t>Source: [AMZN] FY2018 Q1 10-Q (filed 2018-04-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $12,905M (as reported)
+Value: $3,098M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872418000072/amzn-20180331x10q.htm</t>
       </text>
@@ -5569,7 +5573,7 @@
       <text>
         <t>Source: [AMZN] FY2018 Q2 10-Q (filed 2018-07-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $13,035M (as reported)
+Value: $3,243M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872418000108/amzn-20180630x10q.htm</t>
       </text>
@@ -5578,7 +5582,7 @@
       <text>
         <t>Source: [AMZN] FY2018 Q3 10-Q (filed 2018-10-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $13,312M (as reported)
+Value: $3,352M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872418000159/amzn-20180930x10q.htm</t>
       </text>
@@ -5596,7 +5600,7 @@
       <text>
         <t>Source: [AMZN] FY2019 Q1 10-Q (filed 2019-04-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $13,619M (as reported)
+Value: $3,290M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872419000043/amzn-2019331x10q.htm</t>
       </text>
@@ -5605,7 +5609,7 @@
       <text>
         <t>Source: [AMZN] FY2019 Q2 10-Q (filed 2019-07-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $13,938M (as reported)
+Value: $3,562M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872419000071/amzn-2019630x10q.htm</t>
       </text>
@@ -5614,7 +5618,7 @@
       <text>
         <t>Source: [AMZN] FY2019 Q3 10-Q (filed 2019-10-25)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $15,282M (as reported)
+Value: $4,697M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872419000089/amzn-2019930x10q.htm</t>
       </text>
@@ -5632,7 +5636,7 @@
       <text>
         <t>Source: [AMZN] FY2020 Q1 10-Q (filed 2020-05-01)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $20,365M (as reported)
+Value: $6,795M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872420000010/amzn-20200331x10q.htm</t>
       </text>
@@ -5641,7 +5645,7 @@
       <text>
         <t>Source: [AMZN] FY2020 Q2 10-Q (filed 2020-07-31)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $24,263M (as reported)
+Value: $7,459M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872420000021/amzn-20200630.htm</t>
       </text>
@@ -5650,7 +5654,7 @@
       <text>
         <t>Source: [AMZN] FY2020 Q3 10-Q (filed 2020-10-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $30,629M (as reported)
+Value: $11,063M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872420000030/amzn-20200930.htm</t>
       </text>
@@ -5668,7 +5672,7 @@
       <text>
         <t>Source: [AMZN] FY2021 Q1 10-Q (filed 2021-04-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $45,427M (as reported)
+Value: $12,082M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872421000010/amzn-20210331.htm</t>
       </text>
@@ -5677,7 +5681,7 @@
       <text>
         <t>Source: [AMZN] FY2021 Q2 10-Q (filed 2021-07-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $52,256M (as reported)
+Value: $14,288M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872421000020/amzn-20210630.htm</t>
       </text>
@@ -5686,7 +5690,7 @@
       <text>
         <t>Source: [AMZN] FY2021 Q3 10-Q (filed 2021-10-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $56,941M (as reported)
+Value: $15,748M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872421000028/amzn-20210930.htm</t>
       </text>
@@ -5704,7 +5708,7 @@
       <text>
         <t>Source: [AMZN] FY2022 Q1 10-Q (filed 2022-04-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $63,922M (as reported)
+Value: $14,951M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872422000013/amzn-20220331.htm</t>
       </text>
@@ -5713,7 +5717,7 @@
       <text>
         <t>Source: [AMZN] FY2022 Q2 10-Q (filed 2022-07-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $65,358M (as reported)
+Value: $15,724M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872422000019/amzn-20220630.htm</t>
       </text>
@@ -5722,7 +5726,7 @@
       <text>
         <t>Source: [AMZN] FY2022 Q3 10-Q (filed 2022-10-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $65,988M (as reported)
+Value: $16,378M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872422000023/amzn-20220930.htm</t>
       </text>
@@ -5740,7 +5744,7 @@
       <text>
         <t>Source: [AMZN] FY2023 Q1 10-Q (filed 2023-04-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $62,901M (as reported)
+Value: $14,207M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872423000008/amzn-20230331.htm</t>
       </text>
@@ -5749,7 +5753,7 @@
       <text>
         <t>Source: [AMZN] FY2023 Q2 10-Q (filed 2023-08-04)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $58,632M (as reported)
+Value: $11,455M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872423000012/amzn-20230630.htm</t>
       </text>
@@ -5758,7 +5762,7 @@
       <text>
         <t>Source: [AMZN] FY2023 Q3 10-Q (filed 2023-10-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $54,733M (as reported)
+Value: $12,479M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872423000018/amzn-20230930.htm</t>
       </text>
@@ -5776,7 +5780,7 @@
       <text>
         <t>Source: [AMZN] FY2024 Q1 10-Q (filed 2024-05-01)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $53,447M (as reported)
+Value: $14,925M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872424000083/amzn-20240331.htm</t>
       </text>
@@ -5785,7 +5789,7 @@
       <text>
         <t>Source: [AMZN] FY2024 Q2 10-Q (filed 2024-08-02)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $59,612M (as reported)
+Value: $17,620M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872424000130/amzn-20240630.htm</t>
       </text>
@@ -5794,7 +5798,7 @@
       <text>
         <t>Source: [AMZN] FY2024 Q3 10-Q (filed 2024-11-01)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $69,753M (as reported)
+Value: $22,620M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872424000161/amzn-20240930.htm</t>
       </text>
@@ -5812,7 +5816,7 @@
       <text>
         <t>Source: [AMZN] FY2025 Q1 10-Q (filed 2025-05-02)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $93,093M (as reported)
+Value: $25,019M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872425000036/amzn-20250331.htm</t>
       </text>
@@ -5821,7 +5825,7 @@
       <text>
         <t>Source: [AMZN] FY2025 Q2 10-Q (filed 2025-08-01)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $107,656M (as reported)
+Value: $32,183M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872425000086/amzn-20250630.htm</t>
       </text>
@@ -5830,7 +5834,7 @@
       <text>
         <t>Source: [AMZN] FY2025 Q3 10-Q (filed 2025-10-31)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $120,131M (as reported)
+Value: $35,095M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872425000123/amzn-20250930.htm</t>
       </text>
@@ -6100,7 +6104,7 @@
       <text>
         <t>Source: [GOOGL] FY2015 Q2 10-Q (filed 2016-08-04)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $5,442M (as reported)
+Value: $2,515M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000156761922020201/xslForm13F_X01/primary_doc.xml</t>
       </text>
@@ -6109,7 +6113,7 @@
       <text>
         <t>Source: [GOOGL] FY2015 Q3 10-Q (filed 2015-10-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $7,815M (as reported)
+Value: $2,383M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204415000005/alpha10-qq32015.htm</t>
       </text>
@@ -6136,7 +6140,7 @@
       <text>
         <t>Source: [GOOGL] FY2016 Q2 10-Q (filed 2016-08-04)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $4,551M (as reported)
+Value: $2,123M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204416000032/goog10-qq22016.htm</t>
       </text>
@@ -6145,7 +6149,7 @@
       <text>
         <t>Source: [GOOGL] FY2016 Q3 10-Q (filed 2016-11-03)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $7,134M (as reported)
+Value: $2,554M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204416000038/goog10-qq32016.htm</t>
       </text>
@@ -6172,7 +6176,7 @@
       <text>
         <t>Source: [GOOGL] FY2017 Q2 10-Q (filed 2017-07-25)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $5,339M (as reported)
+Value: $2,831M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204417000026/goog10-qq22017.htm</t>
       </text>
@@ -6181,7 +6185,7 @@
       <text>
         <t>Source: [GOOGL] FY2017 Q3 10-Q (filed 2017-10-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $8,877M (as reported)
+Value: $3,538M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204417000042/goog10-qq32017.htm</t>
       </text>
@@ -6208,7 +6212,7 @@
       <text>
         <t>Source: [GOOGL] FY2018 Q2 10-Q (filed 2018-07-24)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $12,776M (as reported)
+Value: $5,477M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204418000027/goog10-qq22018.htm</t>
       </text>
@@ -6217,7 +6221,7 @@
       <text>
         <t>Source: [GOOGL] FY2018 Q3 10-Q (filed 2018-10-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $18,058M (as reported)
+Value: $5,282M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204418000035/goog10-qq32018.htm</t>
       </text>
@@ -6244,7 +6248,7 @@
       <text>
         <t>Source: [GOOGL] FY2019 Q2 10-Q (filed 2019-07-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $10,764M (as reported)
+Value: $6,126M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204419000023/goog10-qq22019.htm</t>
       </text>
@@ -6253,7 +6257,7 @@
       <text>
         <t>Source: [GOOGL] FY2019 Q3 10-Q (filed 2019-10-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $17,496M (as reported)
+Value: $6,732M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204419000032/goog10-qq32019.htm</t>
       </text>
@@ -6280,7 +6284,7 @@
       <text>
         <t>Source: [GOOGL] FY2020 Q2 10-Q (filed 2020-07-31)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $11,396M (as reported)
+Value: $5,391M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204420000032/goog-20200630.htm</t>
       </text>
@@ -6289,7 +6293,7 @@
       <text>
         <t>Source: [GOOGL] FY2020 Q3 10-Q (filed 2020-10-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $16,802M (as reported)
+Value: $5,406M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204420000050/goog-20200930.htm</t>
       </text>
@@ -6937,7 +6941,7 @@
       <text>
         <t>Source: [MSFT] FY2015 Q1 10-Q (filed 2015-04-23)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $4,163M (as reported)
+Value: $1,391M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000119312515144151/d860721d10q.htm</t>
       </text>
@@ -6964,7 +6968,7 @@
       <text>
         <t>Source: [MSFT] FY2015 10-Q (filed 2016-01-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $3,380M (as reported)
+Value: $2,024M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000119312516441821/d15167d10q.htm</t>
       </text>
@@ -6973,7 +6977,7 @@
       <text>
         <t>Source: [MSFT] FY2016 Q1 10-Q (filed 2016-04-21)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $5,688M (as reported)
+Value: $2,308M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000119312516550254/d256147d10q.htm</t>
       </text>
@@ -7000,7 +7004,7 @@
       <text>
         <t>Source: [MSFT] FY2016 10-Q (filed 2017-01-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $4,151M (as reported)
+Value: $1,988M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459017000654/msft-10q_20161231.htm</t>
       </text>
@@ -7009,7 +7013,7 @@
       <text>
         <t>Source: [MSFT] FY2017 Q1 10-Q (filed 2017-04-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $5,846M (as reported)
+Value: $1,695M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459017007547/msft-10q_20170331.htm</t>
       </text>
@@ -7036,7 +7040,7 @@
       <text>
         <t>Source: [MSFT] FY2017 10-Q (filed 2018-01-31)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $4,718M (as reported)
+Value: $2,586M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459018001129/msft-10q_20171231.htm</t>
       </text>
@@ -7045,7 +7049,7 @@
       <text>
         <t>Source: [MSFT] FY2018 Q1 10-Q (filed 2018-04-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $7,652M (as reported)
+Value: $2,934M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459018009307/msft-10q_20180331.htm</t>
       </text>
@@ -7072,7 +7076,7 @@
       <text>
         <t>Source: [MSFT] FY2018 10-Q (filed 2019-01-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $7,309M (as reported)
+Value: $3,707M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459019001392/msft-10q_20181231.htm</t>
       </text>
@@ -7081,7 +7085,7 @@
       <text>
         <t>Source: [MSFT] FY2019 Q1 10-Q (filed 2019-04-24)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $9,874M (as reported)
+Value: $2,565M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459019012709/msft-10q_20190331.htm</t>
       </text>
@@ -7108,7 +7112,7 @@
       <text>
         <t>Source: [MSFT] FY2019 10-Q (filed 2020-01-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $6,930M (as reported)
+Value: $3,545M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459020002450/msft-10q_20191231.htm</t>
       </text>
@@ -7117,7 +7121,7 @@
       <text>
         <t>Source: [MSFT] FY2020 Q1 10-Q (filed 2020-04-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $10,697M (as reported)
+Value: $3,767M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459020019706/msft-10q_20200331.htm</t>
       </text>
@@ -7144,7 +7148,7 @@
       <text>
         <t>Source: [MSFT] FY2020 10-Q (filed 2021-01-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $9,081M (as reported)
+Value: $4,174M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459021002316/msft-10q_20201231.htm</t>
       </text>
@@ -7153,7 +7157,7 @@
       <text>
         <t>Source: [MSFT] FY2021 Q1 10-Q (filed 2021-04-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $14,170M (as reported)
+Value: $5,089M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459021020891/msft-10q_20210331.htm</t>
       </text>
@@ -7180,7 +7184,7 @@
       <text>
         <t>Source: [MSFT] FY2021 10-Q (filed 2022-01-25)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $11,675M (as reported)
+Value: $5,865M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459022002324/msft-10q_20211231.htm</t>
       </text>
@@ -7189,7 +7193,7 @@
       <text>
         <t>Source: [MSFT] FY2022 Q1 10-Q (filed 2022-04-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $17,015M (as reported)
+Value: $5,340M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459022015675/msft-10q_20220331.htm</t>
       </text>
@@ -7216,7 +7220,7 @@
       <text>
         <t>Source: [MSFT] FY2022 10-Q (filed 2023-01-24)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $12,557M (as reported)
+Value: $6,274M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459023000733/msft-10q_20221231.htm</t>
       </text>
@@ -7225,7 +7229,7 @@
       <text>
         <t>Source: [MSFT] FY2023 Q1 10-Q (filed 2023-04-25)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $19,164M (as reported)
+Value: $6,607M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017023014423/msft-20230331.htm</t>
       </text>
@@ -7252,7 +7256,7 @@
       <text>
         <t>Source: [MSFT] FY2023 10-Q (filed 2024-01-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $19,652M (as reported)
+Value: $9,735M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017024008814/msft-20231231.htm</t>
       </text>
@@ -7261,7 +7265,7 @@
       <text>
         <t>Source: [MSFT] FY2024 Q1 10-Q (filed 2024-04-25)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $30,604M (as reported)
+Value: $10,952M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017024048288/msft-20240331.htm</t>
       </text>
@@ -7288,7 +7292,7 @@
       <text>
         <t>Source: [MSFT] FY2024 10-Q (filed 2025-01-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $30,727M (as reported)
+Value: $15,804M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017025010491/msft-20241231.htm</t>
       </text>
@@ -7297,7 +7301,7 @@
       <text>
         <t>Source: [MSFT] FY2025 Q1 10-Q (filed 2025-04-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $47,472M (as reported)
+Value: $16,745M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017025061046/msft-20250331.htm</t>
       </text>
@@ -7314,9 +7318,8 @@
     <comment ref="AR12" authorId="0" shapeId="0">
       <text>
         <t>Source: [MSFT] FY2025 Q3 10-Q (filed 2025-10-29)
-Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $19,394M (as reported)
-Method: XBRL companyfacts API
+Derivation:
+  Derived: H1 = Q1+Q2
 Report: https://www.sec.gov/Archives/edgar/data/789019/000119312525256321/msft-20250930.htm</t>
       </text>
     </comment>
@@ -7324,7 +7327,7 @@
       <text>
         <t>Source: [MSFT] FY2025 10-Q (filed 2026-01-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $49,270M (as reported)
+Value: $29,876M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000119312526027207/msft-20251231.htm</t>
       </text>
@@ -12266,6 +12269,15 @@
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872426000004/amzn-20251231.htm</t>
       </text>
     </comment>
+    <comment ref="J14" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [APLD] FY2021 10-K (filed 2022-08-29)
+Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
+Value: $0M (as reported)
+Method: XBRL companyfacts API
+Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1144879&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
+      </text>
+    </comment>
     <comment ref="K14" authorId="0" shapeId="0">
       <text>
         <t>Source: [APLD] FY2022 10-K (filed 2022-08-29)
@@ -12296,9 +12308,8 @@
     <comment ref="N14" authorId="0" shapeId="0">
       <text>
         <t>Source: [APLD] FY2025 10-K (filed 2025-07-30)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $144M (as reported)
-Method: XBRL companyfacts API
+Derivation:
+  Derived: 9M = Q1+Q2+Q3
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487925000021/apld-20250531.htm</t>
       </text>
     </comment>
@@ -12390,9 +12401,8 @@
     <comment ref="J17" authorId="0" shapeId="0">
       <text>
         <t>Source: [APLD] FY2021 10-K (filed 2022-08-29)
-Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $-0M (as reported)
-Method: XBRL companyfacts API
+Derivation:
+  Derived: Q4 = FY - 9M
 Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1144879&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
       </text>
     </comment>
@@ -12469,7 +12479,7 @@
       <text>
         <t>Source: [APLD] FY2025 10-K (filed 2025-07-30)
 Derivation:
-  Derived: Q2 = H1 - Q1
+  Derived: 9M = Q1+Q2+Q3
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487925000021/apld-20250531.htm</t>
       </text>
     </comment>
@@ -16361,7 +16371,7 @@
       <text>
         <t>Source: [AMZN] FY2017 Q3 10-Q (filed 2017-10-27)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $117,413M (as reported)
+Value: $43,744M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872417000135/amzn-20170930x10q.htm</t>
       </text>
@@ -16386,9 +16396,9 @@
     </comment>
     <comment ref="P8" authorId="0" shapeId="0">
       <text>
-        <t>Source: [AMZN] FY2018 Q2 10-Q (filed 2018-07-27)
+        <t>Source: [AMZN] FY2018 10-K (filed 2019-02-01)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $103,928M (as reported)
+Value: $52,886M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872418000108/amzn-20180630x10q.htm</t>
       </text>
@@ -16397,7 +16407,7 @@
       <text>
         <t>Source: [AMZN] FY2018 Q3 10-Q (filed 2018-10-26)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $160,504M (as reported)
+Value: $56,576M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872418000159/amzn-20180930x10q.htm</t>
       </text>
@@ -16413,7 +16423,7 @@
     </comment>
     <comment ref="S8" authorId="0" shapeId="0">
       <text>
-        <t>Source: [AMZN] FY2019 Q1 10-Q (filed 2019-04-26)
+        <t>Source: [AMZN] FY2019 10-K (filed 2020-01-31)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
 Value: $59,700M (as reported)
 Method: XBRL companyfacts API
@@ -16424,7 +16434,7 @@
       <text>
         <t>Source: [AMZN] FY2019 Q2 10-Q (filed 2019-07-26)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $123,104M (as reported)
+Value: $63,404M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872419000071/amzn-2019630x10q.htm</t>
       </text>
@@ -16433,7 +16443,7 @@
       <text>
         <t>Source: [AMZN] FY2019 Q3 10-Q (filed 2019-10-25)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $193,086M (as reported)
+Value: $69,981M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872419000089/amzn-2019930x10q.htm</t>
       </text>
@@ -16449,7 +16459,7 @@
     </comment>
     <comment ref="W8" authorId="0" shapeId="0">
       <text>
-        <t>Source: [AMZN] FY2020 Q1 10-Q (filed 2020-05-01)
+        <t>Source: [AMZN] FY2020 10-K (filed 2021-02-03)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
 Value: $75,452M (as reported)
 Method: XBRL companyfacts API
@@ -16460,7 +16470,7 @@
       <text>
         <t>Source: [AMZN] FY2020 Q2 10-Q (filed 2020-07-31)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $164,364M (as reported)
+Value: $88,912M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872420000021/amzn-20200630.htm</t>
       </text>
@@ -16469,7 +16479,7 @@
       <text>
         <t>Source: [AMZN] FY2020 Q3 10-Q (filed 2020-10-30)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $260,509M (as reported)
+Value: $96,145M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872420000030/amzn-20200930.htm</t>
       </text>
@@ -16496,7 +16506,7 @@
       <text>
         <t>Source: [AMZN] FY2021 Q2 10-Q (filed 2021-07-30)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $221,598M (as reported)
+Value: $113,080M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872421000020/amzn-20210630.htm</t>
       </text>
@@ -16505,7 +16515,7 @@
       <text>
         <t>Source: [AMZN] FY2021 Q3 10-Q (filed 2021-10-29)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $332,410M (as reported)
+Value: $110,812M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872421000028/amzn-20210930.htm</t>
       </text>
@@ -16532,7 +16542,7 @@
       <text>
         <t>Source: [AMZN] FY2022 Q2 10-Q (filed 2022-07-29)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $237,678M (as reported)
+Value: $121,234M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872422000019/amzn-20220630.htm</t>
       </text>
@@ -16541,7 +16551,7 @@
       <text>
         <t>Source: [AMZN] FY2022 Q3 10-Q (filed 2022-10-28)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $364,779M (as reported)
+Value: $127,101M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872422000023/amzn-20220930.htm</t>
       </text>
@@ -16568,7 +16578,7 @@
       <text>
         <t>Source: [AMZN] FY2023 Q2 10-Q (filed 2023-08-04)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $261,741M (as reported)
+Value: $134,383M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872423000012/amzn-20230630.htm</t>
       </text>
@@ -16577,7 +16587,7 @@
       <text>
         <t>Source: [AMZN] FY2023 Q3 10-Q (filed 2023-10-27)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $404,824M (as reported)
+Value: $143,083M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872423000018/amzn-20230930.htm</t>
       </text>
@@ -16604,7 +16614,7 @@
       <text>
         <t>Source: [AMZN] FY2024 Q2 10-Q (filed 2024-08-02)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $291,290M (as reported)
+Value: $147,977M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872424000130/amzn-20240630.htm</t>
       </text>
@@ -16613,7 +16623,7 @@
       <text>
         <t>Source: [AMZN] FY2024 Q3 10-Q (filed 2024-11-01)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $450,167M (as reported)
+Value: $158,877M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872424000161/amzn-20240930.htm</t>
       </text>
@@ -16640,7 +16650,7 @@
       <text>
         <t>Source: [AMZN] FY2025 Q2 10-Q (filed 2025-08-01)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $323,369M (as reported)
+Value: $167,702M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872425000086/amzn-20250630.htm</t>
       </text>
@@ -16649,7 +16659,7 @@
       <text>
         <t>Source: [AMZN] FY2025 Q3 10-Q (filed 2025-10-31)
 Section: Item 8 - Consolidated Statements of Income, line "Net sales"
-Value: $503,538M (as reported)
+Value: $180,169M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872425000123/amzn-20250930.htm</t>
       </text>
@@ -17107,7 +17117,7 @@
       <text>
         <t>Source: [AMZN] FY2015 Q1 10-Q (filed 2015-04-24)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $4,684M (as reported)
+Value: $871M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872415000038/amzn-20150331x10q.htm</t>
       </text>
@@ -17116,7 +17126,7 @@
       <text>
         <t>Source: [AMZN] FY2015 Q2 10-Q (filed 2015-07-24)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $4,607M (as reported)
+Value: $1,213M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872415000087/amzn-20150630x10q.htm</t>
       </text>
@@ -17125,7 +17135,7 @@
       <text>
         <t>Source: [AMZN] FY2015 Q3 10-Q (filed 2015-10-23)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $4,424M (as reported)
+Value: $1,195M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872415000126/amzn-20150930x10q.htm</t>
       </text>
@@ -17143,7 +17153,7 @@
       <text>
         <t>Source: [AMZN] FY2016 Q1 10-Q (filed 2016-04-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $4,897M (as reported)
+Value: $1,179M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872416000227/amzn-20160331x10q.htm</t>
       </text>
@@ -17152,7 +17162,7 @@
       <text>
         <t>Source: [AMZN] FY2016 Q2 10-Q (filed 2016-07-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $5,395M (as reported)
+Value: $1,711M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872416000286/amzn-20160630x10q.htm</t>
       </text>
@@ -17161,7 +17171,7 @@
       <text>
         <t>Source: [AMZN] FY2016 Q3 10-Q (filed 2016-10-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $6,040M (as reported)
+Value: $1,841M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872416000324/amzn-20160930x10q.htm</t>
       </text>
@@ -17179,7 +17189,7 @@
       <text>
         <t>Source: [AMZN] FY2017 Q1 10-Q (filed 2017-04-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $7,417M (as reported)
+Value: $1,861M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872417000051/amzn-20170331x10q.htm</t>
       </text>
@@ -17188,7 +17198,7 @@
       <text>
         <t>Source: [AMZN] FY2017 Q3 10-Q (filed 2017-10-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $10,750M (as reported)
+Value: $3,074M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872417000135/amzn-20170930x10q.htm</t>
       </text>
@@ -17206,7 +17216,7 @@
       <text>
         <t>Source: [AMZN] FY2018 Q1 10-Q (filed 2018-04-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $12,905M (as reported)
+Value: $3,098M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872418000072/amzn-20180331x10q.htm</t>
       </text>
@@ -17215,7 +17225,7 @@
       <text>
         <t>Source: [AMZN] FY2018 Q2 10-Q (filed 2018-07-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $13,035M (as reported)
+Value: $3,243M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872418000108/amzn-20180630x10q.htm</t>
       </text>
@@ -17224,7 +17234,7 @@
       <text>
         <t>Source: [AMZN] FY2018 Q3 10-Q (filed 2018-10-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $13,312M (as reported)
+Value: $3,352M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872418000159/amzn-20180930x10q.htm</t>
       </text>
@@ -17242,7 +17252,7 @@
       <text>
         <t>Source: [AMZN] FY2019 Q1 10-Q (filed 2019-04-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $13,619M (as reported)
+Value: $3,290M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872419000043/amzn-2019331x10q.htm</t>
       </text>
@@ -17251,7 +17261,7 @@
       <text>
         <t>Source: [AMZN] FY2019 Q2 10-Q (filed 2019-07-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $13,938M (as reported)
+Value: $3,562M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872419000071/amzn-2019630x10q.htm</t>
       </text>
@@ -17260,7 +17270,7 @@
       <text>
         <t>Source: [AMZN] FY2019 Q3 10-Q (filed 2019-10-25)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $15,282M (as reported)
+Value: $4,697M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872419000089/amzn-2019930x10q.htm</t>
       </text>
@@ -17278,7 +17288,7 @@
       <text>
         <t>Source: [AMZN] FY2020 Q1 10-Q (filed 2020-05-01)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $20,365M (as reported)
+Value: $6,795M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872420000010/amzn-20200331x10q.htm</t>
       </text>
@@ -17287,7 +17297,7 @@
       <text>
         <t>Source: [AMZN] FY2020 Q2 10-Q (filed 2020-07-31)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $24,263M (as reported)
+Value: $7,459M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872420000021/amzn-20200630.htm</t>
       </text>
@@ -17296,7 +17306,7 @@
       <text>
         <t>Source: [AMZN] FY2020 Q3 10-Q (filed 2020-10-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $30,629M (as reported)
+Value: $11,063M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872420000030/amzn-20200930.htm</t>
       </text>
@@ -17314,7 +17324,7 @@
       <text>
         <t>Source: [AMZN] FY2021 Q1 10-Q (filed 2021-04-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $45,427M (as reported)
+Value: $12,082M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872421000010/amzn-20210331.htm</t>
       </text>
@@ -17323,7 +17333,7 @@
       <text>
         <t>Source: [AMZN] FY2021 Q2 10-Q (filed 2021-07-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $52,256M (as reported)
+Value: $14,288M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872421000020/amzn-20210630.htm</t>
       </text>
@@ -17332,7 +17342,7 @@
       <text>
         <t>Source: [AMZN] FY2021 Q3 10-Q (filed 2021-10-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $56,941M (as reported)
+Value: $15,748M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872421000028/amzn-20210930.htm</t>
       </text>
@@ -17350,7 +17360,7 @@
       <text>
         <t>Source: [AMZN] FY2022 Q1 10-Q (filed 2022-04-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $63,922M (as reported)
+Value: $14,951M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872422000013/amzn-20220331.htm</t>
       </text>
@@ -17359,7 +17369,7 @@
       <text>
         <t>Source: [AMZN] FY2022 Q2 10-Q (filed 2022-07-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $65,358M (as reported)
+Value: $15,724M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872422000019/amzn-20220630.htm</t>
       </text>
@@ -17368,7 +17378,7 @@
       <text>
         <t>Source: [AMZN] FY2022 Q3 10-Q (filed 2022-10-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $65,988M (as reported)
+Value: $16,378M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872422000023/amzn-20220930.htm</t>
       </text>
@@ -17386,7 +17396,7 @@
       <text>
         <t>Source: [AMZN] FY2023 Q1 10-Q (filed 2023-04-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $62,901M (as reported)
+Value: $14,207M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872423000008/amzn-20230331.htm</t>
       </text>
@@ -17395,7 +17405,7 @@
       <text>
         <t>Source: [AMZN] FY2023 Q2 10-Q (filed 2023-08-04)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $58,632M (as reported)
+Value: $11,455M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872423000012/amzn-20230630.htm</t>
       </text>
@@ -17404,7 +17414,7 @@
       <text>
         <t>Source: [AMZN] FY2023 Q3 10-Q (filed 2023-10-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $54,733M (as reported)
+Value: $12,479M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872423000018/amzn-20230930.htm</t>
       </text>
@@ -17422,7 +17432,7 @@
       <text>
         <t>Source: [AMZN] FY2024 Q1 10-Q (filed 2024-05-01)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $53,447M (as reported)
+Value: $14,925M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872424000083/amzn-20240331.htm</t>
       </text>
@@ -17431,7 +17441,7 @@
       <text>
         <t>Source: [AMZN] FY2024 Q2 10-Q (filed 2024-08-02)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $59,612M (as reported)
+Value: $17,620M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872424000130/amzn-20240630.htm</t>
       </text>
@@ -17440,7 +17450,7 @@
       <text>
         <t>Source: [AMZN] FY2024 Q3 10-Q (filed 2024-11-01)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $69,753M (as reported)
+Value: $22,620M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872424000161/amzn-20240930.htm</t>
       </text>
@@ -17458,7 +17468,7 @@
       <text>
         <t>Source: [AMZN] FY2025 Q1 10-Q (filed 2025-05-02)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $93,093M (as reported)
+Value: $25,019M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872425000036/amzn-20250331.htm</t>
       </text>
@@ -17467,7 +17477,7 @@
       <text>
         <t>Source: [AMZN] FY2025 Q2 10-Q (filed 2025-08-01)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $107,656M (as reported)
+Value: $32,183M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872425000086/amzn-20250630.htm</t>
       </text>
@@ -17476,7 +17486,7 @@
       <text>
         <t>Source: [AMZN] FY2025 Q3 10-Q (filed 2025-10-31)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $120,131M (as reported)
+Value: $35,095M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872425000123/amzn-20250930.htm</t>
       </text>
@@ -17494,7 +17504,7 @@
       <text>
         <t>Source: [AMZN] FY2015 Q1 10-Q (filed 2015-04-24)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $7,845M (as reported)
+Value: $-1,499M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872415000038/amzn-20150331x10q.htm</t>
       </text>
@@ -17503,7 +17513,7 @@
       <text>
         <t>Source: [AMZN] FY2015 Q2 10-Q (filed 2015-07-24)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $8,980M (as reported)
+Value: $1,997M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872415000087/amzn-20150630x10q.htm</t>
       </text>
@@ -17512,7 +17522,7 @@
       <text>
         <t>Source: [AMZN] FY2015 Q3 10-Q (filed 2015-10-23)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $9,823M (as reported)
+Value: $2,610M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872415000126/amzn-20150930x10q.htm</t>
       </text>
@@ -17530,7 +17540,7 @@
       <text>
         <t>Source: [AMZN] FY2016 Q1 10-Q (filed 2016-04-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $11,258M (as reported)
+Value: $-2,160M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872416000227/amzn-20160331x10q.htm</t>
       </text>
@@ -17539,7 +17549,7 @@
       <text>
         <t>Source: [AMZN] FY2016 Q2 10-Q (filed 2016-07-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $12,726M (as reported)
+Value: $3,465M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872416000286/amzn-20160630x10q.htm</t>
       </text>
@@ -17548,7 +17558,7 @@
       <text>
         <t>Source: [AMZN] FY2016 Q3 10-Q (filed 2016-10-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $14,603M (as reported)
+Value: $4,486M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872416000324/amzn-20160930x10q.htm</t>
       </text>
@@ -17566,7 +17576,7 @@
       <text>
         <t>Source: [AMZN] FY2017 Q1 10-Q (filed 2017-04-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $17,634M (as reported)
+Value: $-1,590M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872417000051/amzn-20170331x10q.htm</t>
       </text>
@@ -17575,7 +17585,7 @@
       <text>
         <t>Source: [AMZN] FY2017 Q2 10-Q (filed 2017-07-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $17,885M (as reported)
+Value: $3,829M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872417000100/amzn-20170630x10q.htm</t>
       </text>
@@ -17584,7 +17594,7 @@
       <text>
         <t>Source: [AMZN] FY2017 Q3 10-Q (filed 2017-10-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $17,077M (as reported)
+Value: $3,851M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872417000135/amzn-20170930x10q.htm</t>
       </text>
@@ -17602,7 +17612,7 @@
       <text>
         <t>Source: [AMZN] FY2018 Q1 10-Q (filed 2018-04-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $18,194M (as reported)
+Value: $-1,791M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872418000072/amzn-20180331x10q.htm</t>
       </text>
@@ -17611,7 +17621,7 @@
       <text>
         <t>Source: [AMZN] FY2018 Q2 10-Q (filed 2018-07-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $21,793M (as reported)
+Value: $7,449M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872418000108/amzn-20180630x10q.htm</t>
       </text>
@@ -17620,7 +17630,7 @@
       <text>
         <t>Source: [AMZN] FY2018 Q3 10-Q (filed 2018-10-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $26,604M (as reported)
+Value: $8,588M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872418000159/amzn-20180930x10q.htm</t>
       </text>
@@ -17638,7 +17648,7 @@
       <text>
         <t>Source: [AMZN] FY2019 Q1 10-Q (filed 2019-04-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $34,360M (as reported)
+Value: $1,846M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872419000043/amzn-2019331x10q.htm</t>
       </text>
@@ -17647,7 +17657,7 @@
       <text>
         <t>Source: [AMZN] FY2019 Q2 10-Q (filed 2019-07-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $36,029M (as reported)
+Value: $9,118M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872419000071/amzn-2019630x10q.htm</t>
       </text>
@@ -17656,7 +17666,7 @@
       <text>
         <t>Source: [AMZN] FY2019 Q3 10-Q (filed 2019-10-25)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $35,332M (as reported)
+Value: $7,892M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872419000089/amzn-2019930x10q.htm</t>
       </text>
@@ -17674,7 +17684,7 @@
       <text>
         <t>Source: [AMZN] FY2020 Q1 10-Q (filed 2020-05-01)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $39,732M (as reported)
+Value: $3,064M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872420000010/amzn-20200331x10q.htm</t>
       </text>
@@ -17683,7 +17693,7 @@
       <text>
         <t>Source: [AMZN] FY2020 Q2 10-Q (filed 2020-07-31)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $51,220M (as reported)
+Value: $20,606M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872420000021/amzn-20200630.htm</t>
       </text>
@@ -17692,7 +17702,7 @@
       <text>
         <t>Source: [AMZN] FY2020 Q3 10-Q (filed 2020-10-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $55,292M (as reported)
+Value: $11,964M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872420000030/amzn-20200930.htm</t>
       </text>
@@ -17710,7 +17720,7 @@
       <text>
         <t>Source: [AMZN] FY2021 Q1 10-Q (filed 2021-04-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $67,213M (as reported)
+Value: $4,213M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872421000010/amzn-20210331.htm</t>
       </text>
@@ -17719,7 +17729,7 @@
       <text>
         <t>Source: [AMZN] FY2021 Q2 10-Q (filed 2021-07-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $59,322M (as reported)
+Value: $12,715M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872421000020/amzn-20210630.htm</t>
       </text>
@@ -17728,7 +17738,7 @@
       <text>
         <t>Source: [AMZN] FY2021 Q3 10-Q (filed 2021-10-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $54,671M (as reported)
+Value: $7,313M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872421000028/amzn-20210930.htm</t>
       </text>
@@ -17746,7 +17756,7 @@
       <text>
         <t>Source: [AMZN] FY2022 Q1 10-Q (filed 2022-04-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $39,324M (as reported)
+Value: $-2,790M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872422000013/amzn-20220331.htm</t>
       </text>
@@ -17755,7 +17765,7 @@
       <text>
         <t>Source: [AMZN] FY2022 Q2 10-Q (filed 2022-07-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $35,574M (as reported)
+Value: $8,965M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872422000019/amzn-20220630.htm</t>
       </text>
@@ -17764,7 +17774,7 @@
       <text>
         <t>Source: [AMZN] FY2022 Q3 10-Q (filed 2022-10-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $39,665M (as reported)
+Value: $11,404M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872422000023/amzn-20220930.htm</t>
       </text>
@@ -17782,7 +17792,7 @@
       <text>
         <t>Source: [AMZN] FY2023 Q1 10-Q (filed 2023-04-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $54,330M (as reported)
+Value: $4,788M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872423000008/amzn-20230331.htm</t>
       </text>
@@ -17791,7 +17801,7 @@
       <text>
         <t>Source: [AMZN] FY2023 Q2 10-Q (filed 2023-08-04)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $61,841M (as reported)
+Value: $16,476M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872423000012/amzn-20230630.htm</t>
       </text>
@@ -17800,7 +17810,7 @@
       <text>
         <t>Source: [AMZN] FY2023 Q3 10-Q (filed 2023-10-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $71,654M (as reported)
+Value: $21,217M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872423000018/amzn-20230930.htm</t>
       </text>
@@ -17818,7 +17828,7 @@
       <text>
         <t>Source: [AMZN] FY2024 Q1 10-Q (filed 2024-05-01)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $99,147M (as reported)
+Value: $18,989M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872424000083/amzn-20240331.htm</t>
       </text>
@@ -17827,7 +17837,7 @@
       <text>
         <t>Source: [AMZN] FY2024 Q2 10-Q (filed 2024-08-02)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $107,952M (as reported)
+Value: $25,281M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872424000130/amzn-20240630.htm</t>
       </text>
@@ -17836,7 +17846,7 @@
       <text>
         <t>Source: [AMZN] FY2024 Q3 10-Q (filed 2024-11-01)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $112,706M (as reported)
+Value: $25,971M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872424000161/amzn-20240930.htm</t>
       </text>
@@ -17854,7 +17864,7 @@
       <text>
         <t>Source: [AMZN] FY2025 Q1 10-Q (filed 2025-05-02)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $113,903M (as reported)
+Value: $17,015M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872425000036/amzn-20250331.htm</t>
       </text>
@@ -17863,7 +17873,7 @@
       <text>
         <t>Source: [AMZN] FY2025 Q2 10-Q (filed 2025-08-01)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $121,137M (as reported)
+Value: $32,515M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872425000086/amzn-20250630.htm</t>
       </text>
@@ -17872,7 +17882,7 @@
       <text>
         <t>Source: [AMZN] FY2025 Q3 10-Q (filed 2025-10-31)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $130,691M (as reported)
+Value: $35,525M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872425000123/amzn-20250930.htm</t>
       </text>
@@ -17890,7 +17900,7 @@
       <text>
         <t>Source: [AMZN] FY2016 Q2 10-Q (filed 2016-07-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $7,087M (as reported)
+Value: $1,909M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872416000286/amzn-20160630x10q.htm</t>
       </text>
@@ -17899,7 +17909,7 @@
       <text>
         <t>Source: [AMZN] FY2016 Q3 10-Q (filed 2016-10-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $7,572M (as reported)
+Value: $2,084M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872416000324/amzn-20160930x10q.htm</t>
       </text>
@@ -17917,7 +17927,7 @@
       <text>
         <t>Source: [AMZN] FY2017 Q1 10-Q (filed 2017-04-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $8,725M (as reported)
+Value: $2,435M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872417000051/amzn-20170331x10q.htm</t>
       </text>
@@ -17926,7 +17936,7 @@
       <text>
         <t>Source: [AMZN] FY2017 Q2 10-Q (filed 2017-07-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $9,448M (as reported)
+Value: $2,633M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872417000100/amzn-20170630x10q.htm</t>
       </text>
@@ -17935,7 +17945,7 @@
       <text>
         <t>Source: [AMZN] FY2017 Q3 10-Q (filed 2017-10-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $10,277M (as reported)
+Value: $2,912M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872417000135/amzn-20170930x10q.htm</t>
       </text>
@@ -17953,7 +17963,7 @@
       <text>
         <t>Source: [AMZN] FY2018 Q1 10-Q (filed 2018-04-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $12,714M (as reported)
+Value: $3,671M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872418000072/amzn-20180331x10q.htm</t>
       </text>
@@ -17962,7 +17972,7 @@
       <text>
         <t>Source: [AMZN] FY2018 Q2 10-Q (filed 2018-07-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $13,711M (as reported)
+Value: $3,630M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872418000108/amzn-20180630x10q.htm</t>
       </text>
@@ -17971,7 +17981,7 @@
       <text>
         <t>Source: [AMZN] FY2018 Q3 10-Q (filed 2018-10-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $14,577M (as reported)
+Value: $3,778M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872418000159/amzn-20180930x10q.htm</t>
       </text>
@@ -17989,7 +17999,7 @@
       <text>
         <t>Source: [AMZN] FY2019 Q1 10-Q (filed 2019-04-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $16,524M (as reported)
+Value: $4,854M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872419000043/amzn-2019331x10q.htm</t>
       </text>
@@ -17998,7 +18008,7 @@
       <text>
         <t>Source: [AMZN] FY2019 Q2 10-Q (filed 2019-07-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $18,097M (as reported)
+Value: $5,202M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872419000071/amzn-2019630x10q.htm</t>
       </text>
@@ -18007,7 +18017,7 @@
       <text>
         <t>Source: [AMZN] FY2019 Q3 10-Q (filed 2019-10-25)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $19,881M (as reported)
+Value: $5,563M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872419000089/amzn-2019930x10q.htm</t>
       </text>
@@ -18025,7 +18035,7 @@
       <text>
         <t>Source: [AMZN] FY2020 Q1 10-Q (filed 2020-05-01)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $22,297M (as reported)
+Value: $5,362M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872420000010/amzn-20200331x10q.htm</t>
       </text>
@@ -18034,7 +18044,7 @@
       <text>
         <t>Source: [AMZN] FY2020 Q2 10-Q (filed 2020-07-31)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $22,843M (as reported)
+Value: $5,748M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872420000021/amzn-20200630.htm</t>
       </text>
@@ -18043,7 +18053,7 @@
       <text>
         <t>Source: [AMZN] FY2020 Q3 10-Q (filed 2020-10-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $23,803M (as reported)
+Value: $6,523M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872420000030/amzn-20200930.htm</t>
       </text>
@@ -18061,7 +18071,7 @@
       <text>
         <t>Source: [AMZN] FY2021 Q1 10-Q (filed 2021-04-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $27,397M (as reported)
+Value: $7,508M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872421000010/amzn-20210331.htm</t>
       </text>
@@ -18070,7 +18080,7 @@
       <text>
         <t>Source: [AMZN] FY2021 Q2 10-Q (filed 2021-07-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $29,687M (as reported)
+Value: $8,038M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872421000020/amzn-20210630.htm</t>
       </text>
@@ -18079,7 +18089,7 @@
       <text>
         <t>Source: [AMZN] FY2021 Q3 10-Q (filed 2021-10-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $32,112M (as reported)
+Value: $8,948M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872421000028/amzn-20210930.htm</t>
       </text>
@@ -18097,7 +18107,7 @@
       <text>
         <t>Source: [AMZN] FY2022 Q1 10-Q (filed 2022-04-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $35,766M (as reported)
+Value: $8,978M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872422000013/amzn-20220331.htm</t>
       </text>
@@ -18106,7 +18116,7 @@
       <text>
         <t>Source: [AMZN] FY2022 Q2 10-Q (filed 2022-07-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $37,322M (as reported)
+Value: $9,594M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872422000019/amzn-20220630.htm</t>
       </text>
@@ -18115,7 +18125,7 @@
       <text>
         <t>Source: [AMZN] FY2022 Q3 10-Q (filed 2022-10-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $38,578M (as reported)
+Value: $10,204M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872422000023/amzn-20220930.htm</t>
       </text>
@@ -18133,7 +18143,7 @@
       <text>
         <t>Source: [AMZN] FY2023 Q1 10-Q (filed 2023-04-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $43,851M (as reported)
+Value: $11,123M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872423000008/amzn-20230331.htm</t>
       </text>
@@ -18142,7 +18152,7 @@
       <text>
         <t>Source: [AMZN] FY2023 Q2 10-Q (filed 2023-08-04)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $45,724M (as reported)
+Value: $11,589M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872423000012/amzn-20230630.htm</t>
       </text>
@@ -18151,7 +18161,7 @@
       <text>
         <t>Source: [AMZN] FY2023 Q3 10-Q (filed 2023-10-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $47,528M (as reported)
+Value: $12,131M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872423000018/amzn-20230930.htm</t>
       </text>
@@ -18169,7 +18179,7 @@
       <text>
         <t>Source: [AMZN] FY2024 Q1 10-Q (filed 2024-05-01)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $49,224M (as reported)
+Value: $11,684M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872424000083/amzn-20240331.htm</t>
       </text>
@@ -18178,7 +18188,7 @@
       <text>
         <t>Source: [AMZN] FY2024 Q2 10-Q (filed 2024-08-02)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $49,673M (as reported)
+Value: $12,038M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872424000130/amzn-20240630.htm</t>
       </text>
@@ -18187,7 +18197,7 @@
       <text>
         <t>Source: [AMZN] FY2024 Q3 10-Q (filed 2024-11-01)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $50,984M (as reported)
+Value: $13,442M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872424000161/amzn-20240930.htm</t>
       </text>
@@ -18205,7 +18215,7 @@
       <text>
         <t>Source: [AMZN] FY2025 Q1 10-Q (filed 2025-05-02)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $55,373M (as reported)
+Value: $14,262M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872425000036/amzn-20250331.htm</t>
       </text>
@@ -18214,7 +18224,7 @@
       <text>
         <t>Source: [AMZN] FY2025 Q2 10-Q (filed 2025-08-01)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $58,562M (as reported)
+Value: $15,227M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872425000086/amzn-20250630.htm</t>
       </text>
@@ -18223,7 +18233,7 @@
       <text>
         <t>Source: [AMZN] FY2025 Q3 10-Q (filed 2025-10-31)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $61,916M (as reported)
+Value: $16,796M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872425000123/amzn-20250930.htm</t>
       </text>
@@ -18444,6 +18454,42 @@
 Report: https://www.sec.gov/Archives/edgar/data/1018724/000101872420000030/amzn-20200930.htm</t>
       </text>
     </comment>
+    <comment ref="AA14" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [APLD] FY2021 10-Q (filed 2022-05-13)
+Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
+Value: $0M (as reported)
+Method: XBRL companyfacts API
+Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1144879&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
+      </text>
+    </comment>
+    <comment ref="AB14" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [APLD] FY2021 10-K (filed 2022-08-29)
+Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
+Value: $0M (as reported)
+Method: XBRL companyfacts API
+Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1144879&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
+      </text>
+    </comment>
+    <comment ref="AC14" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [APLD] FY2021 10-Q (filed 2022-10-12)
+Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
+Value: $0M (as reported)
+Method: XBRL companyfacts API
+Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1144879&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
+      </text>
+    </comment>
+    <comment ref="AD14" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [APLD] FY2021 10-Q (filed 2023-01-10)
+Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
+Value: $0M (as reported)
+Method: XBRL companyfacts API
+Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1144879&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
+      </text>
+    </comment>
     <comment ref="AE14" authorId="0" shapeId="0">
       <text>
         <t>Source: [APLD] FY2022 10-Q (filed 2022-05-13)
@@ -18475,7 +18521,7 @@
       <text>
         <t>Source: [APLD] FY2022 10-Q (filed 2023-01-10)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $19M (as reported)
+Value: $12M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487923000028/apld-20221130.htm</t>
       </text>
@@ -18484,7 +18530,7 @@
       <text>
         <t>Source: [APLD] FY2023 10-Q (filed 2023-04-06)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $33M (as reported)
+Value: $14M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487923000101/apld-20230228.htm</t>
       </text>
@@ -18511,7 +18557,7 @@
       <text>
         <t>Source: [APLD] FY2023 10-Q (filed 2024-01-16)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $79M (as reported)
+Value: $42M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487924000010/apld-20231130.htm</t>
       </text>
@@ -18520,7 +18566,7 @@
       <text>
         <t>Source: [APLD] FY2024 10-Q (filed 2024-04-11)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $122M (as reported)
+Value: $43M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487924000078/apld-20240229.htm</t>
       </text>
@@ -18547,7 +18593,7 @@
       <text>
         <t>Source: [APLD] FY2024 10-Q (filed 2025-01-14)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $125M (as reported)
+Value: $64M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487925000006/apld-20241130.htm</t>
       </text>
@@ -18556,7 +18602,7 @@
       <text>
         <t>Source: [APLD] FY2025 10-Q (filed 2025-04-14)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $177M (as reported)
+Value: $53M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000162828025017684/apld-20250228.htm</t>
       </text>
@@ -18564,18 +18610,16 @@
     <comment ref="AR14" authorId="0" shapeId="0">
       <text>
         <t>Source: [APLD] FY2025 10-K (filed 2025-07-30)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $144M (as reported)
-Method: XBRL companyfacts API
+Derivation:
+  Derived: 9M = Q1+Q2+Q3
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487925000021/apld-20250531.htm</t>
       </text>
     </comment>
     <comment ref="AS14" authorId="0" shapeId="0">
       <text>
         <t>Source: [APLD] FY2025 10-Q (filed 2025-10-09)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $64M (as reported)
-Method: XBRL companyfacts API
+Derivation:
+  Derived: 9M = Q1+Q2+Q3
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487925000069/apld-20250831.htm</t>
       </text>
     </comment>
@@ -18583,7 +18627,7 @@
       <text>
         <t>Source: [APLD] FY2025 10-Q (filed 2026-01-08)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $191M (as reported)
+Value: $127M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487926000006/apld-20251130.htm</t>
       </text>
@@ -18592,7 +18636,7 @@
       <text>
         <t>Source: [APLD] FY2026 10-Q (filed 2026-04-08)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $353M (as reported)
+Value: $127M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487926000030/apld-20260228.htm</t>
       </text>
@@ -18938,12 +18982,20 @@
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487926000030/apld-20260228.htm</t>
       </text>
     </comment>
+    <comment ref="AA17" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [APLD] FY2021 10-Q (filed 2022-05-13)
+Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
+Value: $0M (as reported)
+Method: XBRL companyfacts API
+Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1144879&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
+      </text>
+    </comment>
     <comment ref="AB17" authorId="0" shapeId="0">
       <text>
         <t>Source: [APLD] FY2021 10-K (filed 2022-08-29)
-Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
-Value: $-0M (as reported)
-Method: XBRL companyfacts API
+Derivation:
+  Derived: Q4 = FY - 9M
 Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1144879&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
       </text>
     </comment>
@@ -19114,6 +19166,15 @@
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487926000030/apld-20260228.htm</t>
       </text>
     </comment>
+    <comment ref="AA18" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [APLD] FY2021 10-Q (filed 2022-05-13)
+Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
+Value: $0M (as reported)
+Method: XBRL companyfacts API
+Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1144879&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
+      </text>
+    </comment>
     <comment ref="AB18" authorId="0" shapeId="0">
       <text>
         <t>Source: [APLD] FY2021 10-K (filed 2022-08-29)
@@ -19172,7 +19233,7 @@
       <text>
         <t>Source: [APLD] FY2022 10-Q (filed 2023-01-10)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $3M (as reported)
+Value: $2M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487923000028/apld-20221130.htm</t>
       </text>
@@ -19181,7 +19242,7 @@
       <text>
         <t>Source: [APLD] FY2023 10-Q (filed 2023-04-06)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $5M (as reported)
+Value: $2M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487923000101/apld-20230228.htm</t>
       </text>
@@ -19208,7 +19269,7 @@
       <text>
         <t>Source: [APLD] FY2023 10-Q (filed 2024-01-16)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $21M (as reported)
+Value: $13M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487924000010/apld-20231130.htm</t>
       </text>
@@ -19217,7 +19278,7 @@
       <text>
         <t>Source: [APLD] FY2024 10-Q (filed 2024-04-11)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $48M (as reported)
+Value: $26M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487924000078/apld-20240229.htm</t>
       </text>
@@ -19244,7 +19305,7 @@
       <text>
         <t>Source: [APLD] FY2024 10-Q (filed 2025-01-14)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $61M (as reported)
+Value: $26M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487925000006/apld-20241130.htm</t>
       </text>
@@ -19253,7 +19314,7 @@
       <text>
         <t>Source: [APLD] FY2025 10-Q (filed 2025-04-14)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $80M (as reported)
+Value: $19M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000162828025017684/apld-20250228.htm</t>
       </text>
@@ -19262,16 +19323,15 @@
       <text>
         <t>Source: [APLD] FY2025 10-K (filed 2025-07-30)
 Derivation:
-  Derived: Q2 = H1 - Q1
+  Derived: 9M = Q1+Q2+Q3
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487925000021/apld-20250531.htm</t>
       </text>
     </comment>
     <comment ref="AS18" authorId="0" shapeId="0">
       <text>
         <t>Source: [APLD] FY2025 10-Q (filed 2025-10-09)
-Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $4M (as reported)
-Method: XBRL companyfacts API
+Derivation:
+  Derived: 9M = Q1+Q2+Q3
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487925000069/apld-20250831.htm</t>
       </text>
     </comment>
@@ -19279,7 +19339,7 @@
       <text>
         <t>Source: [APLD] FY2025 10-Q (filed 2026-01-08)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $13M (as reported)
+Value: $9M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487926000006/apld-20251130.htm</t>
       </text>
@@ -19288,7 +19348,7 @@
       <text>
         <t>Source: [APLD] FY2026 10-Q (filed 2026-04-08)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Depreciation and amortization"
-Value: $34M (as reported)
+Value: $21M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1144879/000114487926000030/apld-20260228.htm</t>
       </text>
@@ -21060,29 +21120,29 @@
       <text>
         <t>Source: [CRWV] FY2024 Q2 10-Q (filed 2025-08-13)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
+Value: $395M (as reported)
+Method: XBRL companyfacts API
+Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1769628&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
+      </text>
+    </comment>
+    <comment ref="AO32" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [CRWV] FY2024 Q3 10-Q (filed 2025-11-13)
+Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
 Value: $584M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1769628&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
       </text>
     </comment>
-    <comment ref="AO32" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [CRWV] FY2024 Q3 10-Q (filed 2025-11-13)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $1,168M (as reported)
+    <comment ref="AP32" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [CRWV] FY2024 10-K (filed 2026-03-02)
+Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
+Value: $1,915M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1769628&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
       </text>
     </comment>
-    <comment ref="AP32" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [CRWV] FY2024 10-K (filed 2026-03-02)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $1,915M (as reported)
-Method: XBRL companyfacts API
-Report: https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1769628&amp;type=&amp;dateb=&amp;owner=include&amp;count=40</t>
-      </text>
-    </comment>
     <comment ref="AQ32" authorId="0" shapeId="0">
       <text>
         <t>Source: [CRWV] FY2025 Q1 10-Q (filed 2025-05-15)
@@ -21096,7 +21156,7 @@
       <text>
         <t>Source: [CRWV] FY2025 Q2 10-Q (filed 2025-08-13)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $2,194M (as reported)
+Value: $1,213M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1769628/000176962825000041/crwv-20250630.htm</t>
       </text>
@@ -21105,7 +21165,7 @@
       <text>
         <t>Source: [CRWV] FY2025 Q3 10-Q (filed 2025-11-13)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $3,559M (as reported)
+Value: $1,365M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1769628/000176962825000062/crwv-20250930.htm</t>
       </text>
@@ -22272,7 +22332,7 @@
       <text>
         <t>Source: [GOOGL] FY2015 Q2 10-Q (filed 2016-08-04)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $34,985M (as reported)
+Value: $17,727M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000156761922020201/xslForm13F_X01/primary_doc.xml</t>
       </text>
@@ -22281,7 +22341,7 @@
       <text>
         <t>Source: [GOOGL] FY2015 Q3 10-Q (filed 2015-10-29)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $53,660M (as reported)
+Value: $18,675M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204415000005/alpha10-qq32015.htm</t>
       </text>
@@ -22308,7 +22368,7 @@
       <text>
         <t>Source: [GOOGL] FY2016 Q2 10-Q (filed 2016-08-04)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $41,757M (as reported)
+Value: $21,500M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204416000032/goog10-qq22016.htm</t>
       </text>
@@ -22317,7 +22377,7 @@
       <text>
         <t>Source: [GOOGL] FY2016 Q3 10-Q (filed 2016-11-03)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $64,208M (as reported)
+Value: $22,451M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204416000038/goog10-qq32016.htm</t>
       </text>
@@ -22344,7 +22404,7 @@
       <text>
         <t>Source: [GOOGL] FY2017 Q2 10-Q (filed 2017-07-25)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $50,760M (as reported)
+Value: $26,010M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204417000026/goog10-qq22017.htm</t>
       </text>
@@ -22353,7 +22413,7 @@
       <text>
         <t>Source: [GOOGL] FY2017 Q3 10-Q (filed 2017-10-27)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $78,532M (as reported)
+Value: $27,772M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204417000042/goog10-qq32017.htm</t>
       </text>
@@ -22380,7 +22440,7 @@
       <text>
         <t>Source: [GOOGL] FY2018 Q2 10-Q (filed 2018-07-24)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $63,803M (as reported)
+Value: $32,657M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204418000027/goog10-qq22018.htm</t>
       </text>
@@ -22389,7 +22449,7 @@
       <text>
         <t>Source: [GOOGL] FY2018 Q3 10-Q (filed 2018-10-26)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $97,543M (as reported)
+Value: $33,740M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204418000035/goog10-qq32018.htm</t>
       </text>
@@ -22416,7 +22476,7 @@
       <text>
         <t>Source: [GOOGL] FY2019 Q2 10-Q (filed 2019-07-26)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $75,283M (as reported)
+Value: $38,944M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204419000023/goog10-qq22019.htm</t>
       </text>
@@ -22425,7 +22485,7 @@
       <text>
         <t>Source: [GOOGL] FY2019 Q3 10-Q (filed 2019-10-29)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $115,782M (as reported)
+Value: $40,499M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204419000032/goog10-qq32019.htm</t>
       </text>
@@ -22452,7 +22512,7 @@
       <text>
         <t>Source: [GOOGL] FY2020 Q2 10-Q (filed 2020-07-31)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $79,456M (as reported)
+Value: $38,297M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204420000032/goog-20200630.htm</t>
       </text>
@@ -22461,7 +22521,7 @@
       <text>
         <t>Source: [GOOGL] FY2020 Q3 10-Q (filed 2020-10-30)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $125,629M (as reported)
+Value: $46,173M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204420000050/goog-20200930.htm</t>
       </text>
@@ -22488,7 +22548,7 @@
       <text>
         <t>Source: [GOOGL] FY2021 Q2 10-Q (filed 2021-07-28)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $117,194M (as reported)
+Value: $61,880M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204421000047/goog-20210630.htm</t>
       </text>
@@ -22497,7 +22557,7 @@
       <text>
         <t>Source: [GOOGL] FY2021 Q3 10-Q (filed 2021-10-27)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $182,312M (as reported)
+Value: $65,118M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204421000057/goog-20210930.htm</t>
       </text>
@@ -22524,7 +22584,7 @@
       <text>
         <t>Source: [GOOGL] FY2022 Q2 10-Q (filed 2022-07-27)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $137,696M (as reported)
+Value: $69,685M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204422000071/goog-20220630.htm</t>
       </text>
@@ -22533,7 +22593,7 @@
       <text>
         <t>Source: [GOOGL] FY2022 Q3 10-Q (filed 2022-10-26)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $206,788M (as reported)
+Value: $69,092M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204422000090/goog-20220930.htm</t>
       </text>
@@ -22560,7 +22620,7 @@
       <text>
         <t>Source: [GOOGL] FY2023 Q2 10-Q (filed 2023-07-26)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $144,391M (as reported)
+Value: $74,604M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204423000070/goog-20230630.htm</t>
       </text>
@@ -22569,7 +22629,7 @@
       <text>
         <t>Source: [GOOGL] FY2023 Q3 10-Q (filed 2023-10-25)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $221,084M (as reported)
+Value: $76,693M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204423000094/goog-20230930.htm</t>
       </text>
@@ -22596,7 +22656,7 @@
       <text>
         <t>Source: [GOOGL] FY2024 Q2 10-Q (filed 2024-07-24)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $165,281M (as reported)
+Value: $84,742M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204424000079/goog-20240630.htm</t>
       </text>
@@ -22605,7 +22665,7 @@
       <text>
         <t>Source: [GOOGL] FY2024 Q3 10-Q (filed 2024-10-30)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $253,549M (as reported)
+Value: $88,268M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204424000118/goog-20240930.htm</t>
       </text>
@@ -22632,7 +22692,7 @@
       <text>
         <t>Source: [GOOGL] FY2025 Q2 10-Q (filed 2025-07-24)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $186,662M (as reported)
+Value: $96,428M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204425000062/goog-20250630.htm</t>
       </text>
@@ -22641,7 +22701,7 @@
       <text>
         <t>Source: [GOOGL] FY2025 Q3 10-Q (filed 2025-10-30)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $289,007M (as reported)
+Value: $102,346M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204425000091/goog-20250930.htm</t>
       </text>
@@ -22908,7 +22968,7 @@
       <text>
         <t>Source: [GOOGL] FY2015 Q2 10-Q (filed 2016-08-04)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $5,442M (as reported)
+Value: $2,515M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000156761922020201/xslForm13F_X01/primary_doc.xml</t>
       </text>
@@ -22917,7 +22977,7 @@
       <text>
         <t>Source: [GOOGL] FY2015 Q3 10-Q (filed 2015-10-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $7,815M (as reported)
+Value: $2,383M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204415000005/alpha10-qq32015.htm</t>
       </text>
@@ -22944,7 +23004,7 @@
       <text>
         <t>Source: [GOOGL] FY2016 Q2 10-Q (filed 2016-08-04)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $4,551M (as reported)
+Value: $2,123M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204416000032/goog10-qq22016.htm</t>
       </text>
@@ -22953,7 +23013,7 @@
       <text>
         <t>Source: [GOOGL] FY2016 Q3 10-Q (filed 2016-11-03)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $7,134M (as reported)
+Value: $2,554M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204416000038/goog10-qq32016.htm</t>
       </text>
@@ -22980,7 +23040,7 @@
       <text>
         <t>Source: [GOOGL] FY2017 Q2 10-Q (filed 2017-07-25)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $5,339M (as reported)
+Value: $2,831M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204417000026/goog10-qq22017.htm</t>
       </text>
@@ -22989,7 +23049,7 @@
       <text>
         <t>Source: [GOOGL] FY2017 Q3 10-Q (filed 2017-10-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $8,877M (as reported)
+Value: $3,538M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204417000042/goog10-qq32017.htm</t>
       </text>
@@ -23016,7 +23076,7 @@
       <text>
         <t>Source: [GOOGL] FY2018 Q2 10-Q (filed 2018-07-24)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $12,776M (as reported)
+Value: $5,477M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204418000027/goog10-qq22018.htm</t>
       </text>
@@ -23025,7 +23085,7 @@
       <text>
         <t>Source: [GOOGL] FY2018 Q3 10-Q (filed 2018-10-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $18,058M (as reported)
+Value: $5,282M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204418000035/goog10-qq32018.htm</t>
       </text>
@@ -23052,7 +23112,7 @@
       <text>
         <t>Source: [GOOGL] FY2019 Q2 10-Q (filed 2019-07-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $10,764M (as reported)
+Value: $6,126M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204419000023/goog10-qq22019.htm</t>
       </text>
@@ -23061,7 +23121,7 @@
       <text>
         <t>Source: [GOOGL] FY2019 Q3 10-Q (filed 2019-10-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $17,496M (as reported)
+Value: $6,732M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204419000032/goog10-qq32019.htm</t>
       </text>
@@ -23088,7 +23148,7 @@
       <text>
         <t>Source: [GOOGL] FY2020 Q2 10-Q (filed 2020-07-31)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $11,396M (as reported)
+Value: $5,391M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204420000032/goog-20200630.htm</t>
       </text>
@@ -23097,7 +23157,7 @@
       <text>
         <t>Source: [GOOGL] FY2020 Q3 10-Q (filed 2020-10-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Purchases of property and equipment"
-Value: $16,802M (as reported)
+Value: $5,406M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1652044/000165204420000050/goog-20200930.htm</t>
       </text>
@@ -24155,7 +24215,7 @@
       <text>
         <t>Source: [META] FY2015 Q2 10-Q (filed 2015-07-31)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $7,586M (as reported)
+Value: $4,042M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680115000028/fb-6302015x10q.htm</t>
       </text>
@@ -24164,7 +24224,7 @@
       <text>
         <t>Source: [META] FY2015 Q3 10-Q (filed 2015-11-05)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $12,087M (as reported)
+Value: $4,501M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680115000032/fb-9302015x10q.htm</t>
       </text>
@@ -24191,7 +24251,7 @@
       <text>
         <t>Source: [META] FY2016 Q2 10-Q (filed 2016-07-28)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $11,818M (as reported)
+Value: $6,436M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680116000082/fb-6302016x10q.htm</t>
       </text>
@@ -24200,7 +24260,7 @@
       <text>
         <t>Source: [META] FY2016 Q3 10-Q (filed 2016-11-03)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $18,829M (as reported)
+Value: $7,011M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680116000087/fb-9302016x10q.htm</t>
       </text>
@@ -24227,7 +24287,7 @@
       <text>
         <t>Source: [META] FY2017 Q2 10-Q (filed 2017-07-27)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $17,353M (as reported)
+Value: $9,321M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680117000038/fb-06302017x10q.htm</t>
       </text>
@@ -24236,7 +24296,7 @@
       <text>
         <t>Source: [META] FY2017 Q3 10-Q (filed 2017-11-02)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $27,681M (as reported)
+Value: $10,328M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680117000053/fb-09302017x10q.htm</t>
       </text>
@@ -24263,7 +24323,7 @@
       <text>
         <t>Source: [META] FY2018 Q2 10-Q (filed 2018-07-26)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $25,197M (as reported)
+Value: $13,231M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680118000057/fb-06302018x10q.htm</t>
       </text>
@@ -24272,7 +24332,7 @@
       <text>
         <t>Source: [META] FY2018 Q3 10-Q (filed 2018-10-31)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $38,924M (as reported)
+Value: $13,727M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680118000067/fb-09302018x10q.htm</t>
       </text>
@@ -24299,7 +24359,7 @@
       <text>
         <t>Source: [META] FY2019 Q2 10-Q (filed 2019-07-25)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $31,963M (as reported)
+Value: $16,886M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680119000055/fb-06302019x10q.htm</t>
       </text>
@@ -24308,7 +24368,7 @@
       <text>
         <t>Source: [META] FY2019 Q3 10-Q (filed 2019-10-31)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $49,615M (as reported)
+Value: $17,652M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680119000069/fb-09302019x10q.htm</t>
       </text>
@@ -24335,7 +24395,7 @@
       <text>
         <t>Source: [META] FY2020 Q2 10-Q (filed 2020-07-31)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $36,423M (as reported)
+Value: $18,687M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680120000076/fb-06302020x10q.htm</t>
       </text>
@@ -24344,7 +24404,7 @@
       <text>
         <t>Source: [META] FY2020 Q3 10-Q (filed 2020-10-30)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $57,893M (as reported)
+Value: $21,470M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680120000084/fb-09302020x10q.htm</t>
       </text>
@@ -24371,7 +24431,7 @@
       <text>
         <t>Source: [META] FY2021 Q2 10-Q (filed 2021-07-29)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $55,248M (as reported)
+Value: $29,077M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680121000049/fb-20210630.htm</t>
       </text>
@@ -24380,7 +24440,7 @@
       <text>
         <t>Source: [META] FY2021 Q3 10-Q (filed 2021-10-26)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $84,258M (as reported)
+Value: $29,010M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680121000065/fb-20210930.htm</t>
       </text>
@@ -24407,7 +24467,7 @@
       <text>
         <t>Source: [META] FY2022 Q2 10-Q (filed 2022-07-28)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $56,729M (as reported)
+Value: $28,822M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680122000082/meta-20220630.htm</t>
       </text>
@@ -24416,7 +24476,7 @@
       <text>
         <t>Source: [META] FY2022 Q3 10-Q (filed 2022-10-27)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $84,444M (as reported)
+Value: $27,714M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680122000108/meta-20220930.htm</t>
       </text>
@@ -24443,7 +24503,7 @@
       <text>
         <t>Source: [META] FY2023 Q2 10-Q (filed 2023-07-27)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $60,645M (as reported)
+Value: $31,999M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680123000093/meta-20230630.htm</t>
       </text>
@@ -24452,7 +24512,7 @@
       <text>
         <t>Source: [META] FY2023 Q3 10-Q (filed 2023-10-26)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $94,791M (as reported)
+Value: $34,146M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680123000103/meta-20230930.htm</t>
       </text>
@@ -24479,7 +24539,7 @@
       <text>
         <t>Source: [META] FY2024 Q2 10-Q (filed 2024-08-01)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $75,527M (as reported)
+Value: $39,071M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680124000069/meta-20240630.htm</t>
       </text>
@@ -24488,7 +24548,7 @@
       <text>
         <t>Source: [META] FY2024 Q3 10-Q (filed 2024-10-31)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $116,116M (as reported)
+Value: $40,589M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680124000081/meta-20240930.htm</t>
       </text>
@@ -24515,7 +24575,7 @@
       <text>
         <t>Source: [META] FY2025 Q2 10-Q (filed 2025-07-31)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $89,830M (as reported)
+Value: $47,516M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000162828025036791/meta-20250630.htm</t>
       </text>
@@ -24524,7 +24584,7 @@
       <text>
         <t>Source: [META] FY2025 Q3 10-Q (filed 2025-10-30)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $141,073M (as reported)
+Value: $51,242M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000162828025047240/meta-20250930.htm</t>
       </text>
@@ -24970,6 +25030,42 @@
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680116000043/fb-12312015x10k.htm</t>
       </text>
     </comment>
+    <comment ref="G59" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [META] FY2016 10-K (filed 2017-02-03)
+Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
+Value: $2,983M (as reported)
+Method: XBRL companyfacts API
+Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680116000067/fb-3312016x10q.htm</t>
+      </text>
+    </comment>
+    <comment ref="H59" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [META] FY2016 Q2 10-Q (filed 2016-07-28)
+Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
+Value: $6,181M (as reported)
+Method: XBRL companyfacts API
+Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680116000082/fb-6302016x10q.htm</t>
+      </text>
+    </comment>
+    <comment ref="I59" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [META] FY2016 Q3 10-Q (filed 2016-11-03)
+Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
+Value: $9,758M (as reported)
+Method: XBRL companyfacts API
+Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680116000087/fb-9302016x10q.htm</t>
+      </text>
+    </comment>
+    <comment ref="J59" authorId="0" shapeId="0">
+      <text>
+        <t>Source: [META] FY2016 10-K (filed 2017-02-03)
+Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash provided by operating activities"
+Value: $16,108M (as reported)
+Method: XBRL companyfacts API
+Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680117000007/fb-12312016x10k.htm</t>
+      </text>
+    </comment>
     <comment ref="K59" authorId="0" shapeId="0">
       <text>
         <t>Source: [META] FY2017 Q1 10-Q (filed 2017-05-04)
@@ -25888,45 +25984,9 @@
 Report: https://www.sec.gov/Archives/edgar/data/1326801/000132680120000084/fb-09302020x10q.htm</t>
       </text>
     </comment>
-    <comment ref="M62" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [MSFT] FY2017 10-K (filed 2018-08-03)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $24,538M (as reported)
-Method: XBRL companyfacts API
-Report: https://www.sec.gov/Archives/edgar/data/789019/000156459017020171/msft-10q_20170930.htm</t>
-      </text>
-    </comment>
-    <comment ref="N62" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [MSFT] FY2017 10-Q (filed 2018-01-31)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $53,456M (as reported)
-Method: XBRL companyfacts API
-Report: https://www.sec.gov/Archives/edgar/data/789019/000156459018001129/msft-10q_20171231.htm</t>
-      </text>
-    </comment>
-    <comment ref="O62" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [MSFT] FY2018 Q1 10-Q (filed 2018-04-26)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $80,275M (as reported)
-Method: XBRL companyfacts API
-Report: https://www.sec.gov/Archives/edgar/data/789019/000156459018009307/msft-10q_20180331.htm</t>
-      </text>
-    </comment>
-    <comment ref="P62" authorId="0" shapeId="0">
-      <text>
-        <t>Source: [MSFT] FY2018 10-K (filed 2018-08-03)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $110,360M (as reported)
-Method: XBRL companyfacts API
-Report: https://www.sec.gov/Archives/edgar/data/789019/000156459018019062/msft-10k_20180630.htm</t>
-      </text>
-    </comment>
     <comment ref="Q62" authorId="0" shapeId="0">
       <text>
-        <t>Source: [MSFT] FY2018 Q3 10-Q (filed 2018-10-24)
+        <t>Source: [MSFT] FY2018 10-K (filed 2019-08-01)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
 Value: $29,084M (as reported)
 Method: XBRL companyfacts API
@@ -25937,7 +25997,7 @@
       <text>
         <t>Source: [MSFT] FY2018 10-Q (filed 2019-01-30)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $61,555M (as reported)
+Value: $32,471M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459019001392/msft-10q_20181231.htm</t>
       </text>
@@ -25946,7 +26006,7 @@
       <text>
         <t>Source: [MSFT] FY2019 Q1 10-Q (filed 2019-04-24)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $92,126M (as reported)
+Value: $30,571M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459019012709/msft-10q_20190331.htm</t>
       </text>
@@ -25962,7 +26022,7 @@
     </comment>
     <comment ref="U62" authorId="0" shapeId="0">
       <text>
-        <t>Source: [MSFT] FY2019 Q3 10-Q (filed 2019-10-23)
+        <t>Source: [MSFT] FY2019 10-K (filed 2020-07-30)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
 Value: $33,055M (as reported)
 Method: XBRL companyfacts API
@@ -25973,7 +26033,7 @@
       <text>
         <t>Source: [MSFT] FY2019 10-Q (filed 2020-01-29)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $69,961M (as reported)
+Value: $36,906M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459020002450/msft-10q_20191231.htm</t>
       </text>
@@ -25982,7 +26042,7 @@
       <text>
         <t>Source: [MSFT] FY2020 Q1 10-Q (filed 2020-04-29)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $104,982M (as reported)
+Value: $35,021M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459020019706/msft-10q_20200331.htm</t>
       </text>
@@ -26009,7 +26069,7 @@
       <text>
         <t>Source: [MSFT] FY2020 10-Q (filed 2021-01-26)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $80,230M (as reported)
+Value: $43,076M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459021002316/msft-10q_20201231.htm</t>
       </text>
@@ -26018,7 +26078,7 @@
       <text>
         <t>Source: [MSFT] FY2021 Q1 10-Q (filed 2021-04-27)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $121,936M (as reported)
+Value: $41,706M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459021020891/msft-10q_20210331.htm</t>
       </text>
@@ -26045,7 +26105,7 @@
       <text>
         <t>Source: [MSFT] FY2021 10-Q (filed 2022-01-25)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $97,045M (as reported)
+Value: $51,728M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459022002324/msft-10q_20211231.htm</t>
       </text>
@@ -26054,7 +26114,7 @@
       <text>
         <t>Source: [MSFT] FY2022 Q1 10-Q (filed 2022-04-26)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $146,405M (as reported)
+Value: $49,360M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459022015675/msft-10q_20220331.htm</t>
       </text>
@@ -26081,7 +26141,7 @@
       <text>
         <t>Source: [MSFT] FY2022 10-Q (filed 2023-01-24)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $102,869M (as reported)
+Value: $52,747M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459023000733/msft-10q_20221231.htm</t>
       </text>
@@ -26090,7 +26150,7 @@
       <text>
         <t>Source: [MSFT] FY2023 Q1 10-Q (filed 2023-04-25)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $155,726M (as reported)
+Value: $52,857M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017023014423/msft-20230331.htm</t>
       </text>
@@ -26117,7 +26177,7 @@
       <text>
         <t>Source: [MSFT] FY2023 10-Q (filed 2024-01-30)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $118,537M (as reported)
+Value: $62,020M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017024008814/msft-20231231.htm</t>
       </text>
@@ -26126,7 +26186,7 @@
       <text>
         <t>Source: [MSFT] FY2024 Q1 10-Q (filed 2024-04-25)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $180,395M (as reported)
+Value: $61,858M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017024048288/msft-20240331.htm</t>
       </text>
@@ -26153,7 +26213,7 @@
       <text>
         <t>Source: [MSFT] FY2024 10-Q (filed 2025-01-29)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $135,217M (as reported)
+Value: $69,632M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017025010491/msft-20241231.htm</t>
       </text>
@@ -26162,7 +26222,7 @@
       <text>
         <t>Source: [MSFT] FY2025 Q1 10-Q (filed 2025-04-30)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $205,283M (as reported)
+Value: $70,066M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017025061046/msft-20250331.htm</t>
       </text>
@@ -26179,9 +26239,8 @@
     <comment ref="AS62" authorId="0" shapeId="0">
       <text>
         <t>Source: [MSFT] FY2025 Q3 10-Q (filed 2025-10-29)
-Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $77,673M (as reported)
-Method: XBRL companyfacts API
+Derivation:
+  Derived: H1 = Q1+Q2
 Report: https://www.sec.gov/Archives/edgar/data/789019/000119312525256321/msft-20250930.htm</t>
       </text>
     </comment>
@@ -26189,7 +26248,7 @@
       <text>
         <t>Source: [MSFT] FY2025 10-Q (filed 2026-01-28)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $158,946M (as reported)
+Value: $81,273M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000119312526027207/msft-20251231.htm</t>
       </text>
@@ -26618,7 +26677,7 @@
       <text>
         <t>Source: [MSFT] FY2015 Q1 10-Q (filed 2015-04-23)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $4,163M (as reported)
+Value: $1,391M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000119312515144151/d860721d10q.htm</t>
       </text>
@@ -26645,7 +26704,7 @@
       <text>
         <t>Source: [MSFT] FY2015 10-Q (filed 2016-01-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $3,380M (as reported)
+Value: $2,024M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000119312516441821/d15167d10q.htm</t>
       </text>
@@ -26654,7 +26713,7 @@
       <text>
         <t>Source: [MSFT] FY2016 Q1 10-Q (filed 2016-04-21)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $5,688M (as reported)
+Value: $2,308M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000119312516550254/d256147d10q.htm</t>
       </text>
@@ -26681,7 +26740,7 @@
       <text>
         <t>Source: [MSFT] FY2016 10-Q (filed 2017-01-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $4,151M (as reported)
+Value: $1,988M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459017000654/msft-10q_20161231.htm</t>
       </text>
@@ -26690,7 +26749,7 @@
       <text>
         <t>Source: [MSFT] FY2017 Q1 10-Q (filed 2017-04-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $5,846M (as reported)
+Value: $1,695M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459017007547/msft-10q_20170331.htm</t>
       </text>
@@ -26717,7 +26776,7 @@
       <text>
         <t>Source: [MSFT] FY2017 10-Q (filed 2018-01-31)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $4,718M (as reported)
+Value: $2,586M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459018001129/msft-10q_20171231.htm</t>
       </text>
@@ -26726,7 +26785,7 @@
       <text>
         <t>Source: [MSFT] FY2018 Q1 10-Q (filed 2018-04-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $7,652M (as reported)
+Value: $2,934M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459018009307/msft-10q_20180331.htm</t>
       </text>
@@ -26753,7 +26812,7 @@
       <text>
         <t>Source: [MSFT] FY2018 10-Q (filed 2019-01-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $7,309M (as reported)
+Value: $3,707M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459019001392/msft-10q_20181231.htm</t>
       </text>
@@ -26762,7 +26821,7 @@
       <text>
         <t>Source: [MSFT] FY2019 Q1 10-Q (filed 2019-04-24)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $9,874M (as reported)
+Value: $2,565M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459019012709/msft-10q_20190331.htm</t>
       </text>
@@ -26789,7 +26848,7 @@
       <text>
         <t>Source: [MSFT] FY2019 10-Q (filed 2020-01-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $6,930M (as reported)
+Value: $3,545M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459020002450/msft-10q_20191231.htm</t>
       </text>
@@ -26798,7 +26857,7 @@
       <text>
         <t>Source: [MSFT] FY2020 Q1 10-Q (filed 2020-04-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $10,697M (as reported)
+Value: $3,767M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459020019706/msft-10q_20200331.htm</t>
       </text>
@@ -26825,7 +26884,7 @@
       <text>
         <t>Source: [MSFT] FY2020 10-Q (filed 2021-01-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $9,081M (as reported)
+Value: $4,174M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459021002316/msft-10q_20201231.htm</t>
       </text>
@@ -26834,7 +26893,7 @@
       <text>
         <t>Source: [MSFT] FY2021 Q1 10-Q (filed 2021-04-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $14,170M (as reported)
+Value: $5,089M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459021020891/msft-10q_20210331.htm</t>
       </text>
@@ -26861,7 +26920,7 @@
       <text>
         <t>Source: [MSFT] FY2021 10-Q (filed 2022-01-25)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $11,675M (as reported)
+Value: $5,865M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459022002324/msft-10q_20211231.htm</t>
       </text>
@@ -26870,7 +26929,7 @@
       <text>
         <t>Source: [MSFT] FY2022 Q1 10-Q (filed 2022-04-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $17,015M (as reported)
+Value: $5,340M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459022015675/msft-10q_20220331.htm</t>
       </text>
@@ -26897,7 +26956,7 @@
       <text>
         <t>Source: [MSFT] FY2022 10-Q (filed 2023-01-24)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $12,557M (as reported)
+Value: $6,274M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459023000733/msft-10q_20221231.htm</t>
       </text>
@@ -26906,7 +26965,7 @@
       <text>
         <t>Source: [MSFT] FY2023 Q1 10-Q (filed 2023-04-25)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $19,164M (as reported)
+Value: $6,607M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017023014423/msft-20230331.htm</t>
       </text>
@@ -26933,7 +26992,7 @@
       <text>
         <t>Source: [MSFT] FY2023 10-Q (filed 2024-01-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $19,652M (as reported)
+Value: $9,735M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017024008814/msft-20231231.htm</t>
       </text>
@@ -26942,7 +27001,7 @@
       <text>
         <t>Source: [MSFT] FY2024 Q1 10-Q (filed 2024-04-25)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $30,604M (as reported)
+Value: $10,952M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017024048288/msft-20240331.htm</t>
       </text>
@@ -26969,7 +27028,7 @@
       <text>
         <t>Source: [MSFT] FY2024 10-Q (filed 2025-01-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $30,727M (as reported)
+Value: $15,804M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017025010491/msft-20241231.htm</t>
       </text>
@@ -26978,7 +27037,7 @@
       <text>
         <t>Source: [MSFT] FY2025 Q1 10-Q (filed 2025-04-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $47,472M (as reported)
+Value: $16,745M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017025061046/msft-20250331.htm</t>
       </text>
@@ -26995,9 +27054,8 @@
     <comment ref="AS64" authorId="0" shapeId="0">
       <text>
         <t>Source: [MSFT] FY2025 Q3 10-Q (filed 2025-10-29)
-Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $19,394M (as reported)
-Method: XBRL companyfacts API
+Derivation:
+  Derived: H1 = Q1+Q2
 Report: https://www.sec.gov/Archives/edgar/data/789019/000119312525256321/msft-20250930.htm</t>
       </text>
     </comment>
@@ -27005,7 +27063,7 @@
       <text>
         <t>Source: [MSFT] FY2025 10-Q (filed 2026-01-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Additions to property and equipment"
-Value: $49,270M (as reported)
+Value: $29,876M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000119312526027207/msft-20251231.htm</t>
       </text>
@@ -27014,7 +27072,7 @@
       <text>
         <t>Source: [MSFT] FY2016 10-Q (filed 2017-01-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $17,842M (as reported)
+Value: $6,293M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459017000654/msft-10q_20161231.htm</t>
       </text>
@@ -27023,7 +27081,7 @@
       <text>
         <t>Source: [MSFT] FY2017 Q1 10-Q (filed 2017-04-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $28,502M (as reported)
+Value: $10,660M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459017007547/msft-10q_20170331.htm</t>
       </text>
@@ -27050,7 +27108,7 @@
       <text>
         <t>Source: [MSFT] FY2017 10-Q (filed 2018-01-31)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $20,315M (as reported)
+Value: $7,875M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459018001129/msft-10q_20171231.htm</t>
       </text>
@@ -27059,7 +27117,7 @@
       <text>
         <t>Source: [MSFT] FY2018 Q1 10-Q (filed 2018-04-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $32,466M (as reported)
+Value: $12,151M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459018009307/msft-10q_20180331.htm</t>
       </text>
@@ -27086,7 +27144,7 @@
       <text>
         <t>Source: [MSFT] FY2018 10-Q (filed 2019-01-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $22,557M (as reported)
+Value: $8,900M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459019001392/msft-10q_20181231.htm</t>
       </text>
@@ -27095,7 +27153,7 @@
       <text>
         <t>Source: [MSFT] FY2019 Q1 10-Q (filed 2019-04-24)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $36,077M (as reported)
+Value: $13,520M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459019012709/msft-10q_20190331.htm</t>
       </text>
@@ -27122,7 +27180,7 @@
       <text>
         <t>Source: [MSFT] FY2019 10-Q (filed 2020-01-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $24,498M (as reported)
+Value: $10,680M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459020002450/msft-10q_20191231.htm</t>
       </text>
@@ -27131,7 +27189,7 @@
       <text>
         <t>Source: [MSFT] FY2020 Q1 10-Q (filed 2020-04-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $42,002M (as reported)
+Value: $17,504M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459020019706/msft-10q_20200331.htm</t>
       </text>
@@ -27158,7 +27216,7 @@
       <text>
         <t>Source: [MSFT] FY2020 10-Q (filed 2021-01-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $31,851M (as reported)
+Value: $12,516M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459021002316/msft-10q_20201231.htm</t>
       </text>
@@ -27167,7 +27225,7 @@
       <text>
         <t>Source: [MSFT] FY2021 Q1 10-Q (filed 2021-04-27)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $54,030M (as reported)
+Value: $22,179M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459021020891/msft-10q_20210331.htm</t>
       </text>
@@ -27194,7 +27252,7 @@
       <text>
         <t>Source: [MSFT] FY2021 10-Q (filed 2022-01-25)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $39,020M (as reported)
+Value: $14,480M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459022002324/msft-10q_20211231.htm</t>
       </text>
@@ -27203,7 +27261,7 @@
       <text>
         <t>Source: [MSFT] FY2022 Q1 10-Q (filed 2022-04-26)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $64,406M (as reported)
+Value: $25,386M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459022015675/msft-10q_20220331.htm</t>
       </text>
@@ -27230,7 +27288,7 @@
       <text>
         <t>Source: [MSFT] FY2022 10-Q (filed 2023-01-24)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $34,371M (as reported)
+Value: $11,173M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000156459023000733/msft-10q_20221231.htm</t>
       </text>
@@ -27239,7 +27297,7 @@
       <text>
         <t>Source: [MSFT] FY2023 Q1 10-Q (filed 2023-04-25)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $58,812M (as reported)
+Value: $24,441M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017023014423/msft-20230331.htm</t>
       </text>
@@ -27266,7 +27324,7 @@
       <text>
         <t>Source: [MSFT] FY2023 10-Q (filed 2024-01-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $49,436M (as reported)
+Value: $18,853M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017024008814/msft-20231231.htm</t>
       </text>
@@ -27275,7 +27333,7 @@
       <text>
         <t>Source: [MSFT] FY2024 Q1 10-Q (filed 2024-04-25)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $81,353M (as reported)
+Value: $31,917M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017024048288/msft-20240331.htm</t>
       </text>
@@ -27302,7 +27360,7 @@
       <text>
         <t>Source: [MSFT] FY2024 10-Q (filed 2025-01-29)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $56,471M (as reported)
+Value: $22,291M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017025010491/msft-20241231.htm</t>
       </text>
@@ -27311,7 +27369,7 @@
       <text>
         <t>Source: [MSFT] FY2025 Q1 10-Q (filed 2025-04-30)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $93,515M (as reported)
+Value: $37,044M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000095017025061046/msft-20250331.htm</t>
       </text>
@@ -27328,9 +27386,8 @@
     <comment ref="AS65" authorId="0" shapeId="0">
       <text>
         <t>Source: [MSFT] FY2025 Q3 10-Q (filed 2025-10-29)
-Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $45,057M (as reported)
-Method: XBRL companyfacts API
+Derivation:
+  Derived: H1 = Q1+Q2
 Report: https://www.sec.gov/Archives/edgar/data/789019/000119312525256321/msft-20250930.htm</t>
       </text>
     </comment>
@@ -27338,7 +27395,7 @@
       <text>
         <t>Source: [MSFT] FY2025 10-Q (filed 2026-01-28)
 Section: Item 8 - Consolidated Statements of Cash Flows, line "Net cash from operations"
-Value: $80,815M (as reported)
+Value: $35,758M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/789019/000119312526027207/msft-20251231.htm</t>
       </text>
@@ -27765,7 +27822,7 @@
       <text>
         <t>Source: [ORCL] FY2015 10-Q (filed 2015-03-19)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $27,520M (as reported)
+Value: $9,327M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312515098586/d851089d10q.htm</t>
       </text>
@@ -27792,7 +27849,7 @@
       <text>
         <t>Source: [ORCL] FY2015 10-Q (filed 2015-12-18)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $17,441M (as reported)
+Value: $8,993M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312515407703/d134252d10q.htm</t>
       </text>
@@ -27801,7 +27858,7 @@
       <text>
         <t>Source: [ORCL] FY2016 10-Q (filed 2016-03-18)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $26,453M (as reported)
+Value: $9,012M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312516510333/d48108d10q.htm</t>
       </text>
@@ -27828,7 +27885,7 @@
       <text>
         <t>Source: [ORCL] FY2016 10-Q (filed 2016-12-19)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $17,630M (as reported)
+Value: $9,035M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312516797253/d289857d10q.htm</t>
       </text>
@@ -27837,7 +27894,7 @@
       <text>
         <t>Source: [ORCL] FY2017 10-Q (filed 2017-03-17)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $26,835M (as reported)
+Value: $9,205M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312517087309/d353998d10q.htm</t>
       </text>
@@ -27864,7 +27921,7 @@
       <text>
         <t>Source: [ORCL] FY2017 10-Q (filed 2017-12-18)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $18,809M (as reported)
+Value: $9,621M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312517372232/d510241d10q.htm</t>
       </text>
@@ -27873,7 +27930,7 @@
       <text>
         <t>Source: [ORCL] FY2018 10-Q (filed 2018-03-21)
 Section: Item 8 - Consolidated Statements of Income, line "Total revenue"
-Value: $28,579M (as reported)
+Value: $9,771M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312518090646/d548579d10q.htm</t>
       </text>
@@ -27900,7 +27957,7 @@
       <text>
         <t>Source: [ORCL] FY2018 10-Q (filed 2018-12-19)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $18,755M (as reported)
+Value: $9,562M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459018031113/orcl-10q_20181130.htm</t>
       </text>
@@ -27909,7 +27966,7 @@
       <text>
         <t>Source: [ORCL] FY2019 10-Q (filed 2019-03-18)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $28,369M (as reported)
+Value: $9,614M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459019008273/orcl-10q_20190228.htm</t>
       </text>
@@ -27936,7 +27993,7 @@
       <text>
         <t>Source: [ORCL] FY2019 10-Q (filed 2019-12-13)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $18,832M (as reported)
+Value: $9,614M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459019045966/orcl-10q_20191130.htm</t>
       </text>
@@ -27945,7 +28002,7 @@
       <text>
         <t>Source: [ORCL] FY2020 10-Q (filed 2020-03-13)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $28,629M (as reported)
+Value: $9,796M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459020010833/orcl-10q_20200229.htm</t>
       </text>
@@ -27972,7 +28029,7 @@
       <text>
         <t>Source: [ORCL] FY2020 10-Q (filed 2020-12-11)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $19,167M (as reported)
+Value: $9,800M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459020056896/orcl-10q_20201130.htm</t>
       </text>
@@ -27981,7 +28038,7 @@
       <text>
         <t>Source: [ORCL] FY2021 10-Q (filed 2021-03-11)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $29,252M (as reported)
+Value: $10,085M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459021012539/orcl-10q_20210228.htm</t>
       </text>
@@ -28008,7 +28065,7 @@
       <text>
         <t>Source: [ORCL] FY2021 10-Q (filed 2021-12-10)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $20,087M (as reported)
+Value: $10,360M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459021060022/orcl-10q_20211130.htm</t>
       </text>
@@ -28017,7 +28074,7 @@
       <text>
         <t>Source: [ORCL] FY2022 10-Q (filed 2022-03-11)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $30,600M (as reported)
+Value: $10,513M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459022009859/orcl-10q_20220228.htm</t>
       </text>
@@ -28044,7 +28101,7 @@
       <text>
         <t>Source: [ORCL] FY2022 10-Q (filed 2022-12-13)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $23,720M (as reported)
+Value: $12,275M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459022039278/orcl-10q_20221130.htm</t>
       </text>
@@ -28053,7 +28110,7 @@
       <text>
         <t>Source: [ORCL] FY2023 10-Q (filed 2023-03-10)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $36,118M (as reported)
+Value: $12,398M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000156459023003413/orcl-10q_20230228.htm</t>
       </text>
@@ -28080,7 +28137,7 @@
       <text>
         <t>Source: [ORCL] FY2023 10-Q (filed 2023-12-12)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $25,394M (as reported)
+Value: $12,941M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000095017023069682/orcl-20231130.htm</t>
       </text>
@@ -28089,7 +28146,7 @@
       <text>
         <t>Source: [ORCL] FY2024 10-Q (filed 2024-03-12)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $38,674M (as reported)
+Value: $13,280M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000095017024029904/orcl-20240229.htm</t>
       </text>
@@ -28116,7 +28173,7 @@
       <text>
         <t>Source: [ORCL] FY2024 10-Q (filed 2024-12-10)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $27,366M (as reported)
+Value: $14,059M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000095017024134973/orcl-20241130.htm</t>
       </text>
@@ -28125,7 +28182,7 @@
       <text>
         <t>Source: [ORCL] FY2025 10-Q (filed 2025-03-11)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $41,496M (as reported)
+Value: $14,130M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000095017025037143/orcl-20250228.htm</t>
       </text>
@@ -28142,9 +28199,8 @@
     <comment ref="AS74" authorId="0" shapeId="0">
       <text>
         <t>Source: [ORCL] FY2025 10-Q (filed 2025-09-10)
-Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $14,926M (as reported)
-Method: XBRL companyfacts API
+Derivation:
+  Derived: 9M = Q1+Q2+Q3
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312525200095/orcl-20250831.htm</t>
       </text>
     </comment>
@@ -28152,7 +28208,7 @@
       <text>
         <t>Source: [ORCL] FY2025 10-Q (filed 2025-12-11)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $30,983M (as reported)
+Value: $16,058M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312525315925/orcl-20251130.htm</t>
       </text>
@@ -28161,7 +28217,7 @@
       <text>
         <t>Source: [ORCL] FY2026 10-Q (filed 2026-03-11)
 Section: Item 8 - Consolidated Statements of Operations, line "Total revenues"
-Value: $48,173M (as reported)
+Value: $17,190M (as reported)
 Method: XBRL companyfacts API
 Report: https://www.sec.gov/Archives/edgar/data/1341439/000119312526101045/orcl-20260228.htm</t>
       </text>
@@ -30067,7 +30123,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-04-19 15:43 UTC</t>
+          <t>2026-04-19 16:04 UTC</t>
         </is>
       </c>
     </row>
@@ -30583,7 +30639,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-19 15:43 UTC</t>
+          <t>2026-04-19 16:04 UTC</t>
         </is>
       </c>
     </row>
@@ -30698,7 +30754,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -30728,11 +30784,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>xbrl-verified,claude-code,whole-company-copy@0.1.0,reconcile-derived</t>
+          <t>xbrl-verified,claude-code,reconcile-derived,whole-company-copy@0.1.0</t>
         </is>
       </c>
     </row>
@@ -30938,7 +30994,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -30968,11 +31024,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>xbrl-verified,reconcile-derived,claude-code-segment,segment-quarterly@0.1.0,msft-original-10k-restatement-fix,claude-code</t>
+          <t>xbrl-verified,claude-code-segment,segment-quarterly@0.1.0,reconcile-derived,msft-original-10k-restatement-fix,claude-code</t>
         </is>
       </c>
     </row>
@@ -31028,7 +31084,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -32449,6 +32505,9 @@
           <t>APLD</t>
         </is>
       </c>
+      <c r="H4" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="I4" s="9" t="n">
         <v>9</v>
       </c>
@@ -32459,7 +32518,7 @@
         <v>166</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>144</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5">
@@ -33042,22 +33101,22 @@
         <v>37955</v>
       </c>
       <c r="L3" s="9" t="n">
-        <v>117413</v>
+        <v>43744</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>60453</v>
+        <v>134122</v>
       </c>
       <c r="N3" s="9" t="n">
         <v>51042</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>103928</v>
+        <v>52886</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>56576</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>72383</v>
+        <v>176311</v>
       </c>
       <c r="R3" s="9" t="n">
         <v>59700</v>
@@ -33066,10 +33125,10 @@
         <v>63404</v>
       </c>
       <c r="T3" s="9" t="n">
-        <v>69982</v>
+        <v>6577</v>
       </c>
       <c r="U3" s="9" t="n">
-        <v>87436</v>
+        <v>210541</v>
       </c>
       <c r="V3" s="9" t="n">
         <v>75452</v>
@@ -33078,70 +33137,70 @@
         <v>88912</v>
       </c>
       <c r="X3" s="9" t="n">
-        <v>96145</v>
+        <v>7233</v>
       </c>
       <c r="Y3" s="9" t="n">
-        <v>125555</v>
+        <v>289919</v>
       </c>
       <c r="Z3" s="9" t="n">
         <v>108518</v>
       </c>
       <c r="AA3" s="9" t="n">
-        <v>113080</v>
+        <v>4562</v>
       </c>
       <c r="AB3" s="9" t="n">
-        <v>110812</v>
+        <v>-2268</v>
       </c>
       <c r="AC3" s="9" t="n">
-        <v>137412</v>
+        <v>359010</v>
       </c>
       <c r="AD3" s="9" t="n">
         <v>116444</v>
       </c>
       <c r="AE3" s="9" t="n">
-        <v>121234</v>
+        <v>4790</v>
       </c>
       <c r="AF3" s="9" t="n">
-        <v>127101</v>
+        <v>5867</v>
       </c>
       <c r="AG3" s="9" t="n">
-        <v>149204</v>
+        <v>386882</v>
       </c>
       <c r="AH3" s="9" t="n">
         <v>127358</v>
       </c>
       <c r="AI3" s="9" t="n">
-        <v>134383</v>
+        <v>7025</v>
       </c>
       <c r="AJ3" s="9" t="n">
-        <v>143083</v>
+        <v>8700</v>
       </c>
       <c r="AK3" s="9" t="n">
-        <v>169961</v>
+        <v>431702</v>
       </c>
       <c r="AL3" s="9" t="n">
         <v>143313</v>
       </c>
       <c r="AM3" s="9" t="n">
-        <v>147977</v>
+        <v>4664</v>
       </c>
       <c r="AN3" s="9" t="n">
-        <v>158877</v>
+        <v>10900</v>
       </c>
       <c r="AO3" s="9" t="n">
-        <v>187792</v>
+        <v>479082</v>
       </c>
       <c r="AP3" s="9" t="n">
         <v>155667</v>
       </c>
       <c r="AQ3" s="9" t="n">
-        <v>167702</v>
+        <v>12035</v>
       </c>
       <c r="AR3" s="9" t="n">
-        <v>180169</v>
+        <v>12467</v>
       </c>
       <c r="AS3" s="9" t="n">
-        <v>213386</v>
+        <v>536755</v>
       </c>
     </row>
     <row r="4">
@@ -33150,6 +33209,18 @@
           <t>APLD</t>
         </is>
       </c>
+      <c r="Z4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="AD4" s="9" t="n">
         <v>1</v>
       </c>
@@ -33160,46 +33231,46 @@
         <v>7</v>
       </c>
       <c r="AG4" s="9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AH4" s="9" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AI4" s="9" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="AJ4" s="9" t="n">
         <v>36</v>
       </c>
       <c r="AK4" s="9" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="AL4" s="9" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="AM4" s="9" t="n">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="AN4" s="9" t="n">
         <v>61</v>
       </c>
       <c r="AO4" s="9" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="AP4" s="9" t="n">
-        <v>53</v>
+        <v>-11</v>
       </c>
       <c r="AQ4" s="9" t="n">
-        <v>-33</v>
+        <v>125</v>
       </c>
       <c r="AR4" s="9" t="n">
-        <v>64</v>
+        <v>317</v>
       </c>
       <c r="AS4" s="9" t="n">
-        <v>127</v>
+        <v>-191</v>
       </c>
       <c r="AT4" s="9" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -33463,25 +33534,25 @@
         <v>189</v>
       </c>
       <c r="AM7" s="9" t="n">
-        <v>395</v>
+        <v>207</v>
       </c>
       <c r="AN7" s="9" t="n">
-        <v>584</v>
+        <v>189</v>
       </c>
       <c r="AO7" s="9" t="n">
-        <v>747</v>
+        <v>1331</v>
       </c>
       <c r="AP7" s="9" t="n">
         <v>982</v>
       </c>
       <c r="AQ7" s="9" t="n">
-        <v>1213</v>
+        <v>231</v>
       </c>
       <c r="AR7" s="9" t="n">
-        <v>1365</v>
+        <v>152</v>
       </c>
       <c r="AS7" s="9" t="n">
-        <v>1572</v>
+        <v>3766</v>
       </c>
     </row>
     <row r="8">
@@ -33606,133 +33677,133 @@
         <v>17258</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>17727</v>
+        <v>469</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>18675</v>
+        <v>948</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>21329</v>
+        <v>56314</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>20257</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>21500</v>
+        <v>1243</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>22451</v>
+        <v>951</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>26064</v>
+        <v>67821</v>
       </c>
       <c r="J9" s="9" t="n">
         <v>24750</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>26010</v>
+        <v>1260</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>27772</v>
+        <v>1762</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>32323</v>
+        <v>83083</v>
       </c>
       <c r="N9" s="9" t="n">
         <v>31146</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>32657</v>
+        <v>1511</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>33740</v>
+        <v>1083</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>39276</v>
+        <v>103079</v>
       </c>
       <c r="R9" s="9" t="n">
         <v>36339</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>38944</v>
+        <v>2605</v>
       </c>
       <c r="T9" s="9" t="n">
-        <v>40499</v>
+        <v>1555</v>
       </c>
       <c r="U9" s="9" t="n">
-        <v>46075</v>
+        <v>121358</v>
       </c>
       <c r="V9" s="9" t="n">
         <v>41159</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>38297</v>
+        <v>-2862</v>
       </c>
       <c r="X9" s="9" t="n">
-        <v>46173</v>
+        <v>7876</v>
       </c>
       <c r="Y9" s="9" t="n">
-        <v>56898</v>
+        <v>136354</v>
       </c>
       <c r="Z9" s="9" t="n">
         <v>55314</v>
       </c>
       <c r="AA9" s="9" t="n">
-        <v>61880</v>
+        <v>6566</v>
       </c>
       <c r="AB9" s="9" t="n">
-        <v>65118</v>
+        <v>3238</v>
       </c>
       <c r="AC9" s="9" t="n">
-        <v>75325</v>
+        <v>192519</v>
       </c>
       <c r="AD9" s="9" t="n">
         <v>68011</v>
       </c>
       <c r="AE9" s="9" t="n">
-        <v>69685</v>
+        <v>1674</v>
       </c>
       <c r="AF9" s="9" t="n">
-        <v>69092</v>
+        <v>-593</v>
       </c>
       <c r="AG9" s="9" t="n">
-        <v>76048</v>
+        <v>213744</v>
       </c>
       <c r="AH9" s="9" t="n">
         <v>69787</v>
       </c>
       <c r="AI9" s="9" t="n">
-        <v>74604</v>
+        <v>4817</v>
       </c>
       <c r="AJ9" s="9" t="n">
-        <v>76693</v>
+        <v>2089</v>
       </c>
       <c r="AK9" s="9" t="n">
-        <v>86310</v>
+        <v>230701</v>
       </c>
       <c r="AL9" s="9" t="n">
         <v>80539</v>
       </c>
       <c r="AM9" s="9" t="n">
-        <v>84742</v>
+        <v>4203</v>
       </c>
       <c r="AN9" s="9" t="n">
-        <v>88268</v>
+        <v>3526</v>
       </c>
       <c r="AO9" s="9" t="n">
-        <v>96469</v>
+        <v>261750</v>
       </c>
       <c r="AP9" s="9" t="n">
         <v>90234</v>
       </c>
       <c r="AQ9" s="9" t="n">
-        <v>96428</v>
+        <v>6194</v>
       </c>
       <c r="AR9" s="9" t="n">
-        <v>102345</v>
+        <v>5918</v>
       </c>
       <c r="AS9" s="9" t="n">
-        <v>113829</v>
+        <v>300490</v>
       </c>
     </row>
     <row r="10">
@@ -33767,133 +33838,133 @@
         <v>3543</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>4043</v>
+        <v>499</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>4501</v>
+        <v>459</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5841</v>
+        <v>13427</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>5382</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>6436</v>
+        <v>1054</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>7011</v>
+        <v>575</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>8809</v>
+        <v>20627</v>
       </c>
       <c r="J11" s="9" t="n">
         <v>8032</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>9321</v>
+        <v>1289</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>10328</v>
+        <v>1007</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>12972</v>
+        <v>30325</v>
       </c>
       <c r="N11" s="9" t="n">
         <v>11966</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>13231</v>
+        <v>1265</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>13727</v>
+        <v>496</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>16914</v>
+        <v>42111</v>
       </c>
       <c r="R11" s="9" t="n">
         <v>15077</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>16886</v>
+        <v>1809</v>
       </c>
       <c r="T11" s="9" t="n">
-        <v>17652</v>
+        <v>766</v>
       </c>
       <c r="U11" s="9" t="n">
-        <v>21082</v>
+        <v>53045</v>
       </c>
       <c r="V11" s="9" t="n">
         <v>17737</v>
       </c>
       <c r="W11" s="9" t="n">
-        <v>18686</v>
+        <v>950</v>
       </c>
       <c r="X11" s="9" t="n">
-        <v>21470</v>
+        <v>2783</v>
       </c>
       <c r="Y11" s="9" t="n">
-        <v>28072</v>
+        <v>64495</v>
       </c>
       <c r="Z11" s="9" t="n">
         <v>26171</v>
       </c>
       <c r="AA11" s="9" t="n">
-        <v>29077</v>
+        <v>2906</v>
       </c>
       <c r="AB11" s="9" t="n">
-        <v>29010</v>
+        <v>-67</v>
       </c>
       <c r="AC11" s="9" t="n">
-        <v>33671</v>
+        <v>88919</v>
       </c>
       <c r="AD11" s="9" t="n">
         <v>27908</v>
       </c>
       <c r="AE11" s="9" t="n">
-        <v>28821</v>
+        <v>914</v>
       </c>
       <c r="AF11" s="9" t="n">
-        <v>27715</v>
+        <v>-1108</v>
       </c>
       <c r="AG11" s="9" t="n">
-        <v>32165</v>
+        <v>88895</v>
       </c>
       <c r="AH11" s="9" t="n">
         <v>28645</v>
       </c>
       <c r="AI11" s="9" t="n">
-        <v>32000</v>
+        <v>3354</v>
       </c>
       <c r="AJ11" s="9" t="n">
-        <v>34146</v>
+        <v>2147</v>
       </c>
       <c r="AK11" s="9" t="n">
-        <v>40111</v>
+        <v>100756</v>
       </c>
       <c r="AL11" s="9" t="n">
         <v>36455</v>
       </c>
       <c r="AM11" s="9" t="n">
-        <v>39072</v>
+        <v>2616</v>
       </c>
       <c r="AN11" s="9" t="n">
-        <v>40589</v>
+        <v>1518</v>
       </c>
       <c r="AO11" s="9" t="n">
-        <v>48385</v>
+        <v>123912</v>
       </c>
       <c r="AP11" s="9" t="n">
         <v>42314</v>
       </c>
       <c r="AQ11" s="9" t="n">
-        <v>47516</v>
+        <v>5202</v>
       </c>
       <c r="AR11" s="9" t="n">
-        <v>51243</v>
+        <v>3726</v>
       </c>
       <c r="AS11" s="9" t="n">
-        <v>59893</v>
+        <v>149724</v>
       </c>
     </row>
     <row r="12">
@@ -33902,18 +33973,6 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="L12" s="9" t="n">
-        <v>24538</v>
-      </c>
-      <c r="M12" s="9" t="n">
-        <v>53456</v>
-      </c>
-      <c r="N12" s="9" t="n">
-        <v>26819</v>
-      </c>
-      <c r="O12" s="9" t="n">
-        <v>30085</v>
-      </c>
       <c r="P12" s="9" t="n">
         <v>29084</v>
       </c>
@@ -33921,10 +33980,10 @@
         <v>32471</v>
       </c>
       <c r="R12" s="9" t="n">
-        <v>30571</v>
+        <v>-1900</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>33717</v>
+        <v>95272</v>
       </c>
       <c r="T12" s="9" t="n">
         <v>33055</v>
@@ -33933,76 +33992,76 @@
         <v>36906</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>35021</v>
+        <v>-1885</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>38033</v>
+        <v>107994</v>
       </c>
       <c r="X12" s="9" t="n">
         <v>37154</v>
       </c>
       <c r="Y12" s="9" t="n">
-        <v>43076</v>
+        <v>5922</v>
       </c>
       <c r="Z12" s="9" t="n">
-        <v>41706</v>
+        <v>-1370</v>
       </c>
       <c r="AA12" s="9" t="n">
-        <v>46152</v>
+        <v>126382</v>
       </c>
       <c r="AB12" s="9" t="n">
         <v>45317</v>
       </c>
       <c r="AC12" s="9" t="n">
-        <v>51728</v>
+        <v>6411</v>
       </c>
       <c r="AD12" s="9" t="n">
-        <v>49360</v>
+        <v>-2368</v>
       </c>
       <c r="AE12" s="9" t="n">
-        <v>51865</v>
+        <v>148910</v>
       </c>
       <c r="AF12" s="9" t="n">
         <v>50122</v>
       </c>
       <c r="AG12" s="9" t="n">
-        <v>52747</v>
+        <v>2625</v>
       </c>
       <c r="AH12" s="9" t="n">
-        <v>52857</v>
+        <v>110</v>
       </c>
       <c r="AI12" s="9" t="n">
-        <v>56189</v>
+        <v>159058</v>
       </c>
       <c r="AJ12" s="9" t="n">
         <v>56517</v>
       </c>
       <c r="AK12" s="9" t="n">
-        <v>62020</v>
+        <v>5503</v>
       </c>
       <c r="AL12" s="9" t="n">
-        <v>61858</v>
+        <v>-162</v>
       </c>
       <c r="AM12" s="9" t="n">
-        <v>64727</v>
+        <v>183264</v>
       </c>
       <c r="AN12" s="9" t="n">
         <v>65585</v>
       </c>
       <c r="AO12" s="9" t="n">
-        <v>69632</v>
+        <v>4047</v>
       </c>
       <c r="AP12" s="9" t="n">
-        <v>70066</v>
+        <v>434</v>
       </c>
       <c r="AQ12" s="9" t="n">
-        <v>76441</v>
+        <v>211658</v>
       </c>
       <c r="AR12" s="9" t="n">
-        <v>77673</v>
+        <v>158946</v>
       </c>
       <c r="AS12" s="9" t="n">
-        <v>81273</v>
+        <v>-77673</v>
       </c>
     </row>
     <row r="13">
@@ -34022,139 +34081,139 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>27520</v>
+        <v>9327</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>10706</v>
+        <v>28899</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>8448</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>8993</v>
+        <v>545</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>9012</v>
+        <v>19</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>10594</v>
+        <v>28035</v>
       </c>
       <c r="H14" s="9" t="n">
         <v>8595</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>9035</v>
+        <v>440</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>9205</v>
+        <v>170</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>10893</v>
+        <v>28523</v>
       </c>
       <c r="L14" s="9" t="n">
         <v>9187</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>9622</v>
+        <v>434</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>9770</v>
+        <v>150</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>11252</v>
+        <v>30060</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>9193</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>9562</v>
+        <v>369</v>
       </c>
       <c r="R14" s="9" t="n">
-        <v>9614</v>
+        <v>52</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>11137</v>
+        <v>29892</v>
       </c>
       <c r="T14" s="9" t="n">
         <v>9218</v>
       </c>
       <c r="U14" s="9" t="n">
-        <v>9614</v>
+        <v>396</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>9797</v>
+        <v>182</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>10439</v>
+        <v>29272</v>
       </c>
       <c r="X14" s="9" t="n">
         <v>9367</v>
       </c>
       <c r="Y14" s="9" t="n">
-        <v>9800</v>
+        <v>433</v>
       </c>
       <c r="Z14" s="9" t="n">
-        <v>10085</v>
+        <v>285</v>
       </c>
       <c r="AA14" s="9" t="n">
-        <v>11227</v>
+        <v>30394</v>
       </c>
       <c r="AB14" s="9" t="n">
         <v>9728</v>
       </c>
       <c r="AC14" s="9" t="n">
-        <v>10359</v>
+        <v>632</v>
       </c>
       <c r="AD14" s="9" t="n">
-        <v>10513</v>
+        <v>153</v>
       </c>
       <c r="AE14" s="9" t="n">
-        <v>11840</v>
+        <v>31927</v>
       </c>
       <c r="AF14" s="9" t="n">
         <v>11445</v>
       </c>
       <c r="AG14" s="9" t="n">
-        <v>12275</v>
+        <v>830</v>
       </c>
       <c r="AH14" s="9" t="n">
-        <v>12398</v>
+        <v>123</v>
       </c>
       <c r="AI14" s="9" t="n">
-        <v>13836</v>
+        <v>37556</v>
       </c>
       <c r="AJ14" s="9" t="n">
         <v>12453</v>
       </c>
       <c r="AK14" s="9" t="n">
-        <v>12941</v>
+        <v>488</v>
       </c>
       <c r="AL14" s="9" t="n">
-        <v>13280</v>
+        <v>339</v>
       </c>
       <c r="AM14" s="9" t="n">
-        <v>14287</v>
+        <v>39681</v>
       </c>
       <c r="AN14" s="9" t="n">
         <v>13307</v>
       </c>
       <c r="AO14" s="9" t="n">
-        <v>14059</v>
+        <v>752</v>
       </c>
       <c r="AP14" s="9" t="n">
-        <v>14130</v>
+        <v>71</v>
       </c>
       <c r="AQ14" s="9" t="n">
-        <v>15903</v>
+        <v>43269</v>
       </c>
       <c r="AR14" s="9" t="n">
-        <v>14926</v>
+        <v>48174</v>
       </c>
       <c r="AS14" s="9" t="n">
-        <v>16057</v>
+        <v>-32116</v>
       </c>
       <c r="AT14" s="9" t="n">
-        <v>17190</v>
+        <v>1132</v>
       </c>
     </row>
   </sheetData>
@@ -34865,133 +34924,133 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>4684</v>
+        <v>871</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>-77</v>
+        <v>342</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>-183</v>
+        <v>-18</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>165</v>
+        <v>3394</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>4897</v>
+        <v>1179</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>498</v>
+        <v>532</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>645</v>
+        <v>130</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>697</v>
+        <v>4896</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>7417</v>
+        <v>1861</v>
       </c>
       <c r="L3" s="9" t="n">
-        <v>3333</v>
+        <v>1213</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>1205</v>
+        <v>8881</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>12905</v>
+        <v>3098</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="P3" s="9" t="n">
-        <v>277</v>
+        <v>109</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>115</v>
+        <v>10075</v>
       </c>
       <c r="R3" s="9" t="n">
-        <v>13619</v>
+        <v>3290</v>
       </c>
       <c r="S3" s="9" t="n">
-        <v>319</v>
+        <v>272</v>
       </c>
       <c r="T3" s="9" t="n">
-        <v>1344</v>
+        <v>1135</v>
       </c>
       <c r="U3" s="9" t="n">
-        <v>1579</v>
+        <v>12164</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>20365</v>
+        <v>6795</v>
       </c>
       <c r="W3" s="9" t="n">
-        <v>3898</v>
+        <v>664</v>
       </c>
       <c r="X3" s="9" t="n">
-        <v>6366</v>
+        <v>3604</v>
       </c>
       <c r="Y3" s="9" t="n">
-        <v>9511</v>
+        <v>29077</v>
       </c>
       <c r="Z3" s="9" t="n">
-        <v>45427</v>
+        <v>12082</v>
       </c>
       <c r="AA3" s="9" t="n">
-        <v>6829</v>
+        <v>2206</v>
       </c>
       <c r="AB3" s="9" t="n">
-        <v>4685</v>
+        <v>1460</v>
       </c>
       <c r="AC3" s="9" t="n">
-        <v>4112</v>
+        <v>45305</v>
       </c>
       <c r="AD3" s="9" t="n">
-        <v>63922</v>
+        <v>14951</v>
       </c>
       <c r="AE3" s="9" t="n">
-        <v>1436</v>
+        <v>773</v>
       </c>
       <c r="AF3" s="9" t="n">
-        <v>630</v>
+        <v>654</v>
       </c>
       <c r="AG3" s="9" t="n">
-        <v>-2343</v>
+        <v>47267</v>
       </c>
       <c r="AH3" s="9" t="n">
-        <v>62901</v>
+        <v>14207</v>
       </c>
       <c r="AI3" s="9" t="n">
-        <v>-4269</v>
+        <v>-2752</v>
       </c>
       <c r="AJ3" s="9" t="n">
-        <v>-3899</v>
+        <v>1024</v>
       </c>
       <c r="AK3" s="9" t="n">
-        <v>-2004</v>
+        <v>40250</v>
       </c>
       <c r="AL3" s="9" t="n">
-        <v>53447</v>
+        <v>14925</v>
       </c>
       <c r="AM3" s="9" t="n">
-        <v>6165</v>
+        <v>2695</v>
       </c>
       <c r="AN3" s="9" t="n">
-        <v>10141</v>
+        <v>5000</v>
       </c>
       <c r="AO3" s="9" t="n">
-        <v>13246</v>
+        <v>60379</v>
       </c>
       <c r="AP3" s="9" t="n">
-        <v>93093</v>
+        <v>25019</v>
       </c>
       <c r="AQ3" s="9" t="n">
-        <v>14563</v>
+        <v>7164</v>
       </c>
       <c r="AR3" s="9" t="n">
-        <v>12475</v>
+        <v>2912</v>
       </c>
       <c r="AS3" s="9" t="n">
-        <v>11688</v>
+        <v>96724</v>
       </c>
     </row>
     <row r="4">
@@ -35120,73 +35179,73 @@
         <v>2927</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>2515</v>
+        <v>-412</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2373</v>
+        <v>-132</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2100</v>
+        <v>7532</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>2428</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2123</v>
+        <v>-305</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2583</v>
+        <v>431</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>3078</v>
+        <v>7658</v>
       </c>
       <c r="J9" s="9" t="n">
         <v>2508</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>2831</v>
+        <v>323</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>3538</v>
+        <v>707</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>4307</v>
+        <v>9646</v>
       </c>
       <c r="N9" s="9" t="n">
         <v>7299</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>5477</v>
+        <v>-1822</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>5282</v>
+        <v>-195</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>7081</v>
+        <v>19857</v>
       </c>
       <c r="R9" s="9" t="n">
         <v>4638</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>6126</v>
+        <v>1488</v>
       </c>
       <c r="T9" s="9" t="n">
-        <v>6732</v>
+        <v>606</v>
       </c>
       <c r="U9" s="9" t="n">
-        <v>6052</v>
+        <v>16816</v>
       </c>
       <c r="V9" s="9" t="n">
         <v>6005</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>5391</v>
+        <v>-614</v>
       </c>
       <c r="X9" s="9" t="n">
-        <v>5406</v>
+        <v>15</v>
       </c>
       <c r="Y9" s="9" t="n">
-        <v>5479</v>
+        <v>16875</v>
       </c>
       <c r="Z9" s="9" t="n">
         <v>5942</v>
@@ -35420,136 +35479,136 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>4163</v>
+        <v>1391</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>1781</v>
+        <v>4553</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>1356</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2024</v>
+        <v>668</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>2308</v>
+        <v>284</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>2655</v>
+        <v>6035</v>
       </c>
       <c r="H12" s="9" t="n">
         <v>2163</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>1988</v>
+        <v>-175</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1695</v>
+        <v>-293</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>2283</v>
+        <v>6434</v>
       </c>
       <c r="L12" s="9" t="n">
         <v>2132</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>2586</v>
+        <v>454</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>2934</v>
+        <v>348</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3980</v>
+        <v>8698</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>3602</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>3707</v>
+        <v>105</v>
       </c>
       <c r="R12" s="9" t="n">
-        <v>2565</v>
+        <v>-1142</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>4051</v>
+        <v>11360</v>
       </c>
       <c r="T12" s="9" t="n">
         <v>3385</v>
       </c>
       <c r="U12" s="9" t="n">
-        <v>3545</v>
+        <v>160</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>3767</v>
+        <v>222</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>4744</v>
+        <v>11674</v>
       </c>
       <c r="X12" s="9" t="n">
         <v>4907</v>
       </c>
       <c r="Y12" s="9" t="n">
-        <v>4174</v>
+        <v>-733</v>
       </c>
       <c r="Z12" s="9" t="n">
-        <v>5089</v>
+        <v>915</v>
       </c>
       <c r="AA12" s="9" t="n">
-        <v>6452</v>
+        <v>15533</v>
       </c>
       <c r="AB12" s="9" t="n">
         <v>5810</v>
       </c>
       <c r="AC12" s="9" t="n">
-        <v>5865</v>
+        <v>55</v>
       </c>
       <c r="AD12" s="9" t="n">
-        <v>5340</v>
+        <v>-525</v>
       </c>
       <c r="AE12" s="9" t="n">
-        <v>6871</v>
+        <v>18546</v>
       </c>
       <c r="AF12" s="9" t="n">
         <v>6283</v>
       </c>
       <c r="AG12" s="9" t="n">
-        <v>6274</v>
+        <v>-9</v>
       </c>
       <c r="AH12" s="9" t="n">
-        <v>6607</v>
+        <v>333</v>
       </c>
       <c r="AI12" s="9" t="n">
-        <v>8943</v>
+        <v>21500</v>
       </c>
       <c r="AJ12" s="9" t="n">
         <v>9917</v>
       </c>
       <c r="AK12" s="9" t="n">
-        <v>9735</v>
+        <v>-182</v>
       </c>
       <c r="AL12" s="9" t="n">
-        <v>10952</v>
+        <v>1217</v>
       </c>
       <c r="AM12" s="9" t="n">
-        <v>13873</v>
+        <v>33525</v>
       </c>
       <c r="AN12" s="9" t="n">
         <v>14923</v>
       </c>
       <c r="AO12" s="9" t="n">
-        <v>15804</v>
+        <v>881</v>
       </c>
       <c r="AP12" s="9" t="n">
-        <v>16745</v>
+        <v>941</v>
       </c>
       <c r="AQ12" s="9" t="n">
-        <v>17079</v>
+        <v>47806</v>
       </c>
       <c r="AR12" s="9" t="n">
-        <v>19394</v>
+        <v>49270</v>
       </c>
       <c r="AS12" s="9" t="n">
-        <v>29876</v>
+        <v>-19394</v>
       </c>
     </row>
     <row r="13">
@@ -37781,6 +37840,9 @@
           <t>revenue</t>
         </is>
       </c>
+      <c r="J14" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="K14" s="9" t="n">
         <v>9</v>
       </c>
@@ -37791,7 +37853,7 @@
         <v>166</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>144</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15">
@@ -37896,7 +37958,7 @@
         <v>79</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>26</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
@@ -40213,22 +40275,22 @@
         <v>37955</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>117413</v>
+        <v>43744</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>60453</v>
+        <v>134122</v>
       </c>
       <c r="O8" s="9" t="n">
         <v>51042</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>103928</v>
+        <v>52886</v>
       </c>
       <c r="Q8" s="9" t="n">
         <v>56576</v>
       </c>
       <c r="R8" s="9" t="n">
-        <v>72383</v>
+        <v>176311</v>
       </c>
       <c r="S8" s="9" t="n">
         <v>59700</v>
@@ -40237,10 +40299,10 @@
         <v>63404</v>
       </c>
       <c r="U8" s="9" t="n">
-        <v>69982</v>
+        <v>6577</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>87436</v>
+        <v>210541</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>75452</v>
@@ -40249,70 +40311,70 @@
         <v>88912</v>
       </c>
       <c r="Y8" s="9" t="n">
-        <v>96145</v>
+        <v>7233</v>
       </c>
       <c r="Z8" s="9" t="n">
-        <v>125555</v>
+        <v>289919</v>
       </c>
       <c r="AA8" s="9" t="n">
         <v>108518</v>
       </c>
       <c r="AB8" s="9" t="n">
-        <v>113080</v>
+        <v>4562</v>
       </c>
       <c r="AC8" s="9" t="n">
-        <v>110812</v>
+        <v>-2268</v>
       </c>
       <c r="AD8" s="9" t="n">
-        <v>137412</v>
+        <v>359010</v>
       </c>
       <c r="AE8" s="9" t="n">
         <v>116444</v>
       </c>
       <c r="AF8" s="9" t="n">
-        <v>121234</v>
+        <v>4790</v>
       </c>
       <c r="AG8" s="9" t="n">
-        <v>127101</v>
+        <v>5867</v>
       </c>
       <c r="AH8" s="9" t="n">
-        <v>149204</v>
+        <v>386882</v>
       </c>
       <c r="AI8" s="9" t="n">
         <v>127358</v>
       </c>
       <c r="AJ8" s="9" t="n">
-        <v>134383</v>
+        <v>7025</v>
       </c>
       <c r="AK8" s="9" t="n">
-        <v>143083</v>
+        <v>8700</v>
       </c>
       <c r="AL8" s="9" t="n">
-        <v>169961</v>
+        <v>431702</v>
       </c>
       <c r="AM8" s="9" t="n">
         <v>143313</v>
       </c>
       <c r="AN8" s="9" t="n">
-        <v>147977</v>
+        <v>4664</v>
       </c>
       <c r="AO8" s="9" t="n">
-        <v>158877</v>
+        <v>10900</v>
       </c>
       <c r="AP8" s="9" t="n">
-        <v>187792</v>
+        <v>479082</v>
       </c>
       <c r="AQ8" s="9" t="n">
         <v>155667</v>
       </c>
       <c r="AR8" s="9" t="n">
-        <v>167702</v>
+        <v>12035</v>
       </c>
       <c r="AS8" s="9" t="n">
-        <v>180169</v>
+        <v>12467</v>
       </c>
       <c r="AT8" s="9" t="n">
-        <v>213386</v>
+        <v>536755</v>
       </c>
     </row>
     <row r="9">
@@ -40471,133 +40533,133 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>4684</v>
+        <v>871</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>-77</v>
+        <v>342</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>-183</v>
+        <v>-18</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>165</v>
+        <v>3394</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>4897</v>
+        <v>1179</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>498</v>
+        <v>532</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>645</v>
+        <v>130</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>697</v>
+        <v>4896</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>7417</v>
+        <v>1861</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>3333</v>
+        <v>1213</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>1205</v>
+        <v>8881</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>12905</v>
+        <v>3098</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>277</v>
+        <v>109</v>
       </c>
       <c r="R10" s="9" t="n">
-        <v>115</v>
+        <v>10075</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>13619</v>
+        <v>3290</v>
       </c>
       <c r="T10" s="9" t="n">
-        <v>319</v>
+        <v>272</v>
       </c>
       <c r="U10" s="9" t="n">
-        <v>1344</v>
+        <v>1135</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>1579</v>
+        <v>12164</v>
       </c>
       <c r="W10" s="9" t="n">
-        <v>20365</v>
+        <v>6795</v>
       </c>
       <c r="X10" s="9" t="n">
-        <v>3898</v>
+        <v>664</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>6366</v>
+        <v>3604</v>
       </c>
       <c r="Z10" s="9" t="n">
-        <v>9511</v>
+        <v>29077</v>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>45427</v>
+        <v>12082</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>6829</v>
+        <v>2206</v>
       </c>
       <c r="AC10" s="9" t="n">
-        <v>4685</v>
+        <v>1460</v>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>4112</v>
+        <v>45305</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>63922</v>
+        <v>14951</v>
       </c>
       <c r="AF10" s="9" t="n">
-        <v>1436</v>
+        <v>773</v>
       </c>
       <c r="AG10" s="9" t="n">
-        <v>630</v>
+        <v>654</v>
       </c>
       <c r="AH10" s="9" t="n">
-        <v>-2343</v>
+        <v>47267</v>
       </c>
       <c r="AI10" s="9" t="n">
-        <v>62901</v>
+        <v>14207</v>
       </c>
       <c r="AJ10" s="9" t="n">
-        <v>-4269</v>
+        <v>-2752</v>
       </c>
       <c r="AK10" s="9" t="n">
-        <v>-3899</v>
+        <v>1024</v>
       </c>
       <c r="AL10" s="9" t="n">
-        <v>-2004</v>
+        <v>40250</v>
       </c>
       <c r="AM10" s="9" t="n">
-        <v>53447</v>
+        <v>14925</v>
       </c>
       <c r="AN10" s="9" t="n">
-        <v>6165</v>
+        <v>2695</v>
       </c>
       <c r="AO10" s="9" t="n">
-        <v>10141</v>
+        <v>5000</v>
       </c>
       <c r="AP10" s="9" t="n">
-        <v>13246</v>
+        <v>60379</v>
       </c>
       <c r="AQ10" s="9" t="n">
-        <v>93093</v>
+        <v>25019</v>
       </c>
       <c r="AR10" s="9" t="n">
-        <v>14563</v>
+        <v>7164</v>
       </c>
       <c r="AS10" s="9" t="n">
-        <v>12475</v>
+        <v>2912</v>
       </c>
       <c r="AT10" s="9" t="n">
-        <v>11688</v>
+        <v>96724</v>
       </c>
     </row>
     <row r="11">
@@ -40612,136 +40674,136 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>7845</v>
+        <v>1499</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>1135</v>
+        <v>498</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>843</v>
+        <v>613</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>2097</v>
+        <v>9310</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>11258</v>
+        <v>2160</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>1468</v>
+        <v>1305</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>1877</v>
+        <v>1021</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1840</v>
+        <v>11957</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>17634</v>
+        <v>1590</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>251</v>
+        <v>2239</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>-808</v>
+        <v>22</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>1357</v>
+        <v>14583</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>18194</v>
+        <v>1791</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>3599</v>
+        <v>5658</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>4811</v>
+        <v>1139</v>
       </c>
       <c r="R11" s="9" t="n">
-        <v>4119</v>
+        <v>22135</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>34360</v>
+        <v>1846</v>
       </c>
       <c r="T11" s="9" t="n">
-        <v>1669</v>
+        <v>7272</v>
       </c>
       <c r="U11" s="9" t="n">
-        <v>-697</v>
+        <v>-1226</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>3182</v>
+        <v>30622</v>
       </c>
       <c r="W11" s="9" t="n">
-        <v>39732</v>
+        <v>3064</v>
       </c>
       <c r="X11" s="9" t="n">
-        <v>11488</v>
+        <v>17542</v>
       </c>
       <c r="Y11" s="9" t="n">
-        <v>4072</v>
+        <v>-8642</v>
       </c>
       <c r="Z11" s="9" t="n">
-        <v>10772</v>
+        <v>54100</v>
       </c>
       <c r="AA11" s="9" t="n">
-        <v>67213</v>
+        <v>4213</v>
       </c>
       <c r="AB11" s="9" t="n">
-        <v>-7891</v>
+        <v>8502</v>
       </c>
       <c r="AC11" s="9" t="n">
-        <v>-4651</v>
+        <v>-5402</v>
       </c>
       <c r="AD11" s="9" t="n">
-        <v>-8344</v>
+        <v>39014</v>
       </c>
       <c r="AE11" s="9" t="n">
-        <v>39324</v>
+        <v>2790</v>
       </c>
       <c r="AF11" s="9" t="n">
-        <v>-3750</v>
+        <v>6175</v>
       </c>
       <c r="AG11" s="9" t="n">
-        <v>4091</v>
+        <v>2439</v>
       </c>
       <c r="AH11" s="9" t="n">
-        <v>7087</v>
+        <v>35348</v>
       </c>
       <c r="AI11" s="9" t="n">
-        <v>54330</v>
+        <v>4788</v>
       </c>
       <c r="AJ11" s="9" t="n">
-        <v>7511</v>
+        <v>11688</v>
       </c>
       <c r="AK11" s="9" t="n">
-        <v>9813</v>
+        <v>4741</v>
       </c>
       <c r="AL11" s="9" t="n">
-        <v>13292</v>
+        <v>63729</v>
       </c>
       <c r="AM11" s="9" t="n">
-        <v>99147</v>
+        <v>18989</v>
       </c>
       <c r="AN11" s="9" t="n">
-        <v>8805</v>
+        <v>6292</v>
       </c>
       <c r="AO11" s="9" t="n">
-        <v>4754</v>
+        <v>690</v>
       </c>
       <c r="AP11" s="9" t="n">
-        <v>3171</v>
+        <v>89906</v>
       </c>
       <c r="AQ11" s="9" t="n">
-        <v>113903</v>
+        <v>17015</v>
       </c>
       <c r="AR11" s="9" t="n">
-        <v>7234</v>
+        <v>15500</v>
       </c>
       <c r="AS11" s="9" t="n">
-        <v>9554</v>
+        <v>3010</v>
       </c>
       <c r="AT11" s="9" t="n">
-        <v>8823</v>
+        <v>103989</v>
       </c>
     </row>
     <row r="12">
@@ -40756,121 +40818,121 @@
         </is>
       </c>
       <c r="H12" s="9" t="n">
-        <v>7087</v>
+        <v>1909</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>485</v>
+        <v>175</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>-1210</v>
+        <v>4278</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>8725</v>
+        <v>2435</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>723</v>
+        <v>198</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>829</v>
+        <v>279</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1201</v>
+        <v>8566</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>12714</v>
+        <v>3671</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>997</v>
+        <v>-41</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>866</v>
+        <v>148</v>
       </c>
       <c r="R12" s="9" t="n">
-        <v>764</v>
+        <v>11563</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>16524</v>
+        <v>4854</v>
       </c>
       <c r="T12" s="9" t="n">
-        <v>1573</v>
+        <v>348</v>
       </c>
       <c r="U12" s="9" t="n">
-        <v>1784</v>
+        <v>361</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>1908</v>
+        <v>16226</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>22297</v>
+        <v>5362</v>
       </c>
       <c r="X12" s="9" t="n">
-        <v>546</v>
+        <v>386</v>
       </c>
       <c r="Y12" s="9" t="n">
-        <v>960</v>
+        <v>775</v>
       </c>
       <c r="Z12" s="9" t="n">
-        <v>1448</v>
+        <v>18728</v>
       </c>
       <c r="AA12" s="9" t="n">
-        <v>27397</v>
+        <v>7508</v>
       </c>
       <c r="AB12" s="9" t="n">
-        <v>2290</v>
+        <v>530</v>
       </c>
       <c r="AC12" s="9" t="n">
-        <v>2425</v>
+        <v>910</v>
       </c>
       <c r="AD12" s="9" t="n">
-        <v>2184</v>
+        <v>25348</v>
       </c>
       <c r="AE12" s="9" t="n">
-        <v>35766</v>
+        <v>8978</v>
       </c>
       <c r="AF12" s="9" t="n">
-        <v>1556</v>
+        <v>616</v>
       </c>
       <c r="AG12" s="9" t="n">
-        <v>1256</v>
+        <v>610</v>
       </c>
       <c r="AH12" s="9" t="n">
-        <v>3343</v>
+        <v>31717</v>
       </c>
       <c r="AI12" s="9" t="n">
-        <v>43851</v>
+        <v>11123</v>
       </c>
       <c r="AJ12" s="9" t="n">
-        <v>1873</v>
+        <v>466</v>
       </c>
       <c r="AK12" s="9" t="n">
-        <v>1804</v>
+        <v>542</v>
       </c>
       <c r="AL12" s="9" t="n">
-        <v>1135</v>
+        <v>36532</v>
       </c>
       <c r="AM12" s="9" t="n">
-        <v>49224</v>
+        <v>11684</v>
       </c>
       <c r="AN12" s="9" t="n">
-        <v>449</v>
+        <v>354</v>
       </c>
       <c r="AO12" s="9" t="n">
-        <v>1311</v>
+        <v>1404</v>
       </c>
       <c r="AP12" s="9" t="n">
-        <v>1811</v>
+        <v>39353</v>
       </c>
       <c r="AQ12" s="9" t="n">
-        <v>55373</v>
+        <v>14262</v>
       </c>
       <c r="AR12" s="9" t="n">
-        <v>3189</v>
+        <v>965</v>
       </c>
       <c r="AS12" s="9" t="n">
-        <v>3354</v>
+        <v>1569</v>
       </c>
       <c r="AT12" s="9" t="n">
-        <v>3840</v>
+        <v>48960</v>
       </c>
     </row>
     <row r="13">
@@ -40965,6 +41027,18 @@
           <t>revenue</t>
         </is>
       </c>
+      <c r="AA14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="AE14" s="9" t="n">
         <v>1</v>
       </c>
@@ -40975,46 +41049,46 @@
         <v>7</v>
       </c>
       <c r="AH14" s="9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AI14" s="9" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AJ14" s="9" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="AK14" s="9" t="n">
         <v>36</v>
       </c>
       <c r="AL14" s="9" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="AM14" s="9" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="AN14" s="9" t="n">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="AO14" s="9" t="n">
         <v>61</v>
       </c>
       <c r="AP14" s="9" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="AQ14" s="9" t="n">
-        <v>53</v>
+        <v>-11</v>
       </c>
       <c r="AR14" s="9" t="n">
-        <v>-33</v>
+        <v>125</v>
       </c>
       <c r="AS14" s="9" t="n">
-        <v>64</v>
+        <v>317</v>
       </c>
       <c r="AT14" s="9" t="n">
-        <v>127</v>
+        <v>-191</v>
       </c>
       <c r="AU14" s="9" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -41160,6 +41234,9 @@
           <t>operating_cash_flow</t>
         </is>
       </c>
+      <c r="AA17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="AB17" s="9" t="n">
         <v>0</v>
       </c>
@@ -41232,6 +41309,9 @@
           <t>depreciation_amortization</t>
         </is>
       </c>
+      <c r="AA18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="AB18" s="9" t="n">
         <v>0</v>
       </c>
@@ -41251,46 +41331,46 @@
         <v>1</v>
       </c>
       <c r="AH18" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ18" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AK18" s="9" t="n">
         <v>8</v>
       </c>
       <c r="AL18" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM18" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="AM18" s="9" t="n">
-        <v>26</v>
-      </c>
       <c r="AN18" s="9" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="AO18" s="9" t="n">
         <v>34</v>
       </c>
       <c r="AP18" s="9" t="n">
-        <v>26</v>
+        <v>-8</v>
       </c>
       <c r="AQ18" s="9" t="n">
-        <v>19</v>
+        <v>-8</v>
       </c>
       <c r="AR18" s="9" t="n">
-        <v>-53</v>
+        <v>61</v>
       </c>
       <c r="AS18" s="9" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="AT18" s="9" t="n">
-        <v>9</v>
+        <v>-25</v>
       </c>
       <c r="AU18" s="9" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -41929,25 +42009,25 @@
         <v>189</v>
       </c>
       <c r="AN32" s="9" t="n">
-        <v>395</v>
+        <v>207</v>
       </c>
       <c r="AO32" s="9" t="n">
-        <v>584</v>
+        <v>189</v>
       </c>
       <c r="AP32" s="9" t="n">
-        <v>747</v>
+        <v>1331</v>
       </c>
       <c r="AQ32" s="9" t="n">
         <v>982</v>
       </c>
       <c r="AR32" s="9" t="n">
-        <v>1213</v>
+        <v>231</v>
       </c>
       <c r="AS32" s="9" t="n">
-        <v>1365</v>
+        <v>152</v>
       </c>
       <c r="AT32" s="9" t="n">
-        <v>1572</v>
+        <v>3766</v>
       </c>
     </row>
     <row r="33">
@@ -42415,133 +42495,133 @@
         <v>17258</v>
       </c>
       <c r="D44" s="9" t="n">
-        <v>17727</v>
+        <v>469</v>
       </c>
       <c r="E44" s="9" t="n">
-        <v>18675</v>
+        <v>948</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>21329</v>
+        <v>56314</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>20257</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>21500</v>
+        <v>1243</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>22451</v>
+        <v>951</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>26064</v>
+        <v>67821</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>24750</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>26010</v>
+        <v>1260</v>
       </c>
       <c r="M44" s="9" t="n">
-        <v>27772</v>
+        <v>1762</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>32323</v>
+        <v>83083</v>
       </c>
       <c r="O44" s="9" t="n">
         <v>31146</v>
       </c>
       <c r="P44" s="9" t="n">
-        <v>32657</v>
+        <v>1511</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>33740</v>
+        <v>1083</v>
       </c>
       <c r="R44" s="9" t="n">
-        <v>39276</v>
+        <v>103079</v>
       </c>
       <c r="S44" s="9" t="n">
         <v>36339</v>
       </c>
       <c r="T44" s="9" t="n">
-        <v>38944</v>
+        <v>2605</v>
       </c>
       <c r="U44" s="9" t="n">
-        <v>40499</v>
+        <v>1555</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>46075</v>
+        <v>121358</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>41159</v>
       </c>
       <c r="X44" s="9" t="n">
-        <v>38297</v>
+        <v>-2862</v>
       </c>
       <c r="Y44" s="9" t="n">
-        <v>46173</v>
+        <v>7876</v>
       </c>
       <c r="Z44" s="9" t="n">
-        <v>56898</v>
+        <v>136354</v>
       </c>
       <c r="AA44" s="9" t="n">
         <v>55314</v>
       </c>
       <c r="AB44" s="9" t="n">
-        <v>61880</v>
+        <v>6566</v>
       </c>
       <c r="AC44" s="9" t="n">
-        <v>65118</v>
+        <v>3238</v>
       </c>
       <c r="AD44" s="9" t="n">
-        <v>75325</v>
+        <v>192519</v>
       </c>
       <c r="AE44" s="9" t="n">
         <v>68011</v>
       </c>
       <c r="AF44" s="9" t="n">
-        <v>69685</v>
+        <v>1674</v>
       </c>
       <c r="AG44" s="9" t="n">
-        <v>69092</v>
+        <v>-593</v>
       </c>
       <c r="AH44" s="9" t="n">
-        <v>76048</v>
+        <v>213744</v>
       </c>
       <c r="AI44" s="9" t="n">
         <v>69787</v>
       </c>
       <c r="AJ44" s="9" t="n">
-        <v>74604</v>
+        <v>4817</v>
       </c>
       <c r="AK44" s="9" t="n">
-        <v>76693</v>
+        <v>2089</v>
       </c>
       <c r="AL44" s="9" t="n">
-        <v>86310</v>
+        <v>230701</v>
       </c>
       <c r="AM44" s="9" t="n">
         <v>80539</v>
       </c>
       <c r="AN44" s="9" t="n">
-        <v>84742</v>
+        <v>4203</v>
       </c>
       <c r="AO44" s="9" t="n">
-        <v>88268</v>
+        <v>3526</v>
       </c>
       <c r="AP44" s="9" t="n">
-        <v>96469</v>
+        <v>261750</v>
       </c>
       <c r="AQ44" s="9" t="n">
         <v>90234</v>
       </c>
       <c r="AR44" s="9" t="n">
-        <v>96428</v>
+        <v>6194</v>
       </c>
       <c r="AS44" s="9" t="n">
-        <v>102345</v>
+        <v>5918</v>
       </c>
       <c r="AT44" s="9" t="n">
-        <v>113829</v>
+        <v>300490</v>
       </c>
     </row>
     <row r="45">
@@ -42643,73 +42723,73 @@
         <v>2927</v>
       </c>
       <c r="D46" s="9" t="n">
-        <v>2515</v>
+        <v>-412</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>2373</v>
+        <v>-132</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>2100</v>
+        <v>7532</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>2428</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>2123</v>
+        <v>-305</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>2583</v>
+        <v>431</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>3078</v>
+        <v>7658</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>2508</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>2831</v>
+        <v>323</v>
       </c>
       <c r="M46" s="9" t="n">
-        <v>3538</v>
+        <v>707</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>4307</v>
+        <v>9646</v>
       </c>
       <c r="O46" s="9" t="n">
         <v>7299</v>
       </c>
       <c r="P46" s="9" t="n">
-        <v>5477</v>
+        <v>-1822</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>5282</v>
+        <v>-195</v>
       </c>
       <c r="R46" s="9" t="n">
-        <v>7081</v>
+        <v>19857</v>
       </c>
       <c r="S46" s="9" t="n">
         <v>4638</v>
       </c>
       <c r="T46" s="9" t="n">
-        <v>6126</v>
+        <v>1488</v>
       </c>
       <c r="U46" s="9" t="n">
-        <v>6732</v>
+        <v>606</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>6052</v>
+        <v>16816</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>6005</v>
       </c>
       <c r="X46" s="9" t="n">
-        <v>5391</v>
+        <v>-614</v>
       </c>
       <c r="Y46" s="9" t="n">
-        <v>5406</v>
+        <v>15</v>
       </c>
       <c r="Z46" s="9" t="n">
-        <v>5479</v>
+        <v>16875</v>
       </c>
       <c r="AA46" s="9" t="n">
         <v>5942</v>
@@ -43177,133 +43257,133 @@
         <v>3543</v>
       </c>
       <c r="D56" s="9" t="n">
-        <v>4043</v>
+        <v>499</v>
       </c>
       <c r="E56" s="9" t="n">
-        <v>4501</v>
+        <v>459</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>5841</v>
+        <v>13427</v>
       </c>
       <c r="G56" s="9" t="n">
         <v>5382</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>6436</v>
+        <v>1054</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>7011</v>
+        <v>575</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>8809</v>
+        <v>20627</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>8032</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>9321</v>
+        <v>1289</v>
       </c>
       <c r="M56" s="9" t="n">
-        <v>10328</v>
+        <v>1007</v>
       </c>
       <c r="N56" s="9" t="n">
-        <v>12972</v>
+        <v>30325</v>
       </c>
       <c r="O56" s="9" t="n">
         <v>11966</v>
       </c>
       <c r="P56" s="9" t="n">
-        <v>13231</v>
+        <v>1265</v>
       </c>
       <c r="Q56" s="9" t="n">
-        <v>13727</v>
+        <v>496</v>
       </c>
       <c r="R56" s="9" t="n">
-        <v>16914</v>
+        <v>42111</v>
       </c>
       <c r="S56" s="9" t="n">
         <v>15077</v>
       </c>
       <c r="T56" s="9" t="n">
-        <v>16886</v>
+        <v>1809</v>
       </c>
       <c r="U56" s="9" t="n">
-        <v>17652</v>
+        <v>766</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>21082</v>
+        <v>53045</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>17737</v>
       </c>
       <c r="X56" s="9" t="n">
-        <v>18686</v>
+        <v>950</v>
       </c>
       <c r="Y56" s="9" t="n">
-        <v>21470</v>
+        <v>2783</v>
       </c>
       <c r="Z56" s="9" t="n">
-        <v>28072</v>
+        <v>64495</v>
       </c>
       <c r="AA56" s="9" t="n">
         <v>26171</v>
       </c>
       <c r="AB56" s="9" t="n">
-        <v>29077</v>
+        <v>2906</v>
       </c>
       <c r="AC56" s="9" t="n">
-        <v>29010</v>
+        <v>-67</v>
       </c>
       <c r="AD56" s="9" t="n">
-        <v>33671</v>
+        <v>88919</v>
       </c>
       <c r="AE56" s="9" t="n">
         <v>27908</v>
       </c>
       <c r="AF56" s="9" t="n">
-        <v>28821</v>
+        <v>914</v>
       </c>
       <c r="AG56" s="9" t="n">
-        <v>27715</v>
+        <v>-1108</v>
       </c>
       <c r="AH56" s="9" t="n">
-        <v>32165</v>
+        <v>88895</v>
       </c>
       <c r="AI56" s="9" t="n">
         <v>28645</v>
       </c>
       <c r="AJ56" s="9" t="n">
-        <v>32000</v>
+        <v>3354</v>
       </c>
       <c r="AK56" s="9" t="n">
-        <v>34146</v>
+        <v>2147</v>
       </c>
       <c r="AL56" s="9" t="n">
-        <v>40111</v>
+        <v>100756</v>
       </c>
       <c r="AM56" s="9" t="n">
         <v>36455</v>
       </c>
       <c r="AN56" s="9" t="n">
-        <v>39072</v>
+        <v>2616</v>
       </c>
       <c r="AO56" s="9" t="n">
-        <v>40589</v>
+        <v>1518</v>
       </c>
       <c r="AP56" s="9" t="n">
-        <v>48385</v>
+        <v>123912</v>
       </c>
       <c r="AQ56" s="9" t="n">
         <v>42314</v>
       </c>
       <c r="AR56" s="9" t="n">
-        <v>47516</v>
+        <v>5202</v>
       </c>
       <c r="AS56" s="9" t="n">
-        <v>51243</v>
+        <v>3726</v>
       </c>
       <c r="AT56" s="9" t="n">
-        <v>59893</v>
+        <v>149724</v>
       </c>
     </row>
     <row r="57">
@@ -43485,6 +43565,18 @@
       <c r="F59" s="9" t="n">
         <v>2827</v>
       </c>
+      <c r="G59" s="9" t="n">
+        <v>2983</v>
+      </c>
+      <c r="H59" s="9" t="n">
+        <v>6181</v>
+      </c>
+      <c r="I59" s="9" t="n">
+        <v>3577</v>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>6350</v>
+      </c>
       <c r="K59" s="9" t="n">
         <v>5058</v>
       </c>
@@ -43827,18 +43919,6 @@
           <t>revenue</t>
         </is>
       </c>
-      <c r="M62" s="9" t="n">
-        <v>24538</v>
-      </c>
-      <c r="N62" s="9" t="n">
-        <v>53456</v>
-      </c>
-      <c r="O62" s="9" t="n">
-        <v>26819</v>
-      </c>
-      <c r="P62" s="9" t="n">
-        <v>30085</v>
-      </c>
       <c r="Q62" s="9" t="n">
         <v>29084</v>
       </c>
@@ -43846,10 +43926,10 @@
         <v>32471</v>
       </c>
       <c r="S62" s="9" t="n">
-        <v>30571</v>
+        <v>-1900</v>
       </c>
       <c r="T62" s="9" t="n">
-        <v>33717</v>
+        <v>95272</v>
       </c>
       <c r="U62" s="9" t="n">
         <v>33055</v>
@@ -43858,76 +43938,76 @@
         <v>36906</v>
       </c>
       <c r="W62" s="9" t="n">
-        <v>35021</v>
+        <v>-1885</v>
       </c>
       <c r="X62" s="9" t="n">
-        <v>38033</v>
+        <v>107994</v>
       </c>
       <c r="Y62" s="9" t="n">
         <v>37154</v>
       </c>
       <c r="Z62" s="9" t="n">
-        <v>43076</v>
+        <v>5922</v>
       </c>
       <c r="AA62" s="9" t="n">
-        <v>41706</v>
+        <v>-1370</v>
       </c>
       <c r="AB62" s="9" t="n">
-        <v>46152</v>
+        <v>126382</v>
       </c>
       <c r="AC62" s="9" t="n">
         <v>45317</v>
       </c>
       <c r="AD62" s="9" t="n">
-        <v>51728</v>
+        <v>6411</v>
       </c>
       <c r="AE62" s="9" t="n">
-        <v>49360</v>
+        <v>-2368</v>
       </c>
       <c r="AF62" s="9" t="n">
-        <v>51865</v>
+        <v>148910</v>
       </c>
       <c r="AG62" s="9" t="n">
         <v>50122</v>
       </c>
       <c r="AH62" s="9" t="n">
-        <v>52747</v>
+        <v>2625</v>
       </c>
       <c r="AI62" s="9" t="n">
-        <v>52857</v>
+        <v>110</v>
       </c>
       <c r="AJ62" s="9" t="n">
-        <v>56189</v>
+        <v>159058</v>
       </c>
       <c r="AK62" s="9" t="n">
         <v>56517</v>
       </c>
       <c r="AL62" s="9" t="n">
-        <v>62020</v>
+        <v>5503</v>
       </c>
       <c r="AM62" s="9" t="n">
-        <v>61858</v>
+        <v>-162</v>
       </c>
       <c r="AN62" s="9" t="n">
-        <v>64727</v>
+        <v>183264</v>
       </c>
       <c r="AO62" s="9" t="n">
         <v>65585</v>
       </c>
       <c r="AP62" s="9" t="n">
-        <v>69632</v>
+        <v>4047</v>
       </c>
       <c r="AQ62" s="9" t="n">
-        <v>70066</v>
+        <v>434</v>
       </c>
       <c r="AR62" s="9" t="n">
-        <v>76441</v>
+        <v>211658</v>
       </c>
       <c r="AS62" s="9" t="n">
-        <v>77673</v>
+        <v>158946</v>
       </c>
       <c r="AT62" s="9" t="n">
-        <v>81273</v>
+        <v>-77673</v>
       </c>
     </row>
     <row r="63">
@@ -44080,136 +44160,136 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>4163</v>
+        <v>1391</v>
       </c>
       <c r="D64" s="9" t="n">
-        <v>1781</v>
+        <v>4553</v>
       </c>
       <c r="E64" s="9" t="n">
         <v>1356</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>2024</v>
+        <v>668</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>2308</v>
+        <v>284</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>2655</v>
+        <v>6035</v>
       </c>
       <c r="I64" s="9" t="n">
         <v>2163</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>1988</v>
+        <v>-175</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>1695</v>
+        <v>-293</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>2283</v>
+        <v>6434</v>
       </c>
       <c r="M64" s="9" t="n">
         <v>2132</v>
       </c>
       <c r="N64" s="9" t="n">
-        <v>2586</v>
+        <v>454</v>
       </c>
       <c r="O64" s="9" t="n">
-        <v>2934</v>
+        <v>348</v>
       </c>
       <c r="P64" s="9" t="n">
-        <v>3980</v>
+        <v>8698</v>
       </c>
       <c r="Q64" s="9" t="n">
         <v>3602</v>
       </c>
       <c r="R64" s="9" t="n">
-        <v>3707</v>
+        <v>105</v>
       </c>
       <c r="S64" s="9" t="n">
-        <v>2565</v>
+        <v>-1142</v>
       </c>
       <c r="T64" s="9" t="n">
-        <v>4051</v>
+        <v>11360</v>
       </c>
       <c r="U64" s="9" t="n">
         <v>3385</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>3545</v>
+        <v>160</v>
       </c>
       <c r="W64" s="9" t="n">
-        <v>3767</v>
+        <v>222</v>
       </c>
       <c r="X64" s="9" t="n">
-        <v>4744</v>
+        <v>11674</v>
       </c>
       <c r="Y64" s="9" t="n">
         <v>4907</v>
       </c>
       <c r="Z64" s="9" t="n">
-        <v>4174</v>
+        <v>-733</v>
       </c>
       <c r="AA64" s="9" t="n">
-        <v>5089</v>
+        <v>915</v>
       </c>
       <c r="AB64" s="9" t="n">
-        <v>6452</v>
+        <v>15533</v>
       </c>
       <c r="AC64" s="9" t="n">
         <v>5810</v>
       </c>
       <c r="AD64" s="9" t="n">
-        <v>5865</v>
+        <v>55</v>
       </c>
       <c r="AE64" s="9" t="n">
-        <v>5340</v>
+        <v>-525</v>
       </c>
       <c r="AF64" s="9" t="n">
-        <v>6871</v>
+        <v>18546</v>
       </c>
       <c r="AG64" s="9" t="n">
         <v>6283</v>
       </c>
       <c r="AH64" s="9" t="n">
-        <v>6274</v>
+        <v>-9</v>
       </c>
       <c r="AI64" s="9" t="n">
-        <v>6607</v>
+        <v>333</v>
       </c>
       <c r="AJ64" s="9" t="n">
-        <v>8943</v>
+        <v>21500</v>
       </c>
       <c r="AK64" s="9" t="n">
         <v>9917</v>
       </c>
       <c r="AL64" s="9" t="n">
-        <v>9735</v>
+        <v>-182</v>
       </c>
       <c r="AM64" s="9" t="n">
-        <v>10952</v>
+        <v>1217</v>
       </c>
       <c r="AN64" s="9" t="n">
-        <v>13873</v>
+        <v>33525</v>
       </c>
       <c r="AO64" s="9" t="n">
         <v>14923</v>
       </c>
       <c r="AP64" s="9" t="n">
-        <v>15804</v>
+        <v>881</v>
       </c>
       <c r="AQ64" s="9" t="n">
-        <v>16745</v>
+        <v>941</v>
       </c>
       <c r="AR64" s="9" t="n">
-        <v>17079</v>
+        <v>47806</v>
       </c>
       <c r="AS64" s="9" t="n">
-        <v>19394</v>
+        <v>49270</v>
       </c>
       <c r="AT64" s="9" t="n">
-        <v>29876</v>
+        <v>-19394</v>
       </c>
     </row>
     <row r="65">
@@ -44224,115 +44304,115 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>17842</v>
+        <v>6293</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>10660</v>
+        <v>4367</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>11005</v>
+        <v>28847</v>
       </c>
       <c r="M65" s="9" t="n">
         <v>12440</v>
       </c>
       <c r="N65" s="9" t="n">
-        <v>7875</v>
+        <v>-4565</v>
       </c>
       <c r="O65" s="9" t="n">
-        <v>12151</v>
+        <v>4276</v>
       </c>
       <c r="P65" s="9" t="n">
-        <v>11418</v>
+        <v>31733</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>13657</v>
       </c>
       <c r="R65" s="9" t="n">
-        <v>8900</v>
+        <v>-4757</v>
       </c>
       <c r="S65" s="9" t="n">
-        <v>13520</v>
+        <v>4620</v>
       </c>
       <c r="T65" s="9" t="n">
-        <v>16108</v>
+        <v>38665</v>
       </c>
       <c r="U65" s="9" t="n">
         <v>13818</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>10680</v>
+        <v>-3138</v>
       </c>
       <c r="W65" s="9" t="n">
-        <v>17504</v>
+        <v>6824</v>
       </c>
       <c r="X65" s="9" t="n">
-        <v>18673</v>
+        <v>43171</v>
       </c>
       <c r="Y65" s="9" t="n">
         <v>19335</v>
       </c>
       <c r="Z65" s="9" t="n">
-        <v>12516</v>
+        <v>-6819</v>
       </c>
       <c r="AA65" s="9" t="n">
-        <v>22179</v>
+        <v>9663</v>
       </c>
       <c r="AB65" s="9" t="n">
-        <v>22710</v>
+        <v>54561</v>
       </c>
       <c r="AC65" s="9" t="n">
         <v>24540</v>
       </c>
       <c r="AD65" s="9" t="n">
-        <v>14480</v>
+        <v>-10060</v>
       </c>
       <c r="AE65" s="9" t="n">
-        <v>25386</v>
+        <v>10906</v>
       </c>
       <c r="AF65" s="9" t="n">
-        <v>24629</v>
+        <v>63649</v>
       </c>
       <c r="AG65" s="9" t="n">
         <v>23198</v>
       </c>
       <c r="AH65" s="9" t="n">
-        <v>11173</v>
+        <v>-12025</v>
       </c>
       <c r="AI65" s="9" t="n">
-        <v>24441</v>
+        <v>13268</v>
       </c>
       <c r="AJ65" s="9" t="n">
-        <v>28770</v>
+        <v>63141</v>
       </c>
       <c r="AK65" s="9" t="n">
         <v>30583</v>
       </c>
       <c r="AL65" s="9" t="n">
-        <v>18853</v>
+        <v>-11730</v>
       </c>
       <c r="AM65" s="9" t="n">
-        <v>31917</v>
+        <v>13064</v>
       </c>
       <c r="AN65" s="9" t="n">
-        <v>37195</v>
+        <v>86631</v>
       </c>
       <c r="AO65" s="9" t="n">
         <v>34180</v>
       </c>
       <c r="AP65" s="9" t="n">
-        <v>22291</v>
+        <v>-11889</v>
       </c>
       <c r="AQ65" s="9" t="n">
-        <v>37044</v>
+        <v>14753</v>
       </c>
       <c r="AR65" s="9" t="n">
-        <v>42647</v>
+        <v>99118</v>
       </c>
       <c r="AS65" s="9" t="n">
-        <v>45057</v>
+        <v>80815</v>
       </c>
       <c r="AT65" s="9" t="n">
-        <v>35758</v>
+        <v>-45057</v>
       </c>
     </row>
     <row r="66">
@@ -44581,139 +44661,139 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>27520</v>
+        <v>9327</v>
       </c>
       <c r="D74" s="9" t="n">
-        <v>10706</v>
+        <v>28899</v>
       </c>
       <c r="E74" s="9" t="n">
         <v>8448</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>8993</v>
+        <v>545</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>9012</v>
+        <v>19</v>
       </c>
       <c r="H74" s="9" t="n">
-        <v>10594</v>
+        <v>28035</v>
       </c>
       <c r="I74" s="9" t="n">
         <v>8595</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>9035</v>
+        <v>440</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>9205</v>
+        <v>170</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>10893</v>
+        <v>28523</v>
       </c>
       <c r="M74" s="9" t="n">
         <v>9187</v>
       </c>
       <c r="N74" s="9" t="n">
-        <v>9622</v>
+        <v>434</v>
       </c>
       <c r="O74" s="9" t="n">
-        <v>9770</v>
+        <v>150</v>
       </c>
       <c r="P74" s="9" t="n">
-        <v>11252</v>
+        <v>30060</v>
       </c>
       <c r="Q74" s="9" t="n">
         <v>9193</v>
       </c>
       <c r="R74" s="9" t="n">
-        <v>9562</v>
+        <v>369</v>
       </c>
       <c r="S74" s="9" t="n">
-        <v>9614</v>
+        <v>52</v>
       </c>
       <c r="T74" s="9" t="n">
-        <v>11137</v>
+        <v>29892</v>
       </c>
       <c r="U74" s="9" t="n">
         <v>9218</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>9614</v>
+        <v>396</v>
       </c>
       <c r="W74" s="9" t="n">
-        <v>9797</v>
+        <v>182</v>
       </c>
       <c r="X74" s="9" t="n">
-        <v>10439</v>
+        <v>29272</v>
       </c>
       <c r="Y74" s="9" t="n">
         <v>9367</v>
       </c>
       <c r="Z74" s="9" t="n">
-        <v>9800</v>
+        <v>433</v>
       </c>
       <c r="AA74" s="9" t="n">
-        <v>10085</v>
+        <v>285</v>
       </c>
       <c r="AB74" s="9" t="n">
-        <v>11227</v>
+        <v>30394</v>
       </c>
       <c r="AC74" s="9" t="n">
         <v>9728</v>
       </c>
       <c r="AD74" s="9" t="n">
-        <v>10359</v>
+        <v>632</v>
       </c>
       <c r="AE74" s="9" t="n">
-        <v>10513</v>
+        <v>153</v>
       </c>
       <c r="AF74" s="9" t="n">
-        <v>11840</v>
+        <v>31927</v>
       </c>
       <c r="AG74" s="9" t="n">
         <v>11445</v>
       </c>
       <c r="AH74" s="9" t="n">
-        <v>12275</v>
+        <v>830</v>
       </c>
       <c r="AI74" s="9" t="n">
-        <v>12398</v>
+        <v>123</v>
       </c>
       <c r="AJ74" s="9" t="n">
-        <v>13836</v>
+        <v>37556</v>
       </c>
       <c r="AK74" s="9" t="n">
         <v>12453</v>
       </c>
       <c r="AL74" s="9" t="n">
-        <v>12941</v>
+        <v>488</v>
       </c>
       <c r="AM74" s="9" t="n">
-        <v>13280</v>
+        <v>339</v>
       </c>
       <c r="AN74" s="9" t="n">
-        <v>14287</v>
+        <v>39681</v>
       </c>
       <c r="AO74" s="9" t="n">
         <v>13307</v>
       </c>
       <c r="AP74" s="9" t="n">
-        <v>14059</v>
+        <v>752</v>
       </c>
       <c r="AQ74" s="9" t="n">
-        <v>14130</v>
+        <v>71</v>
       </c>
       <c r="AR74" s="9" t="n">
-        <v>15903</v>
+        <v>43269</v>
       </c>
       <c r="AS74" s="9" t="n">
-        <v>14926</v>
+        <v>48174</v>
       </c>
       <c r="AT74" s="9" t="n">
-        <v>16057</v>
+        <v>-32116</v>
       </c>
       <c r="AU74" s="9" t="n">
-        <v>17190</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="75">
